--- a/database/event/5286/event_5286_evp_summary.xlsx
+++ b/database/event/5286/event_5286_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.183</v>
+        <v>6.1492</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1159</v>
+        <v>1.1098</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0764</v>
+        <v>2.0059</v>
       </c>
       <c r="E2" t="n">
-        <v>6.183</v>
+        <v>6.1492</v>
       </c>
       <c r="F2" t="n">
-        <v>6.0112</v>
+        <v>5.9774</v>
       </c>
       <c r="G2" t="n">
         <v>0.1718</v>
       </c>
       <c r="H2" t="n">
-        <v>7.1225</v>
+        <v>7.0695</v>
       </c>
       <c r="I2" t="n">
         <v>7.189</v>
@@ -548,7 +548,7 @@
         <v>1.0842</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0056</v>
+        <v>1.9496</v>
       </c>
       <c r="E3" t="n">
         <v>6.0077</v>
@@ -594,7 +594,7 @@
         <v>0.9407</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6844</v>
+        <v>1.6328</v>
       </c>
       <c r="E4" t="n">
         <v>5.2126</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8496</v>
+        <v>4.8213</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8752</v>
+        <v>0.8701</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5378</v>
+        <v>1.4769</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8496</v>
+        <v>4.8213</v>
       </c>
       <c r="F5" t="n">
-        <v>5.273</v>
+        <v>5.2447</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4234</v>
       </c>
       <c r="H5" t="n">
-        <v>5.965</v>
+        <v>5.9206</v>
       </c>
       <c r="I5" t="n">
         <v>6.0206</v>
@@ -686,7 +686,7 @@
         <v>0.8651</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5151</v>
+        <v>1.4658</v>
       </c>
       <c r="E6" t="n">
         <v>4.7934</v>
@@ -732,7 +732,7 @@
         <v>0.8353</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4485</v>
+        <v>1.4002</v>
       </c>
       <c r="E7" t="n">
         <v>4.6287</v>
@@ -778,7 +778,7 @@
         <v>0.7345</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2228</v>
+        <v>1.1775</v>
       </c>
       <c r="E8" t="n">
         <v>4.0699</v>
@@ -824,7 +824,7 @@
         <v>0.6293</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9454</v>
       </c>
       <c r="E9" t="n">
         <v>3.4872</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1793</v>
+        <v>3.1591</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5738</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.863</v>
+        <v>0.8147</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1793</v>
+        <v>3.1591</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1793</v>
+        <v>4.1591</v>
       </c>
       <c r="G10" t="n">
         <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2501</v>
+        <v>4.2185</v>
       </c>
       <c r="I10" t="n">
         <v>4.2898</v>
@@ -916,7 +916,7 @@
         <v>0.4912</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6782</v>
+        <v>0.6405</v>
       </c>
       <c r="E11" t="n">
         <v>2.7218</v>
@@ -962,7 +962,7 @@
         <v>0.4719</v>
       </c>
       <c r="D12" t="n">
-        <v>0.635</v>
+        <v>0.5978</v>
       </c>
       <c r="E12" t="n">
         <v>2.6148</v>
@@ -1008,7 +1008,7 @@
         <v>0.4638</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6168</v>
+        <v>0.5799</v>
       </c>
       <c r="E13" t="n">
         <v>2.5699</v>
@@ -1054,7 +1054,7 @@
         <v>0.4308</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5429</v>
+        <v>0.5071</v>
       </c>
       <c r="E14" t="n">
         <v>2.387</v>
@@ -1100,7 +1100,7 @@
         <v>0.4119</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5008</v>
+        <v>0.4655</v>
       </c>
       <c r="E15" t="n">
         <v>2.2826</v>
@@ -1146,7 +1146,7 @@
         <v>0.332</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3218</v>
+        <v>0.289</v>
       </c>
       <c r="E16" t="n">
         <v>1.8396</v>
@@ -1192,7 +1192,7 @@
         <v>0.2302</v>
       </c>
       <c r="D17" t="n">
-        <v>0.094</v>
+        <v>0.0643</v>
       </c>
       <c r="E17" t="n">
         <v>1.2756</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2551</v>
+        <v>1.2412</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2265</v>
+        <v>0.224</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0857</v>
+        <v>0.0506</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2551</v>
+        <v>1.2412</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8737</v>
+        <v>1.8598</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6186</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8737</v>
+        <v>1.8598</v>
       </c>
       <c r="I18" t="n">
         <v>1.8912</v>
@@ -1284,7 +1284,7 @@
         <v>0.2224</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0765</v>
+        <v>0.047</v>
       </c>
       <c r="E19" t="n">
         <v>1.2323</v>
@@ -1330,7 +1330,7 @@
         <v>0.2158</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0618</v>
+        <v>0.0326</v>
       </c>
       <c r="E20" t="n">
         <v>1.196</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9528</v>
+        <v>0.9429</v>
       </c>
       <c r="C21" t="n">
-        <v>0.172</v>
+        <v>0.1702</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0365</v>
+        <v>-0.0683</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9528</v>
+        <v>0.9429</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3237</v>
+        <v>1.3138</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3709</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3237</v>
+        <v>1.3138</v>
       </c>
       <c r="I21" t="n">
         <v>1.336</v>
@@ -1422,7 +1422,7 @@
         <v>0.1662</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0493</v>
+        <v>-0.077</v>
       </c>
       <c r="E22" t="n">
         <v>0.9209000000000001</v>
@@ -1468,7 +1468,7 @@
         <v>0.1619</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.059</v>
+        <v>-0.0866</v>
       </c>
       <c r="E23" t="n">
         <v>0.8969</v>
@@ -1514,7 +1514,7 @@
         <v>0.1551</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0741</v>
+        <v>-0.1014</v>
       </c>
       <c r="E24" t="n">
         <v>0.8596</v>
@@ -1560,7 +1560,7 @@
         <v>0.1488</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0882</v>
+        <v>-0.1153</v>
       </c>
       <c r="E25" t="n">
         <v>0.8247</v>
@@ -1606,7 +1606,7 @@
         <v>0.1322</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1254</v>
+        <v>-0.152</v>
       </c>
       <c r="E26" t="n">
         <v>0.7326</v>
@@ -1652,7 +1652,7 @@
         <v>0.113</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1684</v>
+        <v>-0.1945</v>
       </c>
       <c r="E27" t="n">
         <v>0.6261</v>
@@ -1698,7 +1698,7 @@
         <v>0.0871</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2263</v>
+        <v>-0.2516</v>
       </c>
       <c r="E28" t="n">
         <v>0.4828</v>
@@ -1744,7 +1744,7 @@
         <v>0.0341</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3451</v>
+        <v>-0.3687</v>
       </c>
       <c r="E29" t="n">
         <v>0.1889</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0273</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4826</v>
+        <v>-0.5043</v>
       </c>
       <c r="E30" t="n">
         <v>-0.1515</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0585</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5523</v>
+        <v>-0.573</v>
       </c>
       <c r="E31" t="n">
         <v>-0.324</v>
@@ -1882,7 +1882,7 @@
         <v>-0.07820000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.6165</v>
       </c>
       <c r="E32" t="n">
         <v>-0.4331</v>
@@ -1928,7 +1928,7 @@
         <v>-0.0968</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6381</v>
+        <v>-0.6577</v>
       </c>
       <c r="E33" t="n">
         <v>-0.5365</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1262</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7039</v>
+        <v>-0.7226</v>
       </c>
       <c r="E34" t="n">
         <v>-0.6995</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1276</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.707</v>
+        <v>-0.7256</v>
       </c>
       <c r="E35" t="n">
         <v>-0.707</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1519</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7613</v>
+        <v>-0.7792</v>
       </c>
       <c r="E36" t="n">
         <v>-0.8415</v>
@@ -2112,7 +2112,7 @@
         <v>-0.175</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8131</v>
+        <v>-0.8302</v>
       </c>
       <c r="E37" t="n">
         <v>-0.9696</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3602</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2276</v>
+        <v>-1.239</v>
       </c>
       <c r="E38" t="n">
         <v>-1.9957</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3779</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2673</v>
+        <v>-1.2782</v>
       </c>
       <c r="E39" t="n">
         <v>-2.0941</v>
@@ -2250,7 +2250,7 @@
         <v>-0.4786</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4928</v>
+        <v>-1.5005</v>
       </c>
       <c r="E40" t="n">
         <v>-2.6521</v>
@@ -2296,7 +2296,7 @@
         <v>-0.5489000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.65</v>
+        <v>-1.6556</v>
       </c>
       <c r="E41" t="n">
         <v>-3.0413</v>

--- a/database/event/5286/event_5286_evp_summary.xlsx
+++ b/database/event/5286/event_5286_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1492</v>
+        <v>5.7286</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1098</v>
+        <v>1.0338</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0059</v>
+        <v>1.9482</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1492</v>
+        <v>5.7286</v>
       </c>
       <c r="F2" t="n">
-        <v>5.9774</v>
+        <v>3.7674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1718</v>
+        <v>1.9612</v>
       </c>
       <c r="H2" t="n">
-        <v>7.0695</v>
+        <v>4.9128</v>
       </c>
       <c r="I2" t="n">
-        <v>7.189</v>
+        <v>4.9128</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1718</v>
+        <v>1.9612</v>
       </c>
       <c r="K2" t="n">
-        <v>384</v>
+        <v>316</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3608</v>
+        <v>6.874</v>
       </c>
       <c r="N2" t="n">
-        <v>413</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0077</v>
+        <v>5.4645</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0842</v>
+        <v>0.9862</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9496</v>
+        <v>1.8289</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0077</v>
+        <v>5.4645</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8929</v>
+        <v>5.1646</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1148</v>
+        <v>0.2999</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8929</v>
+        <v>7.9806</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8929</v>
+        <v>8.650499999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1148</v>
+        <v>0.2999</v>
       </c>
       <c r="K3" t="n">
-        <v>316</v>
+        <v>384</v>
       </c>
       <c r="L3" t="n">
         <v>29</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0077</v>
+        <v>8.950399999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>345</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4">
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2126</v>
+        <v>4.7185</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9407</v>
+        <v>0.8516</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6328</v>
+        <v>1.4922</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2126</v>
+        <v>4.7185</v>
       </c>
       <c r="F4" t="n">
-        <v>5.2126</v>
+        <v>4.7185</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.8704</v>
+        <v>7.0011</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8704</v>
+        <v>7.0011</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8704</v>
+        <v>7.0011</v>
       </c>
       <c r="N4" t="n">
         <v>296</v>
@@ -630,127 +630,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8213</v>
+        <v>4.6306</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8701</v>
+        <v>0.8357</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4769</v>
+        <v>1.4525</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8213</v>
+        <v>4.6306</v>
       </c>
       <c r="F5" t="n">
-        <v>5.2447</v>
+        <v>3.4438</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4234</v>
+        <v>1.1868</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9206</v>
+        <v>4.2021</v>
       </c>
       <c r="I5" t="n">
-        <v>6.0206</v>
+        <v>4.2021</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4234</v>
+        <v>1.1868</v>
       </c>
       <c r="K5" t="n">
-        <v>384</v>
+        <v>316</v>
       </c>
       <c r="L5" t="n">
         <v>29</v>
       </c>
       <c r="M5" t="n">
-        <v>5.5972</v>
+        <v>5.3889</v>
       </c>
       <c r="N5" t="n">
-        <v>413</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7934</v>
+        <v>4.5646</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8651</v>
+        <v>0.8238</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4658</v>
+        <v>1.4227</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7934</v>
+        <v>4.5646</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7934</v>
+        <v>4.7704</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0.2058</v>
       </c>
       <c r="H6" t="n">
-        <v>5.213</v>
+        <v>7.115</v>
       </c>
       <c r="I6" t="n">
-        <v>5.213</v>
+        <v>7.7123</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0.2058</v>
       </c>
       <c r="K6" t="n">
-        <v>318</v>
+        <v>384</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M6" t="n">
-        <v>5.213</v>
+        <v>7.5065</v>
       </c>
       <c r="N6" t="n">
-        <v>318</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6287</v>
+        <v>4.5074</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8353</v>
+        <v>0.8135</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4002</v>
+        <v>1.3969</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6287</v>
+        <v>4.5074</v>
       </c>
       <c r="F7" t="n">
-        <v>3.542</v>
+        <v>2.7401</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0867</v>
+        <v>1.7673</v>
       </c>
       <c r="H7" t="n">
-        <v>3.542</v>
+        <v>2.7401</v>
       </c>
       <c r="I7" t="n">
-        <v>3.542</v>
+        <v>2.7401</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0867</v>
+        <v>1.7673</v>
       </c>
       <c r="K7" t="n">
         <v>316</v>
@@ -759,7 +759,7 @@
         <v>29</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6287</v>
+        <v>4.507400000000001</v>
       </c>
       <c r="N7" t="n">
         <v>345</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0699</v>
+        <v>4.453</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7345</v>
+        <v>0.8036</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1775</v>
+        <v>1.3723</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0699</v>
+        <v>4.453</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3933</v>
+        <v>4.453</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6766</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3933</v>
+        <v>6.4182</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3933</v>
+        <v>6.4182</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6766</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L8" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.069900000000001</v>
+        <v>6.4182</v>
       </c>
       <c r="N8" t="n">
-        <v>345</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4872</v>
+        <v>3.4989</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6293</v>
+        <v>0.6315</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9454</v>
+        <v>0.9416</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4872</v>
+        <v>3.4989</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4872</v>
+        <v>3.4989</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4872</v>
+        <v>4.3231</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4872</v>
+        <v>4.3231</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4872</v>
+        <v>4.3231</v>
       </c>
       <c r="N9" t="n">
         <v>318</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1591</v>
+        <v>3.2563</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.5877</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8147</v>
+        <v>0.832</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1591</v>
+        <v>3.2563</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1591</v>
+        <v>3.2563</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2185</v>
+        <v>3.7905</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2898</v>
+        <v>3.7905</v>
       </c>
       <c r="J10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>384</v>
+        <v>318</v>
       </c>
       <c r="L10" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2898</v>
+        <v>3.7905</v>
       </c>
       <c r="N10" t="n">
-        <v>413</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7218</v>
+        <v>3.1172</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4912</v>
+        <v>0.5626</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6405</v>
+        <v>0.7692</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7218</v>
+        <v>3.1172</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7218</v>
+        <v>3.1172</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7218</v>
+        <v>3.4851</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7218</v>
+        <v>3.4851</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7218</v>
+        <v>3.4851</v>
       </c>
       <c r="N11" t="n">
         <v>216</v>
@@ -952,78 +952,78 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6148</v>
+        <v>2.9639</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4719</v>
+        <v>0.5349</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5978</v>
+        <v>0.7</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6148</v>
+        <v>2.9639</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6148</v>
+        <v>3.6238</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.6599</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6148</v>
+        <v>4.5974</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6148</v>
+        <v>4.9833</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.6599</v>
       </c>
       <c r="K12" t="n">
-        <v>237</v>
+        <v>384</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6148</v>
+        <v>4.323399999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>237</v>
+        <v>413</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5699</v>
+        <v>2.8258</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4638</v>
+        <v>0.51</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5799</v>
+        <v>0.6377</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5699</v>
+        <v>2.8258</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5699</v>
+        <v>2.8258</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5699</v>
+        <v>2.8453</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5699</v>
+        <v>2.8453</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5699</v>
+        <v>2.8453</v>
       </c>
       <c r="N13" t="n">
         <v>318</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.387</v>
+        <v>2.8215</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4308</v>
+        <v>0.5092</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5071</v>
+        <v>0.6358</v>
       </c>
       <c r="E14" t="n">
-        <v>2.387</v>
+        <v>2.8215</v>
       </c>
       <c r="F14" t="n">
-        <v>2.387</v>
+        <v>2.8215</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.387</v>
+        <v>2.8357</v>
       </c>
       <c r="I14" t="n">
-        <v>2.387</v>
+        <v>2.8357</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.387</v>
+        <v>2.8357</v>
       </c>
       <c r="N14" t="n">
-        <v>216</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Xeppaa</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2826</v>
+        <v>2.8133</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4119</v>
+        <v>0.5077</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4655</v>
+        <v>0.6321</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2826</v>
+        <v>2.8133</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2826</v>
+        <v>2.8133</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2826</v>
+        <v>2.8178</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2826</v>
+        <v>2.8178</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2826</v>
+        <v>2.8178</v>
       </c>
       <c r="N15" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>Xeppaa</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8396</v>
+        <v>2.6771</v>
       </c>
       <c r="C16" t="n">
-        <v>0.332</v>
+        <v>0.4831</v>
       </c>
       <c r="D16" t="n">
-        <v>0.289</v>
+        <v>0.5706</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8396</v>
+        <v>2.6771</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8396</v>
+        <v>2.6771</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8396</v>
+        <v>2.6771</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8396</v>
+        <v>2.6771</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>318</v>
+        <v>217</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8396</v>
+        <v>2.6771</v>
       </c>
       <c r="N16" t="n">
-        <v>318</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2756</v>
+        <v>2.3493</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2302</v>
+        <v>0.424</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0643</v>
+        <v>0.4226</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2756</v>
+        <v>2.3493</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2756</v>
+        <v>2.3493</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2756</v>
+        <v>2.3493</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2756</v>
+        <v>2.3493</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2756</v>
+        <v>2.3493</v>
       </c>
       <c r="N17" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2412</v>
+        <v>2.0725</v>
       </c>
       <c r="C18" t="n">
-        <v>0.224</v>
+        <v>0.374</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0506</v>
+        <v>0.2976</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2412</v>
+        <v>2.0725</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8598</v>
+        <v>2.4931</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6186</v>
+        <v>-0.4206</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8598</v>
+        <v>2.4931</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8912</v>
+        <v>2.7024</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6186</v>
+        <v>-0.4206</v>
       </c>
       <c r="K18" t="n">
         <v>384</v>
@@ -1265,7 +1265,7 @@
         <v>29</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2726</v>
+        <v>2.2818</v>
       </c>
       <c r="N18" t="n">
         <v>413</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2323</v>
+        <v>2.0025</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2224</v>
+        <v>0.3614</v>
       </c>
       <c r="D19" t="n">
-        <v>0.047</v>
+        <v>0.266</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2323</v>
+        <v>2.0025</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2323</v>
+        <v>2.0025</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2323</v>
+        <v>2.0025</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2323</v>
+        <v>2.0025</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2323</v>
+        <v>2.0025</v>
       </c>
       <c r="N19" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.196</v>
+        <v>1.7858</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2158</v>
+        <v>0.3223</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0326</v>
+        <v>0.1682</v>
       </c>
       <c r="E20" t="n">
-        <v>1.196</v>
+        <v>1.7858</v>
       </c>
       <c r="F20" t="n">
-        <v>1.196</v>
+        <v>1.7858</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.196</v>
+        <v>1.7858</v>
       </c>
       <c r="I20" t="n">
-        <v>1.196</v>
+        <v>1.7858</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.196</v>
+        <v>1.7858</v>
       </c>
       <c r="N20" t="n">
         <v>237</v>
@@ -1366,369 +1366,369 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9429</v>
+        <v>1.6804</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1702</v>
+        <v>0.3033</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0683</v>
+        <v>0.1206</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9429</v>
+        <v>1.6804</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3138</v>
+        <v>1.6804</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3138</v>
+        <v>1.6804</v>
       </c>
       <c r="I21" t="n">
-        <v>1.336</v>
+        <v>1.6804</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>384</v>
+        <v>237</v>
       </c>
       <c r="L21" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9651000000000001</v>
+        <v>1.6804</v>
       </c>
       <c r="N21" t="n">
-        <v>413</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9209000000000001</v>
+        <v>1.6667</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1662</v>
+        <v>0.3008</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.077</v>
+        <v>0.1144</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9209000000000001</v>
+        <v>1.6667</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9209000000000001</v>
+        <v>1.8584</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.1917</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9209000000000001</v>
+        <v>1.8584</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9209000000000001</v>
+        <v>1.8584</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.1917</v>
       </c>
       <c r="K22" t="n">
-        <v>236</v>
+        <v>316</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9209000000000001</v>
+        <v>1.6667</v>
       </c>
       <c r="N22" t="n">
-        <v>236</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8969</v>
+        <v>1.5796</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1619</v>
+        <v>0.2851</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0866</v>
+        <v>0.0751</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8969</v>
+        <v>1.5796</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8969</v>
+        <v>0.0108</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1.5688</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8969</v>
+        <v>0.0108</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8969</v>
+        <v>0.0108</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1.5688</v>
       </c>
       <c r="K23" t="n">
-        <v>236</v>
+        <v>316</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8969</v>
+        <v>1.5796</v>
       </c>
       <c r="N23" t="n">
-        <v>236</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8596</v>
+        <v>1.4122</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1551</v>
+        <v>0.2549</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1014</v>
+        <v>-0.0005</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8596</v>
+        <v>1.4122</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7934</v>
+        <v>1.4122</v>
       </c>
       <c r="G24" t="n">
-        <v>1.653</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7934</v>
+        <v>1.4122</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7934</v>
+        <v>1.4122</v>
       </c>
       <c r="J24" t="n">
-        <v>1.653</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="L24" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8596</v>
+        <v>1.4122</v>
       </c>
       <c r="N24" t="n">
-        <v>345</v>
+        <v>296</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8247</v>
+        <v>1.3978</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1488</v>
+        <v>0.2523</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1153</v>
+        <v>-0.007</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8247</v>
+        <v>1.3978</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1771</v>
+        <v>1.3978</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3524</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1771</v>
+        <v>1.3978</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1771</v>
+        <v>1.3978</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3524</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="L25" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8247</v>
+        <v>1.3978</v>
       </c>
       <c r="N25" t="n">
-        <v>345</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7326</v>
+        <v>1.3137</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1322</v>
+        <v>0.2371</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.152</v>
+        <v>-0.0449</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7326</v>
+        <v>1.3137</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7326</v>
+        <v>1.3137</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7326</v>
+        <v>1.3137</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7326</v>
+        <v>1.3137</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7326</v>
+        <v>1.3137</v>
       </c>
       <c r="N26" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6261</v>
+        <v>1.2064</v>
       </c>
       <c r="C27" t="n">
-        <v>0.113</v>
+        <v>0.2177</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1945</v>
+        <v>-0.0934</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6261</v>
+        <v>1.2064</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6261</v>
+        <v>1.4834</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.277</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6261</v>
+        <v>1.4834</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6261</v>
+        <v>1.6079</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.277</v>
       </c>
       <c r="K27" t="n">
-        <v>296</v>
+        <v>384</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6261</v>
+        <v>1.3309</v>
       </c>
       <c r="N27" t="n">
-        <v>296</v>
+        <v>413</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4828</v>
+        <v>1.0321</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0871</v>
+        <v>0.1863</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2516</v>
+        <v>-0.1721</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4828</v>
+        <v>1.0321</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4828</v>
+        <v>1.0321</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4828</v>
+        <v>1.0321</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4828</v>
+        <v>1.0321</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4828</v>
+        <v>1.0321</v>
       </c>
       <c r="N28" t="n">
-        <v>296</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1889</v>
+        <v>0.9889</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0341</v>
+        <v>0.1785</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3687</v>
+        <v>-0.1916</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1889</v>
+        <v>0.9889</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1889</v>
+        <v>0.9889</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1889</v>
+        <v>0.9889</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1889</v>
+        <v>0.9889</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1889</v>
+        <v>0.9889</v>
       </c>
       <c r="N29" t="n">
         <v>318</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1515</v>
+        <v>0.4853</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0273</v>
+        <v>0.0876</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5043</v>
+        <v>-0.4189</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1515</v>
+        <v>0.4853</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1515</v>
+        <v>0.4853</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1515</v>
+        <v>0.4853</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1515</v>
+        <v>0.4853</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1515</v>
+        <v>0.4853</v>
       </c>
       <c r="N30" t="n">
         <v>237</v>
@@ -1826,78 +1826,78 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>vanity</t>
+          <t>motm</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.324</v>
+        <v>0.1399</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0585</v>
+        <v>0.0252</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.573</v>
+        <v>-0.5749</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.324</v>
+        <v>0.1399</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.324</v>
+        <v>0.1399</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.324</v>
+        <v>0.1399</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.324</v>
+        <v>0.1399</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>217</v>
+        <v>296</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.324</v>
+        <v>0.1399</v>
       </c>
       <c r="N31" t="n">
-        <v>217</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jonji</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4331</v>
+        <v>0.0849</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.0153</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6165</v>
+        <v>-0.5997</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4331</v>
+        <v>0.0849</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4331</v>
+        <v>0.0849</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4331</v>
+        <v>0.0849</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4331</v>
+        <v>0.0849</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4331</v>
+        <v>0.0849</v>
       </c>
       <c r="N32" t="n">
         <v>217</v>
@@ -1918,170 +1918,170 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>motm</t>
+          <t>Jonji</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5365</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0968</v>
+        <v>0.0148</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6577</v>
+        <v>-0.601</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5365</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5365</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5365</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5365</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>296</v>
+        <v>217</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5365</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>296</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>vanity</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6995</v>
+        <v>-0.0368</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1262</v>
+        <v>-0.0066</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7226</v>
+        <v>-0.6546</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6995</v>
+        <v>-0.0368</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6995</v>
+        <v>-0.0368</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6995</v>
+        <v>-0.0368</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6995</v>
+        <v>-0.0368</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6995</v>
+        <v>-0.0368</v>
       </c>
       <c r="N34" t="n">
-        <v>236</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>s0m</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.707</v>
+        <v>-0.0835</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1276</v>
+        <v>-0.0151</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7256</v>
+        <v>-0.6757</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.707</v>
+        <v>-0.0835</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.707</v>
+        <v>-0.0835</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.707</v>
+        <v>-0.0835</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.707</v>
+        <v>-0.0835</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.707</v>
+        <v>-0.0835</v>
       </c>
       <c r="N35" t="n">
-        <v>217</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>s0m</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8415</v>
+        <v>-0.1469</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1519</v>
+        <v>-0.0265</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7792</v>
+        <v>-0.7043</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8415</v>
+        <v>-0.1469</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8415</v>
+        <v>-0.1469</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8415</v>
+        <v>-0.1469</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8415</v>
+        <v>-0.1469</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8415</v>
+        <v>-0.1469</v>
       </c>
       <c r="N36" t="n">
         <v>236</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9696</v>
+        <v>-0.2131</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.175</v>
+        <v>-0.0385</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8302</v>
+        <v>-0.7342</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9696</v>
+        <v>-0.2131</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9696</v>
+        <v>-0.2131</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9696</v>
+        <v>-0.2131</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9696</v>
+        <v>-0.2131</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9696</v>
+        <v>-0.2131</v>
       </c>
       <c r="N37" t="n">
         <v>296</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.9957</v>
+        <v>-0.864</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3602</v>
+        <v>-0.1559</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.239</v>
+        <v>-1.0281</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.9957</v>
+        <v>-0.864</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.9957</v>
+        <v>-0.864</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.9957</v>
+        <v>-0.864</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.9957</v>
+        <v>-0.864</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.9957</v>
+        <v>-0.864</v>
       </c>
       <c r="N38" t="n">
         <v>236</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.0941</v>
+        <v>-0.9559</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3779</v>
+        <v>-0.1725</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2782</v>
+        <v>-1.0696</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.0941</v>
+        <v>-0.9559</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.0941</v>
+        <v>-0.9559</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.0941</v>
+        <v>-0.9559</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.0941</v>
+        <v>-0.9559</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.0941</v>
+        <v>-0.9559</v>
       </c>
       <c r="N39" t="n">
         <v>216</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.6521</v>
+        <v>-1.7135</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4786</v>
+        <v>-0.3092</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5005</v>
+        <v>-1.4116</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.6521</v>
+        <v>-1.7135</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.6521</v>
+        <v>-1.7135</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.6521</v>
+        <v>-1.7135</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.6521</v>
+        <v>-1.7135</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.6521</v>
+        <v>-1.7135</v>
       </c>
       <c r="N40" t="n">
         <v>216</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0413</v>
+        <v>-2.4364</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.4397</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6556</v>
+        <v>-1.7379</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0413</v>
+        <v>-2.4364</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.0413</v>
+        <v>-2.4364</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.0413</v>
+        <v>-2.4364</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.0413</v>
+        <v>-2.4364</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.0413</v>
+        <v>-2.4364</v>
       </c>
       <c r="N41" t="n">
         <v>217</v>
@@ -2429,10 +2429,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9089</v>
+        <v>0.9002</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9089</v>
+        <v>0.9002</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6743</v>
+        <v>0.6653</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6743</v>
+        <v>0.6653</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.21</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5975</v>
+        <v>0.5928</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5975</v>
+        <v>0.5928</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2313</v>
+        <v>0.2847</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2313</v>
+        <v>0.2847</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.89</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4894</v>
+        <v>-0.4205</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4894</v>
+        <v>-0.4205</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.08</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2294</v>
+        <v>0.2321</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2294</v>
+        <v>0.2321</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.98</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0102</v>
+        <v>-0.0269</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0102</v>
+        <v>-0.0269</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1598</v>
+        <v>-0.1141</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1598</v>
+        <v>-0.1141</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2254</v>
+        <v>-0.1458</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2254</v>
+        <v>-0.1458</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.68</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5275</v>
+        <v>-0.3439</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5275</v>
+        <v>-0.3439</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.66</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4405</v>
+        <v>1.2959</v>
       </c>
       <c r="J12" t="n">
-        <v>40.334</v>
+        <v>36.2852</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.65</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4217</v>
+        <v>1.2841</v>
       </c>
       <c r="J13" t="n">
-        <v>39.8076</v>
+        <v>35.9548</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.35</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7677</v>
+        <v>0.8671</v>
       </c>
       <c r="J14" t="n">
-        <v>21.4956</v>
+        <v>24.2788</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4892</v>
+        <v>0.594</v>
       </c>
       <c r="J15" t="n">
-        <v>13.6976</v>
+        <v>16.632</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.137</v>
+        <v>0.2288</v>
       </c>
       <c r="J16" t="n">
-        <v>3.836</v>
+        <v>6.4064</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3972</v>
+        <v>0.4457</v>
       </c>
       <c r="J17" t="n">
-        <v>11.1216</v>
+        <v>12.4796</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.76</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3607</v>
+        <v>-0.2501</v>
       </c>
       <c r="J18" t="n">
-        <v>-10.0996</v>
+        <v>-7.0028</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.7</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4588</v>
+        <v>-0.3065</v>
       </c>
       <c r="J19" t="n">
-        <v>-12.8464</v>
+        <v>-8.582000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4737</v>
+        <v>-0.316</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.2636</v>
+        <v>-8.848000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6528</v>
+        <v>-0.4379</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.2784</v>
+        <v>-12.2612</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.38</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6115</v>
+        <v>0.7418</v>
       </c>
       <c r="J22" t="n">
-        <v>22.014</v>
+        <v>26.7048</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.016</v>
+        <v>0.0343</v>
       </c>
       <c r="J23" t="n">
-        <v>0.576</v>
+        <v>1.2348</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.95</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1465</v>
+        <v>-0.0789</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.274</v>
+        <v>-2.8404</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.93</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1844</v>
+        <v>-0.1032</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.6384</v>
+        <v>-3.7152</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2697</v>
+        <v>-0.1595</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.709199999999999</v>
+        <v>-5.742</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8647</v>
+        <v>1.5774</v>
       </c>
       <c r="J27" t="n">
-        <v>67.1292</v>
+        <v>56.7864</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.97</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2228</v>
+        <v>-0.157</v>
       </c>
       <c r="J28" t="n">
-        <v>-8.020799999999999</v>
+        <v>-5.652</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.95</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2922</v>
+        <v>-0.2253</v>
       </c>
       <c r="J29" t="n">
-        <v>-10.5192</v>
+        <v>-8.110799999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4153</v>
+        <v>-0.3491</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.9508</v>
+        <v>-12.5676</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5264</v>
+        <v>-0.4634</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.9504</v>
+        <v>-16.6824</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.21</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4862</v>
+        <v>0.5697</v>
       </c>
       <c r="J32" t="n">
-        <v>10.2102</v>
+        <v>11.9637</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.75</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3774</v>
+        <v>-0.2592</v>
       </c>
       <c r="J33" t="n">
-        <v>-7.9254</v>
+        <v>-5.4432</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.74</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3945</v>
+        <v>-0.2686</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.2845</v>
+        <v>-5.6406</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.64</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.3628</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.4429</v>
+        <v>-7.6188</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.51</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7161</v>
+        <v>-0.4841</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.0381</v>
+        <v>-10.1661</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.62</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3693</v>
+        <v>1.2504</v>
       </c>
       <c r="J37" t="n">
-        <v>28.7553</v>
+        <v>26.2584</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.57</v>
       </c>
       <c r="I38" t="n">
-        <v>1.2725</v>
+        <v>1.1906</v>
       </c>
       <c r="J38" t="n">
-        <v>26.7225</v>
+        <v>25.0026</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.34</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7499</v>
+        <v>0.8472</v>
       </c>
       <c r="J39" t="n">
-        <v>15.7479</v>
+        <v>17.7912</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.28</v>
       </c>
       <c r="I40" t="n">
-        <v>0.61</v>
+        <v>0.7133</v>
       </c>
       <c r="J40" t="n">
-        <v>12.81</v>
+        <v>14.9793</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.12</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2209</v>
+        <v>0.3155</v>
       </c>
       <c r="J41" t="n">
-        <v>4.6389</v>
+        <v>6.6255</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.97</v>
       </c>
       <c r="I42" t="n">
-        <v>1.9583</v>
+        <v>1.6565</v>
       </c>
       <c r="J42" t="n">
-        <v>39.166</v>
+        <v>33.13</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.71</v>
       </c>
       <c r="I43" t="n">
-        <v>1.5355</v>
+        <v>1.3561</v>
       </c>
       <c r="J43" t="n">
-        <v>30.71</v>
+        <v>27.122</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6545</v>
+        <v>0.7579</v>
       </c>
       <c r="J44" t="n">
-        <v>13.09</v>
+        <v>15.158</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.02</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.08110000000000001</v>
+        <v>0.0031</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.622</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.95</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3793</v>
+        <v>-0.2941</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.586</v>
+        <v>-5.882</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.95</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0098</v>
+        <v>-0.0402</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.196</v>
+        <v>-0.804</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.75</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.3685</v>
+        <v>-0.258</v>
       </c>
       <c r="J48" t="n">
-        <v>-7.37</v>
+        <v>-5.16</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.71</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4369</v>
+        <v>-0.2952</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.738</v>
+        <v>-5.904</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4526</v>
+        <v>-0.3046</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.052</v>
+        <v>-6.092</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4829</v>
+        <v>-0.3234</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.657999999999999</v>
+        <v>-6.468</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2526</v>
+        <v>1.1548</v>
       </c>
       <c r="J52" t="n">
-        <v>35.0728</v>
+        <v>32.3344</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3503</v>
+        <v>0.3298</v>
       </c>
       <c r="J53" t="n">
-        <v>9.808400000000001</v>
+        <v>9.234400000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.03</v>
       </c>
       <c r="I54" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1179</v>
       </c>
       <c r="J54" t="n">
-        <v>2.436</v>
+        <v>3.3012</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4277</v>
+        <v>-0.3672</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.9756</v>
+        <v>-10.2816</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6664</v>
+        <v>-0.6138</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.6592</v>
+        <v>-17.1864</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.62</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8793</v>
+        <v>1.0691</v>
       </c>
       <c r="J57" t="n">
-        <v>24.6204</v>
+        <v>29.9348</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.29</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4886</v>
+        <v>0.5803</v>
       </c>
       <c r="J58" t="n">
-        <v>13.6808</v>
+        <v>16.2484</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.84</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3377</v>
+        <v>-0.2047</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.4556</v>
+        <v>-5.7316</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3956</v>
+        <v>-0.2453</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.0768</v>
+        <v>-6.8684</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4908</v>
+        <v>-0.3138</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.7424</v>
+        <v>-8.7864</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.3</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5749</v>
+        <v>0.6901</v>
       </c>
       <c r="J62" t="n">
-        <v>15.5223</v>
+        <v>18.6327</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.92</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1082</v>
+        <v>-0.0963</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.9214</v>
+        <v>-2.6001</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.76</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3989</v>
+        <v>-0.2598</v>
       </c>
       <c r="J64" t="n">
-        <v>-10.7703</v>
+        <v>-7.0146</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.66</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5407</v>
+        <v>-0.3555</v>
       </c>
       <c r="J65" t="n">
-        <v>-14.5989</v>
+        <v>-9.5985</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.61</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6066</v>
+        <v>-0.4023</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.3782</v>
+        <v>-10.8621</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3733</v>
+        <v>1.2421</v>
       </c>
       <c r="J67" t="n">
-        <v>37.0791</v>
+        <v>33.5367</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.24</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5894</v>
+        <v>0.646</v>
       </c>
       <c r="J68" t="n">
-        <v>15.9138</v>
+        <v>17.442</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.23</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5615</v>
+        <v>0.623</v>
       </c>
       <c r="J69" t="n">
-        <v>15.1605</v>
+        <v>16.821</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.2</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4815</v>
+        <v>0.5515</v>
       </c>
       <c r="J70" t="n">
-        <v>13.0005</v>
+        <v>14.8905</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1412</v>
+        <v>-0.0614</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.8124</v>
+        <v>-1.6578</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.17</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3459</v>
+        <v>0.3885</v>
       </c>
       <c r="J72" t="n">
-        <v>8.993399999999999</v>
+        <v>10.101</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.14</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>0.3309</v>
       </c>
       <c r="J73" t="n">
-        <v>7.8</v>
+        <v>8.603400000000001</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0824</v>
+        <v>-0.0485</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.1424</v>
+        <v>-1.261</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.82</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3499</v>
+        <v>-0.2167</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.0974</v>
+        <v>-5.6342</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3647</v>
+        <v>-0.2269</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.482200000000001</v>
+        <v>-5.8994</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.29</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8017</v>
+        <v>0.788</v>
       </c>
       <c r="J77" t="n">
-        <v>20.8442</v>
+        <v>20.488</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.28</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7782</v>
+        <v>0.7644</v>
       </c>
       <c r="J78" t="n">
-        <v>20.2332</v>
+        <v>19.8744</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1437</v>
+        <v>0.1983</v>
       </c>
       <c r="J79" t="n">
-        <v>3.7362</v>
+        <v>5.1558</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I80" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.1337</v>
       </c>
       <c r="J80" t="n">
-        <v>1.9838</v>
+        <v>3.4762</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.04</v>
       </c>
       <c r="I81" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.1337</v>
       </c>
       <c r="J81" t="n">
-        <v>1.9838</v>
+        <v>3.4762</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.69</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4747</v>
+        <v>1.3222</v>
       </c>
       <c r="J82" t="n">
-        <v>32.4434</v>
+        <v>29.0884</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.66</v>
       </c>
       <c r="I83" t="n">
-        <v>1.4187</v>
+        <v>1.2873</v>
       </c>
       <c r="J83" t="n">
-        <v>31.2114</v>
+        <v>28.3206</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.41</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8777</v>
+        <v>0.9785</v>
       </c>
       <c r="J84" t="n">
-        <v>19.3094</v>
+        <v>21.527</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.37</v>
       </c>
       <c r="I85" t="n">
-        <v>0.7871</v>
+        <v>0.9012</v>
       </c>
       <c r="J85" t="n">
-        <v>17.3162</v>
+        <v>19.8264</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.1</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1512</v>
+        <v>0.2469</v>
       </c>
       <c r="J86" t="n">
-        <v>3.3264</v>
+        <v>5.4318</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.09</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3408</v>
+        <v>0.3744</v>
       </c>
       <c r="J87" t="n">
-        <v>7.4976</v>
+        <v>8.236800000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.66</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.4776</v>
+        <v>-0.3315</v>
       </c>
       <c r="J88" t="n">
-        <v>-10.5072</v>
+        <v>-7.293</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.5101</v>
+        <v>-0.3498</v>
       </c>
       <c r="J89" t="n">
-        <v>-11.2222</v>
+        <v>-7.6956</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.55</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6411</v>
+        <v>-0.4336</v>
       </c>
       <c r="J90" t="n">
-        <v>-14.1042</v>
+        <v>-9.539199999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.49</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7212</v>
+        <v>-0.4898</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.8664</v>
+        <v>-10.7756</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.56</v>
       </c>
       <c r="I92" t="n">
-        <v>1.3493</v>
+        <v>1.2227</v>
       </c>
       <c r="J92" t="n">
-        <v>40.479</v>
+        <v>36.681</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.16</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4192</v>
+        <v>0.466</v>
       </c>
       <c r="J93" t="n">
-        <v>12.576</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2159</v>
+        <v>0.2782</v>
       </c>
       <c r="J94" t="n">
-        <v>6.477</v>
+        <v>8.346</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.07</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1551</v>
+        <v>0.2193</v>
       </c>
       <c r="J95" t="n">
-        <v>4.653</v>
+        <v>6.579</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.03</v>
       </c>
       <c r="I96" t="n">
-        <v>0.0223</v>
+        <v>0.089</v>
       </c>
       <c r="J96" t="n">
-        <v>0.669</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.46</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7235</v>
+        <v>0.8963</v>
       </c>
       <c r="J97" t="n">
-        <v>21.705</v>
+        <v>26.889</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.16</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3309</v>
+        <v>0.3695</v>
       </c>
       <c r="J98" t="n">
-        <v>9.927</v>
+        <v>11.085</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3196</v>
+        <v>-0.1962</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.587999999999999</v>
+        <v>-5.886</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.77</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4221</v>
+        <v>-0.2667</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.663</v>
+        <v>-8.000999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5429</v>
+        <v>-0.3531</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.287</v>
+        <v>-10.593</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.88</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0872</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.42</v>
+        <v>-1.744</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.67</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.405</v>
+        <v>-0.3144</v>
       </c>
       <c r="J103" t="n">
-        <v>-8.1</v>
+        <v>-6.288</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.66</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4216</v>
+        <v>-0.3239</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.432</v>
+        <v>-6.478</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.51</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.6748</v>
+        <v>-0.4605</v>
       </c>
       <c r="J105" t="n">
-        <v>-13.496</v>
+        <v>-9.210000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.41</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8086</v>
+        <v>-0.5551</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.172</v>
+        <v>-11.102</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7631</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="J107" t="n">
-        <v>15.262</v>
+        <v>14.082</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.6543</v>
       </c>
       <c r="J108" t="n">
-        <v>14.122</v>
+        <v>13.086</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.48</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.5646</v>
       </c>
       <c r="J109" t="n">
-        <v>11.824</v>
+        <v>11.292</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.46</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5595</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="J110" t="n">
-        <v>11.19</v>
+        <v>10.898</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.26</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3047</v>
+        <v>0.326</v>
       </c>
       <c r="J111" t="n">
-        <v>6.094</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.42</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0437</v>
+        <v>1.0299</v>
       </c>
       <c r="J112" t="n">
-        <v>28.1799</v>
+        <v>27.8073</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.41</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0225</v>
+        <v>1.0145</v>
       </c>
       <c r="J113" t="n">
-        <v>27.6075</v>
+        <v>27.3915</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.9135</v>
+        <v>0.9208</v>
       </c>
       <c r="J114" t="n">
-        <v>24.6645</v>
+        <v>24.8616</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.98</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2331</v>
+        <v>-0.1517</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.2937</v>
+        <v>-4.0959</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.97</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2703</v>
+        <v>-0.189</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.2981</v>
+        <v>-5.103</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.28</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5478</v>
+        <v>0.6519</v>
       </c>
       <c r="J117" t="n">
-        <v>14.7906</v>
+        <v>17.6013</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.85</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2466</v>
+        <v>-0.1716</v>
       </c>
       <c r="J118" t="n">
-        <v>-6.6582</v>
+        <v>-4.6332</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.74</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4294</v>
+        <v>-0.2794</v>
       </c>
       <c r="J119" t="n">
-        <v>-11.5938</v>
+        <v>-7.5438</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.72</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4583</v>
+        <v>-0.2987</v>
       </c>
       <c r="J120" t="n">
-        <v>-12.3741</v>
+        <v>-8.0649</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5278</v>
+        <v>-0.3463</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.2506</v>
+        <v>-9.350099999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>1.284</v>
+        <v>1.1761</v>
       </c>
       <c r="J122" t="n">
-        <v>38.52</v>
+        <v>35.283</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.28</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8134</v>
+        <v>0.7872</v>
       </c>
       <c r="J123" t="n">
-        <v>24.402</v>
+        <v>23.616</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.99</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.129</v>
+        <v>-0.0725</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.87</v>
+        <v>-2.175</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3759</v>
+        <v>-0.3126</v>
       </c>
       <c r="J125" t="n">
-        <v>-11.277</v>
+        <v>-9.378</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.71</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.9058</v>
+        <v>-0.8713</v>
       </c>
       <c r="J126" t="n">
-        <v>-27.174</v>
+        <v>-26.139</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.5</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7467</v>
+        <v>0.9278</v>
       </c>
       <c r="J127" t="n">
-        <v>22.401</v>
+        <v>27.834</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.99</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0646</v>
+        <v>-0.0251</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.938</v>
+        <v>-0.753</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.95</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1536</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.608</v>
+        <v>-2.436</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2087</v>
+        <v>-0.1173</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.261</v>
+        <v>-3.519</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2428</v>
+        <v>-0.14</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.284</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.11</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2394</v>
+        <v>0.2631</v>
       </c>
       <c r="J132" t="n">
-        <v>7.182</v>
+        <v>7.893</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.09</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2049</v>
+        <v>0.2226</v>
       </c>
       <c r="J133" t="n">
-        <v>6.147</v>
+        <v>6.678</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1684</v>
+        <v>0.1806</v>
       </c>
       <c r="J134" t="n">
-        <v>5.052</v>
+        <v>5.418</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1408</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.224</v>
+        <v>-2.319</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3127</v>
+        <v>-0.1896</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.381</v>
+        <v>-5.688</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.34</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9404</v>
+        <v>0.9225</v>
       </c>
       <c r="J137" t="n">
-        <v>28.212</v>
+        <v>27.675</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.53</v>
+        <v>0.5082</v>
       </c>
       <c r="J138" t="n">
-        <v>15.9</v>
+        <v>15.246</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3539</v>
+        <v>0.3505</v>
       </c>
       <c r="J139" t="n">
-        <v>10.617</v>
+        <v>10.515</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.97</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.219</v>
+        <v>-0.1549</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.57</v>
+        <v>-4.647</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.89</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4689</v>
+        <v>-0.4049</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.067</v>
+        <v>-12.147</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7854</v>
+        <v>0.9764</v>
       </c>
       <c r="J142" t="n">
-        <v>19.635</v>
+        <v>24.41</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.24</v>
       </c>
       <c r="I143" t="n">
-        <v>0.427</v>
+        <v>0.4989</v>
       </c>
       <c r="J143" t="n">
-        <v>10.675</v>
+        <v>12.4725</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.96</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1291</v>
+        <v>-0.067</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.2275</v>
+        <v>-1.675</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3777</v>
+        <v>-0.2333</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.442500000000001</v>
+        <v>-5.8325</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.65</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.59</v>
+        <v>-0.3872</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.75</v>
+        <v>-9.68</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.82</v>
       </c>
       <c r="I147" t="n">
-        <v>1.8215</v>
+        <v>1.5422</v>
       </c>
       <c r="J147" t="n">
-        <v>45.5375</v>
+        <v>38.555</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.07</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1504</v>
+        <v>0.2168</v>
       </c>
       <c r="J148" t="n">
-        <v>3.76</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.06</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1191</v>
+        <v>0.1861</v>
       </c>
       <c r="J149" t="n">
-        <v>2.9775</v>
+        <v>4.6525</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.06</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1191</v>
+        <v>0.1861</v>
       </c>
       <c r="J150" t="n">
-        <v>2.9775</v>
+        <v>4.6525</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.95</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3258</v>
+        <v>-0.2484</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.145</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.039</v>
+        <v>-0.0639</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.702</v>
+        <v>-1.1502</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1063</v>
+        <v>-0.1129</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.9134</v>
+        <v>-2.0322</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.55</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.6191</v>
+        <v>-0.4238</v>
       </c>
       <c r="J154" t="n">
-        <v>-11.1438</v>
+        <v>-7.6284</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.48</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.7175</v>
+        <v>-0.4895</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.915</v>
+        <v>-8.811</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.36</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8727</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.7086</v>
+        <v>-10.8594</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.19</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3087</v>
+        <v>1.1383</v>
       </c>
       <c r="J157" t="n">
-        <v>23.5566</v>
+        <v>20.4894</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.62</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7408</v>
+        <v>0.6959</v>
       </c>
       <c r="J158" t="n">
-        <v>13.3344</v>
+        <v>12.5262</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.6</v>
       </c>
       <c r="I159" t="n">
-        <v>0.717</v>
+        <v>0.6766</v>
       </c>
       <c r="J159" t="n">
-        <v>12.906</v>
+        <v>12.1788</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.29</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3291</v>
+        <v>0.353</v>
       </c>
       <c r="J160" t="n">
-        <v>5.9238</v>
+        <v>6.354</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.09</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0568</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="J161" t="n">
-        <v>1.0224</v>
+        <v>1.7748</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.92</v>
       </c>
       <c r="I162" t="n">
-        <v>1.8733</v>
+        <v>1.5835</v>
       </c>
       <c r="J162" t="n">
-        <v>41.2126</v>
+        <v>34.837</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.42</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.9939</v>
       </c>
       <c r="J163" t="n">
-        <v>19.6834</v>
+        <v>21.8658</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.35</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7382</v>
+        <v>0.8562</v>
       </c>
       <c r="J164" t="n">
-        <v>16.2404</v>
+        <v>18.8364</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.33</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6939</v>
+        <v>0.8122</v>
       </c>
       <c r="J165" t="n">
-        <v>15.2658</v>
+        <v>17.8684</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.26</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5374</v>
+        <v>0.6526</v>
       </c>
       <c r="J166" t="n">
-        <v>11.8228</v>
+        <v>14.3572</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.01</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1771</v>
+        <v>0.1562</v>
       </c>
       <c r="J167" t="n">
-        <v>3.8962</v>
+        <v>3.4364</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.78</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2683</v>
+        <v>-0.2196</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.9026</v>
+        <v>-4.8312</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.6</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.5738</v>
+        <v>-0.3882</v>
       </c>
       <c r="J169" t="n">
-        <v>-12.6236</v>
+        <v>-8.5404</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.54</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6573</v>
+        <v>-0.4443</v>
       </c>
       <c r="J170" t="n">
-        <v>-14.4606</v>
+        <v>-9.7746</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.54</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6573</v>
+        <v>-0.4443</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.4606</v>
+        <v>-9.7746</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9459</v>
+        <v>0.9266</v>
       </c>
       <c r="J172" t="n">
-        <v>34.0524</v>
+        <v>33.3576</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.1</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3307</v>
+        <v>0.3251</v>
       </c>
       <c r="J173" t="n">
-        <v>11.9052</v>
+        <v>11.7036</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.08</v>
       </c>
       <c r="I174" t="n">
-        <v>0.252</v>
+        <v>0.2699</v>
       </c>
       <c r="J174" t="n">
-        <v>9.071999999999999</v>
+        <v>9.7164</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0722</v>
+        <v>-0.0193</v>
       </c>
       <c r="J175" t="n">
-        <v>-2.5992</v>
+        <v>-0.6948</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.91</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.408</v>
+        <v>-0.3441</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.688</v>
+        <v>-12.3876</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.1</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2135</v>
+        <v>0.2382</v>
       </c>
       <c r="J177" t="n">
-        <v>7.686</v>
+        <v>8.575200000000001</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1584</v>
+        <v>0.1765</v>
       </c>
       <c r="J178" t="n">
-        <v>5.7024</v>
+        <v>6.354</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.03</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0653</v>
+        <v>0.0872</v>
       </c>
       <c r="J179" t="n">
-        <v>2.3508</v>
+        <v>3.1392</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0398</v>
+        <v>0.0618</v>
       </c>
       <c r="J180" t="n">
-        <v>1.4328</v>
+        <v>2.2248</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1284</v>
+        <v>-0.0668</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.6224</v>
+        <v>-2.4048</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.36</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9457</v>
+        <v>0.9392</v>
       </c>
       <c r="J182" t="n">
-        <v>33.0995</v>
+        <v>32.872</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.35</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9236</v>
+        <v>0.9176</v>
       </c>
       <c r="J183" t="n">
-        <v>32.326</v>
+        <v>32.116</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6401</v>
+        <v>0.6377</v>
       </c>
       <c r="J184" t="n">
-        <v>22.4035</v>
+        <v>22.3195</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2844</v>
+        <v>-0.2088</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.954000000000001</v>
+        <v>-7.308</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3492</v>
+        <v>-0.2745</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.222</v>
+        <v>-9.6075</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.41</v>
       </c>
       <c r="I187" t="n">
-        <v>0.662</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>23.17</v>
+        <v>28.35</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.11</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2494</v>
+        <v>0.2698</v>
       </c>
       <c r="J188" t="n">
-        <v>8.728999999999999</v>
+        <v>9.443</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.97</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.049</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.01</v>
+        <v>-1.715</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.75</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4511</v>
+        <v>-0.2869</v>
       </c>
       <c r="J190" t="n">
-        <v>-15.7885</v>
+        <v>-10.0415</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.518</v>
+        <v>-0.3349</v>
       </c>
       <c r="J191" t="n">
-        <v>-18.13</v>
+        <v>-11.7215</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.94</v>
       </c>
       <c r="I192" t="n">
-        <v>1.8706</v>
+        <v>1.5863</v>
       </c>
       <c r="J192" t="n">
-        <v>35.5414</v>
+        <v>30.1397</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.57</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1874</v>
+        <v>1.1702</v>
       </c>
       <c r="J193" t="n">
-        <v>22.5606</v>
+        <v>22.2338</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.52</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0629</v>
+        <v>1.1137</v>
       </c>
       <c r="J194" t="n">
-        <v>20.1951</v>
+        <v>21.1603</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.38</v>
       </c>
       <c r="I195" t="n">
-        <v>0.7669</v>
+        <v>0.9034</v>
       </c>
       <c r="J195" t="n">
-        <v>14.5711</v>
+        <v>17.1646</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.34</v>
       </c>
       <c r="I196" t="n">
-        <v>0.6823</v>
+        <v>0.8161</v>
       </c>
       <c r="J196" t="n">
-        <v>12.9637</v>
+        <v>15.5059</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.86</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.0999</v>
+        <v>-0.1084</v>
       </c>
       <c r="J197" t="n">
-        <v>-1.8981</v>
+        <v>-2.0596</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.77</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.243</v>
+        <v>-0.2105</v>
       </c>
       <c r="J198" t="n">
-        <v>-4.617</v>
+        <v>-3.9995</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.5982</v>
+        <v>-0.4123</v>
       </c>
       <c r="J199" t="n">
-        <v>-11.3658</v>
+        <v>-7.8337</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.47</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.7271</v>
+        <v>-0.4967</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.8149</v>
+        <v>-9.4373</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.43</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7804</v>
+        <v>-0.5346</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.8276</v>
+        <v>-10.1574</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.3</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5616</v>
+        <v>0.6705</v>
       </c>
       <c r="J202" t="n">
-        <v>13.4784</v>
+        <v>16.092</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.99</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0249</v>
+        <v>-0.0075</v>
       </c>
       <c r="J203" t="n">
-        <v>0.5976</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.78</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3807</v>
+        <v>-0.2447</v>
       </c>
       <c r="J204" t="n">
-        <v>-9.136799999999999</v>
+        <v>-5.8728</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.7</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4952</v>
+        <v>-0.3221</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.8848</v>
+        <v>-7.7304</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5622</v>
+        <v>-0.3694</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.4928</v>
+        <v>-8.865600000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.44</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0666</v>
+        <v>1.0502</v>
       </c>
       <c r="J207" t="n">
-        <v>25.5984</v>
+        <v>25.2048</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.44</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0666</v>
+        <v>1.0502</v>
       </c>
       <c r="J208" t="n">
-        <v>25.5984</v>
+        <v>25.2048</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.29</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7246</v>
+        <v>0.7557</v>
       </c>
       <c r="J209" t="n">
-        <v>17.3904</v>
+        <v>18.1368</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.23</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5513</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="J210" t="n">
-        <v>13.2312</v>
+        <v>14.892</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4096</v>
+        <v>-0.33</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.830399999999999</v>
+        <v>-7.92</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.9</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0733</v>
+        <v>0.9849</v>
       </c>
       <c r="J212" t="n">
-        <v>23.6126</v>
+        <v>21.6678</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.51</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6592</v>
+        <v>0.6025</v>
       </c>
       <c r="J213" t="n">
-        <v>14.5024</v>
+        <v>13.255</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.45</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5856</v>
+        <v>0.5404</v>
       </c>
       <c r="J214" t="n">
-        <v>12.8832</v>
+        <v>11.8888</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.06</v>
       </c>
       <c r="I215" t="n">
-        <v>0.029</v>
+        <v>0.0697</v>
       </c>
       <c r="J215" t="n">
-        <v>0.638</v>
+        <v>1.5334</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.06</v>
       </c>
       <c r="I216" t="n">
-        <v>0.029</v>
+        <v>0.0697</v>
       </c>
       <c r="J216" t="n">
-        <v>0.638</v>
+        <v>1.5334</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.01</v>
       </c>
       <c r="I217" t="n">
-        <v>0.1556</v>
+        <v>0.0975</v>
       </c>
       <c r="J217" t="n">
-        <v>3.4232</v>
+        <v>2.145</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.77</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3111</v>
+        <v>-0.2376</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.8442</v>
+        <v>-5.2272</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4595</v>
+        <v>-0.3114</v>
       </c>
       <c r="J219" t="n">
-        <v>-10.109</v>
+        <v>-6.8508</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4595</v>
+        <v>-0.3114</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.109</v>
+        <v>-6.8508</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.54</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6706</v>
+        <v>-0.4517</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.7532</v>
+        <v>-9.9374</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.32</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.6479</v>
       </c>
       <c r="J222" t="n">
-        <v>15.7412</v>
+        <v>18.7891</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.12</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2576</v>
+        <v>0.284</v>
       </c>
       <c r="J223" t="n">
-        <v>7.4704</v>
+        <v>8.236000000000001</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.03</v>
       </c>
       <c r="I224" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0902</v>
       </c>
       <c r="J224" t="n">
-        <v>2.5201</v>
+        <v>2.6158</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.92</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1961</v>
+        <v>-0.1127</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.6869</v>
+        <v>-3.2683</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5732</v>
+        <v>-0.3749</v>
       </c>
       <c r="J226" t="n">
-        <v>-16.6228</v>
+        <v>-10.8721</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.25</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7437</v>
+        <v>0.7148</v>
       </c>
       <c r="J227" t="n">
-        <v>21.5673</v>
+        <v>20.7292</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.2</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6202</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J228" t="n">
-        <v>17.9858</v>
+        <v>17.1158</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.14</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4591</v>
+        <v>0.435</v>
       </c>
       <c r="J229" t="n">
-        <v>13.3139</v>
+        <v>12.615</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.93</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3445</v>
+        <v>-0.2816</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.990500000000001</v>
+        <v>-8.166399999999999</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.87</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5168</v>
+        <v>-0.4562</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.9872</v>
+        <v>-13.2298</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.56</v>
       </c>
       <c r="I232" t="n">
-        <v>1.3463</v>
+        <v>1.221</v>
       </c>
       <c r="J232" t="n">
-        <v>40.389</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5433</v>
+        <v>0.5617</v>
       </c>
       <c r="J233" t="n">
-        <v>16.299</v>
+        <v>16.851</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.14</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3573</v>
+        <v>0.4136</v>
       </c>
       <c r="J234" t="n">
-        <v>10.719</v>
+        <v>12.408</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.06</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1209</v>
+        <v>0.1871</v>
       </c>
       <c r="J235" t="n">
-        <v>3.627</v>
+        <v>5.613</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.98</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2193</v>
+        <v>-0.1417</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.579</v>
+        <v>-4.251</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.24</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4588</v>
+        <v>0.5317</v>
       </c>
       <c r="J237" t="n">
-        <v>13.764</v>
+        <v>15.951</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2485</v>
+        <v>0.2615</v>
       </c>
       <c r="J238" t="n">
-        <v>7.455</v>
+        <v>7.845</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.128</v>
+        <v>-0.0832</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.84</v>
+        <v>-2.496</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3699</v>
+        <v>-0.2326</v>
       </c>
       <c r="J240" t="n">
-        <v>-11.097</v>
+        <v>-6.978</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.65</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5748</v>
+        <v>-0.3771</v>
       </c>
       <c r="J241" t="n">
-        <v>-17.244</v>
+        <v>-11.313</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.54</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2413</v>
+        <v>1.1647</v>
       </c>
       <c r="J242" t="n">
-        <v>29.7912</v>
+        <v>27.9528</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.47</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0992</v>
+        <v>1.0782</v>
       </c>
       <c r="J243" t="n">
-        <v>26.3808</v>
+        <v>25.8768</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.32</v>
       </c>
       <c r="I244" t="n">
-        <v>0.7438</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="J244" t="n">
-        <v>17.8512</v>
+        <v>19.512</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.21</v>
       </c>
       <c r="I245" t="n">
-        <v>0.4692</v>
+        <v>0.5605</v>
       </c>
       <c r="J245" t="n">
-        <v>11.2608</v>
+        <v>13.452</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.09</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1579</v>
+        <v>0.2444</v>
       </c>
       <c r="J246" t="n">
-        <v>3.7896</v>
+        <v>5.8656</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.86</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1731</v>
+        <v>-0.1492</v>
       </c>
       <c r="J247" t="n">
-        <v>-4.1544</v>
+        <v>-3.5808</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.83</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2234</v>
+        <v>-0.1812</v>
       </c>
       <c r="J248" t="n">
-        <v>-5.3616</v>
+        <v>-4.3488</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.79</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2916</v>
+        <v>-0.2215</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.9984</v>
+        <v>-5.316</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.76</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3537</v>
+        <v>-0.2494</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.488799999999999</v>
+        <v>-5.9856</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.58</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.4181</v>
       </c>
       <c r="J251" t="n">
-        <v>-14.988</v>
+        <v>-10.0344</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.13</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3215</v>
+        <v>0.3467</v>
       </c>
       <c r="J252" t="n">
-        <v>9.323499999999999</v>
+        <v>10.0543</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.01</v>
       </c>
       <c r="I253" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J253" t="n">
-        <v>2.7608</v>
+        <v>1.9024</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.96</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0442</v>
+        <v>-0.0515</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.2818</v>
+        <v>-1.4935</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.78</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.38</v>
+        <v>-0.2444</v>
       </c>
       <c r="J255" t="n">
-        <v>-11.02</v>
+        <v>-7.0876</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.53</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7125</v>
+        <v>-0.4801</v>
       </c>
       <c r="J256" t="n">
-        <v>-20.6625</v>
+        <v>-13.9229</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.33</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9073</v>
+        <v>0.8915</v>
       </c>
       <c r="J257" t="n">
-        <v>26.3117</v>
+        <v>25.8535</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.32</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8848</v>
+        <v>0.8681</v>
       </c>
       <c r="J258" t="n">
-        <v>25.6592</v>
+        <v>25.1749</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>0.0538</v>
+        <v>0.1055</v>
       </c>
       <c r="J259" t="n">
-        <v>1.5602</v>
+        <v>3.0595</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.97</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2282</v>
+        <v>-0.1602</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.6178</v>
+        <v>-4.6458</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.93</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3606</v>
+        <v>-0.292</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.4574</v>
+        <v>-8.468</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.67</v>
       </c>
       <c r="I262" t="n">
-        <v>0.906</v>
+        <v>0.8219</v>
       </c>
       <c r="J262" t="n">
-        <v>26.274</v>
+        <v>23.8351</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.24</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3911</v>
+        <v>0.336</v>
       </c>
       <c r="J263" t="n">
-        <v>11.3419</v>
+        <v>9.744</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.09</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1364</v>
+        <v>0.1443</v>
       </c>
       <c r="J264" t="n">
-        <v>3.9556</v>
+        <v>4.1847</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.06</v>
       </c>
       <c r="I265" t="n">
-        <v>0.082</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J265" t="n">
-        <v>2.378</v>
+        <v>2.8855</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.66</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5917</v>
+        <v>-0.388</v>
       </c>
       <c r="J266" t="n">
-        <v>-17.1593</v>
+        <v>-11.252</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.11</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2509</v>
+        <v>0.2073</v>
       </c>
       <c r="J267" t="n">
-        <v>7.2761</v>
+        <v>6.0117</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.07</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1809</v>
+        <v>0.1433</v>
       </c>
       <c r="J268" t="n">
-        <v>5.2461</v>
+        <v>4.1557</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.01</v>
       </c>
       <c r="I269" t="n">
-        <v>0.0499</v>
+        <v>0.0307</v>
       </c>
       <c r="J269" t="n">
-        <v>1.4471</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.97</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0837</v>
+        <v>-0.0487</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.4273</v>
+        <v>-1.4123</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.76</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4365</v>
+        <v>-0.2767</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.6585</v>
+        <v>-8.0243</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.29</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5216</v>
+        <v>0.6166</v>
       </c>
       <c r="J272" t="n">
-        <v>14.6048</v>
+        <v>17.2648</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.09</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2269</v>
+        <v>0.237</v>
       </c>
       <c r="J273" t="n">
-        <v>6.3532</v>
+        <v>6.636</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.97</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.0606</v>
+        <v>-0.047</v>
       </c>
       <c r="J274" t="n">
-        <v>-1.6968</v>
+        <v>-1.316</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3583</v>
+        <v>-0.224</v>
       </c>
       <c r="J275" t="n">
-        <v>-10.0324</v>
+        <v>-6.272</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.63</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6022</v>
+        <v>-0.3971</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.8616</v>
+        <v>-11.1188</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.42</v>
       </c>
       <c r="I277" t="n">
-        <v>1.0848</v>
+        <v>1.0495</v>
       </c>
       <c r="J277" t="n">
-        <v>30.3744</v>
+        <v>29.386</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.32</v>
       </c>
       <c r="I278" t="n">
-        <v>0.8673</v>
+        <v>0.8562</v>
       </c>
       <c r="J278" t="n">
-        <v>24.2844</v>
+        <v>23.9736</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.04</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0733</v>
+        <v>0.1322</v>
       </c>
       <c r="J279" t="n">
-        <v>2.0524</v>
+        <v>3.7016</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.03</v>
       </c>
       <c r="I280" t="n">
-        <v>0.0375</v>
+        <v>0.0975</v>
       </c>
       <c r="J280" t="n">
-        <v>1.05</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.93</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3727</v>
+        <v>-0.3005</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.4356</v>
+        <v>-8.414</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.47</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1616</v>
+        <v>1.1029</v>
       </c>
       <c r="J282" t="n">
-        <v>31.3632</v>
+        <v>29.7783</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9064</v>
+        <v>0.9073</v>
       </c>
       <c r="J283" t="n">
-        <v>24.4728</v>
+        <v>24.4971</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.32</v>
       </c>
       <c r="I284" t="n">
-        <v>0.8384</v>
+        <v>0.8394</v>
       </c>
       <c r="J284" t="n">
-        <v>22.6368</v>
+        <v>22.6638</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.98</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2236</v>
+        <v>-0.1447</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.0372</v>
+        <v>-3.9069</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.88</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5303</v>
+        <v>-0.4605</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.3181</v>
+        <v>-12.4335</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.17</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3788</v>
+        <v>0.4224</v>
       </c>
       <c r="J287" t="n">
-        <v>10.2276</v>
+        <v>11.4048</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.14</v>
       </c>
       <c r="I288" t="n">
-        <v>0.3333</v>
+        <v>0.3629</v>
       </c>
       <c r="J288" t="n">
-        <v>8.9991</v>
+        <v>9.798299999999999</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.84</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2889</v>
+        <v>-0.1856</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.8003</v>
+        <v>-5.0112</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.7</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4973</v>
+        <v>-0.3231</v>
       </c>
       <c r="J290" t="n">
-        <v>-13.4271</v>
+        <v>-8.723699999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.61</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6153</v>
+        <v>-0.4077</v>
       </c>
       <c r="J291" t="n">
-        <v>-16.6131</v>
+        <v>-11.0079</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.44</v>
       </c>
       <c r="I292" t="n">
-        <v>0.6905</v>
+        <v>0.6504</v>
       </c>
       <c r="J292" t="n">
-        <v>24.858</v>
+        <v>23.4144</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.16</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3208</v>
+        <v>0.2764</v>
       </c>
       <c r="J293" t="n">
-        <v>11.5488</v>
+        <v>9.9504</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.12</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2576</v>
+        <v>0.2173</v>
       </c>
       <c r="J294" t="n">
-        <v>9.2736</v>
+        <v>7.8228</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.76</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.442</v>
+        <v>-0.2797</v>
       </c>
       <c r="J295" t="n">
-        <v>-15.912</v>
+        <v>-10.0692</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.57</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6832</v>
+        <v>-0.4575</v>
       </c>
       <c r="J296" t="n">
-        <v>-24.5952</v>
+        <v>-16.47</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.61</v>
       </c>
       <c r="I297" t="n">
-        <v>0.8583</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="J297" t="n">
-        <v>30.8988</v>
+        <v>27.8532</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.08</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1434</v>
+        <v>0.1356</v>
       </c>
       <c r="J298" t="n">
-        <v>5.1624</v>
+        <v>4.8816</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.96</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1443</v>
+        <v>-0.0722</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.1948</v>
+        <v>-2.5992</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1825</v>
+        <v>-0.0974</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.57</v>
+        <v>-3.5064</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.85</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3295</v>
+        <v>-0.1978</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.862</v>
+        <v>-7.1208</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.65</v>
       </c>
       <c r="I302" t="n">
-        <v>1.4998</v>
+        <v>1.3237</v>
       </c>
       <c r="J302" t="n">
-        <v>35.9952</v>
+        <v>31.7688</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.13</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3091</v>
+        <v>0.3793</v>
       </c>
       <c r="J303" t="n">
-        <v>7.4184</v>
+        <v>9.103199999999999</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.12</v>
       </c>
       <c r="I304" t="n">
-        <v>0.2814</v>
+        <v>0.3523</v>
       </c>
       <c r="J304" t="n">
-        <v>6.7536</v>
+        <v>8.4552</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.12</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2814</v>
+        <v>0.3523</v>
       </c>
       <c r="J305" t="n">
-        <v>6.7536</v>
+        <v>8.4552</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.1</v>
       </c>
       <c r="I306" t="n">
-        <v>0.2249</v>
+        <v>0.2969</v>
       </c>
       <c r="J306" t="n">
-        <v>5.3976</v>
+        <v>7.1256</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.19</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4235</v>
+        <v>0.4806</v>
       </c>
       <c r="J307" t="n">
-        <v>10.164</v>
+        <v>11.5344</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.93</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.1672</v>
+        <v>-2.0352</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.9</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1463</v>
+        <v>-0.1195</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.5112</v>
+        <v>-2.868</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.67</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5278</v>
+        <v>-0.3463</v>
       </c>
       <c r="J310" t="n">
-        <v>-12.6672</v>
+        <v>-8.311199999999999</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.57</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6579</v>
+        <v>-0.4397</v>
       </c>
       <c r="J311" t="n">
-        <v>-15.7896</v>
+        <v>-10.5528</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.36</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9307</v>
+        <v>0.9302</v>
       </c>
       <c r="J312" t="n">
-        <v>25.1289</v>
+        <v>25.1154</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.3</v>
       </c>
       <c r="I313" t="n">
-        <v>0.7942</v>
+        <v>0.7946</v>
       </c>
       <c r="J313" t="n">
-        <v>21.4434</v>
+        <v>21.4542</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.24</v>
       </c>
       <c r="I314" t="n">
-        <v>0.6468</v>
+        <v>0.6549</v>
       </c>
       <c r="J314" t="n">
-        <v>17.4636</v>
+        <v>17.6823</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.13</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3241</v>
+        <v>0.3856</v>
       </c>
       <c r="J315" t="n">
-        <v>8.7507</v>
+        <v>10.4112</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.95</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3272</v>
+        <v>-0.2494</v>
       </c>
       <c r="J316" t="n">
-        <v>-8.8344</v>
+        <v>-6.7338</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.17</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3495</v>
+        <v>0.3918</v>
       </c>
       <c r="J317" t="n">
-        <v>9.436500000000001</v>
+        <v>10.5786</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.16</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3345</v>
+        <v>0.3727</v>
       </c>
       <c r="J318" t="n">
-        <v>9.031499999999999</v>
+        <v>10.0629</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1224</v>
+        <v>-0.0733</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.3048</v>
+        <v>-1.9791</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.91</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2006</v>
+        <v>-0.12</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.4162</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.67</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.554</v>
+        <v>-0.3614</v>
       </c>
       <c r="J321" t="n">
-        <v>-14.958</v>
+        <v>-9.7578</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.44</v>
       </c>
       <c r="I322" t="n">
-        <v>1.109</v>
+        <v>1.0682</v>
       </c>
       <c r="J322" t="n">
-        <v>29.943</v>
+        <v>28.8414</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.33</v>
       </c>
       <c r="I323" t="n">
-        <v>0.8713</v>
+        <v>0.8678</v>
       </c>
       <c r="J323" t="n">
-        <v>23.5251</v>
+        <v>23.4306</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.25</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6816</v>
+        <v>0.6818</v>
       </c>
       <c r="J324" t="n">
-        <v>18.4032</v>
+        <v>18.4086</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.17</v>
       </c>
       <c r="I325" t="n">
-        <v>0.4492</v>
+        <v>0.4909</v>
       </c>
       <c r="J325" t="n">
-        <v>12.1284</v>
+        <v>13.2543</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.72</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.9081</v>
+        <v>-0.8718</v>
       </c>
       <c r="J326" t="n">
-        <v>-24.5187</v>
+        <v>-23.5386</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.31</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5455</v>
+        <v>0.6493</v>
       </c>
       <c r="J327" t="n">
-        <v>14.7285</v>
+        <v>17.5311</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.09</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2246</v>
+        <v>0.2353</v>
       </c>
       <c r="J328" t="n">
-        <v>6.0642</v>
+        <v>6.3531</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.97</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.065</v>
+        <v>-0.0475</v>
       </c>
       <c r="J329" t="n">
-        <v>-1.755</v>
+        <v>-1.2825</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.92</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1788</v>
+        <v>-0.1079</v>
       </c>
       <c r="J330" t="n">
-        <v>-4.8276</v>
+        <v>-2.9133</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.53</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7245</v>
+        <v>-0.4891</v>
       </c>
       <c r="J331" t="n">
-        <v>-19.5615</v>
+        <v>-13.2057</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.65</v>
       </c>
       <c r="I332" t="n">
-        <v>1.4663</v>
+        <v>1.3052</v>
       </c>
       <c r="J332" t="n">
-        <v>41.0564</v>
+        <v>36.5456</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.53</v>
       </c>
       <c r="I333" t="n">
-        <v>1.2356</v>
+        <v>1.1581</v>
       </c>
       <c r="J333" t="n">
-        <v>34.5968</v>
+        <v>32.4268</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.42</v>
       </c>
       <c r="I334" t="n">
-        <v>1.0087</v>
+        <v>1.0156</v>
       </c>
       <c r="J334" t="n">
-        <v>28.2436</v>
+        <v>28.4368</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.08</v>
       </c>
       <c r="I335" t="n">
-        <v>0.1393</v>
+        <v>0.222</v>
       </c>
       <c r="J335" t="n">
-        <v>3.9004</v>
+        <v>6.216</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.8</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.7511</v>
+        <v>-0.6966</v>
       </c>
       <c r="J336" t="n">
-        <v>-21.0308</v>
+        <v>-19.5048</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.22</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4725</v>
+        <v>0.5476</v>
       </c>
       <c r="J337" t="n">
-        <v>13.23</v>
+        <v>15.3328</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.87</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1926</v>
+        <v>-0.1499</v>
       </c>
       <c r="J338" t="n">
-        <v>-5.3928</v>
+        <v>-4.1972</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.75</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.4089</v>
+        <v>-0.2676</v>
       </c>
       <c r="J339" t="n">
-        <v>-11.4492</v>
+        <v>-7.4928</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4958</v>
+        <v>-0.3251</v>
       </c>
       <c r="J340" t="n">
-        <v>-13.8824</v>
+        <v>-9.1028</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.65</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5505</v>
+        <v>-0.3629</v>
       </c>
       <c r="J341" t="n">
-        <v>-15.414</v>
+        <v>-10.1612</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.53</v>
       </c>
       <c r="I342" t="n">
-        <v>1.2828</v>
+        <v>1.1803</v>
       </c>
       <c r="J342" t="n">
-        <v>33.3528</v>
+        <v>30.6878</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.5</v>
       </c>
       <c r="I343" t="n">
-        <v>1.2232</v>
+        <v>1.142</v>
       </c>
       <c r="J343" t="n">
-        <v>31.8032</v>
+        <v>29.692</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.1</v>
       </c>
       <c r="I344" t="n">
-        <v>0.2372</v>
+        <v>0.303</v>
       </c>
       <c r="J344" t="n">
-        <v>6.1672</v>
+        <v>7.878</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.98</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2229</v>
+        <v>-0.1442</v>
       </c>
       <c r="J345" t="n">
-        <v>-5.7954</v>
+        <v>-3.7492</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.88</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="J346" t="n">
-        <v>-13.7722</v>
+        <v>-11.96</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.23</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4708</v>
+        <v>0.5452</v>
       </c>
       <c r="J347" t="n">
-        <v>12.2408</v>
+        <v>14.1752</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.97</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.02</v>
+        <v>-0.037</v>
       </c>
       <c r="J348" t="n">
-        <v>-0.52</v>
+        <v>-0.962</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.84</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.2815</v>
+        <v>-0.1839</v>
       </c>
       <c r="J349" t="n">
-        <v>-7.319</v>
+        <v>-4.7814</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.76</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4079</v>
+        <v>-0.2632</v>
       </c>
       <c r="J350" t="n">
-        <v>-10.6054</v>
+        <v>-6.8432</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.58</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.65</v>
+        <v>-0.4335</v>
       </c>
       <c r="J351" t="n">
-        <v>-16.9</v>
+        <v>-11.271</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.61</v>
       </c>
       <c r="I352" t="n">
-        <v>0.8031</v>
+        <v>0.7245</v>
       </c>
       <c r="J352" t="n">
-        <v>20.0775</v>
+        <v>18.1125</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.38</v>
       </c>
       <c r="I353" t="n">
-        <v>0.5336</v>
+        <v>0.4783</v>
       </c>
       <c r="J353" t="n">
-        <v>13.34</v>
+        <v>11.9575</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.33</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4672</v>
+        <v>0.4231</v>
       </c>
       <c r="J354" t="n">
-        <v>11.68</v>
+        <v>10.5775</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.28</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3886</v>
+        <v>0.3679</v>
       </c>
       <c r="J355" t="n">
-        <v>9.715</v>
+        <v>9.1975</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.4166</v>
+        <v>-0.257</v>
       </c>
       <c r="J356" t="n">
-        <v>-10.415</v>
+        <v>-6.425</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.13</v>
       </c>
       <c r="I357" t="n">
-        <v>0.3261</v>
+        <v>0.2693</v>
       </c>
       <c r="J357" t="n">
-        <v>8.1525</v>
+        <v>6.7325</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.99</v>
       </c>
       <c r="I358" t="n">
-        <v>0.0308</v>
+        <v>-0.0052</v>
       </c>
       <c r="J358" t="n">
-        <v>0.77</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.89</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1752</v>
+        <v>-0.1325</v>
       </c>
       <c r="J359" t="n">
-        <v>-4.38</v>
+        <v>-3.3125</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.71</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.4777</v>
+        <v>-0.3107</v>
       </c>
       <c r="J360" t="n">
-        <v>-11.9425</v>
+        <v>-7.7675</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.63</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5851</v>
+        <v>-0.3863</v>
       </c>
       <c r="J361" t="n">
-        <v>-14.6275</v>
+        <v>-9.657500000000001</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.32</v>
       </c>
       <c r="I362" t="n">
-        <v>0.5316</v>
+        <v>0.6355</v>
       </c>
       <c r="J362" t="n">
-        <v>15.948</v>
+        <v>19.065</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.21</v>
       </c>
       <c r="I363" t="n">
-        <v>0.3828</v>
+        <v>0.4437</v>
       </c>
       <c r="J363" t="n">
-        <v>11.484</v>
+        <v>13.311</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>0.96</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.1311</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J364" t="n">
-        <v>-3.933</v>
+        <v>-2.028</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>0.89</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.2572</v>
+        <v>-0.1502</v>
       </c>
       <c r="J365" t="n">
-        <v>-7.716</v>
+        <v>-4.506</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.84</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.335</v>
+        <v>-0.2034</v>
       </c>
       <c r="J366" t="n">
-        <v>-10.05</v>
+        <v>-6.102</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.28</v>
       </c>
       <c r="I367" t="n">
-        <v>0.8066</v>
+        <v>0.7824</v>
       </c>
       <c r="J367" t="n">
-        <v>24.198</v>
+        <v>23.472</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.09</v>
       </c>
       <c r="I368" t="n">
-        <v>0.2824</v>
+        <v>0.297</v>
       </c>
       <c r="J368" t="n">
-        <v>8.472</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.08</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2451</v>
+        <v>0.2689</v>
       </c>
       <c r="J369" t="n">
-        <v>7.353</v>
+        <v>8.067</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>1.06</v>
       </c>
       <c r="I370" t="n">
-        <v>0.1757</v>
+        <v>0.2097</v>
       </c>
       <c r="J370" t="n">
-        <v>5.271</v>
+        <v>6.291</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.95</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.2869</v>
+        <v>-0.222</v>
       </c>
       <c r="J371" t="n">
-        <v>-8.606999999999999</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.17</v>
       </c>
       <c r="I372" t="n">
-        <v>0.3459</v>
+        <v>0.3885</v>
       </c>
       <c r="J372" t="n">
-        <v>14.5278</v>
+        <v>16.317</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.05</v>
       </c>
       <c r="I373" t="n">
-        <v>0.1433</v>
+        <v>0.1431</v>
       </c>
       <c r="J373" t="n">
-        <v>6.0186</v>
+        <v>6.0102</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>0.99</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.023</v>
+        <v>-0.0195</v>
       </c>
       <c r="J374" t="n">
-        <v>-0.966</v>
+        <v>-0.819</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.91</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.2043</v>
+        <v>-0.1211</v>
       </c>
       <c r="J375" t="n">
-        <v>-8.5806</v>
+        <v>-5.0862</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.79</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.3937</v>
+        <v>-0.2469</v>
       </c>
       <c r="J376" t="n">
-        <v>-16.5354</v>
+        <v>-10.3698</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.42</v>
       </c>
       <c r="I377" t="n">
-        <v>1.0963</v>
+        <v>1.0555</v>
       </c>
       <c r="J377" t="n">
-        <v>46.0446</v>
+        <v>44.331</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.24</v>
       </c>
       <c r="I378" t="n">
-        <v>0.6913</v>
+        <v>0.6736</v>
       </c>
       <c r="J378" t="n">
-        <v>29.0346</v>
+        <v>28.2912</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>1.09</v>
       </c>
       <c r="I379" t="n">
-        <v>0.2496</v>
+        <v>0.2909</v>
       </c>
       <c r="J379" t="n">
-        <v>10.4832</v>
+        <v>12.2178</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.96</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.268</v>
+        <v>-0.1978</v>
       </c>
       <c r="J380" t="n">
-        <v>-11.256</v>
+        <v>-8.307600000000001</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.92</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3945</v>
+        <v>-0.3252</v>
       </c>
       <c r="J381" t="n">
-        <v>-16.569</v>
+        <v>-13.6584</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.37</v>
       </c>
       <c r="I382" t="n">
-        <v>0.6207</v>
+        <v>0.7524</v>
       </c>
       <c r="J382" t="n">
-        <v>16.7589</v>
+        <v>20.3148</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>1.08</v>
       </c>
       <c r="I383" t="n">
-        <v>0.2062</v>
+        <v>0.2135</v>
       </c>
       <c r="J383" t="n">
-        <v>5.5674</v>
+        <v>5.7645</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>0.95</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.119</v>
+        <v>-0.0728</v>
       </c>
       <c r="J384" t="n">
-        <v>-3.213</v>
+        <v>-1.9656</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.82</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.3456</v>
+        <v>-0.2148</v>
       </c>
       <c r="J385" t="n">
-        <v>-9.331200000000001</v>
+        <v>-5.7996</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.61</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.6284</v>
+        <v>-0.4164</v>
       </c>
       <c r="J386" t="n">
-        <v>-16.9668</v>
+        <v>-11.2428</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.43</v>
       </c>
       <c r="I387" t="n">
-        <v>1.081</v>
+        <v>1.0515</v>
       </c>
       <c r="J387" t="n">
-        <v>29.187</v>
+        <v>28.3905</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.32</v>
       </c>
       <c r="I388" t="n">
-        <v>0.8407</v>
+        <v>0.8406</v>
       </c>
       <c r="J388" t="n">
-        <v>22.6989</v>
+        <v>22.6962</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>1.13</v>
       </c>
       <c r="I389" t="n">
-        <v>0.3241</v>
+        <v>0.3856</v>
       </c>
       <c r="J389" t="n">
-        <v>8.7507</v>
+        <v>10.4112</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>1.12</v>
       </c>
       <c r="I390" t="n">
-        <v>0.2957</v>
+        <v>0.3587</v>
       </c>
       <c r="J390" t="n">
-        <v>7.9839</v>
+        <v>9.684900000000001</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.98</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.2222</v>
+        <v>-0.1437</v>
       </c>
       <c r="J391" t="n">
-        <v>-5.9994</v>
+        <v>-3.8799</v>
       </c>
     </row>
     <row r="392">
@@ -18029,10 +18029,10 @@
         <v>1.52</v>
       </c>
       <c r="I392" t="n">
-        <v>0.7887</v>
+        <v>0.981</v>
       </c>
       <c r="J392" t="n">
-        <v>22.0836</v>
+        <v>27.468</v>
       </c>
     </row>
     <row r="393">
@@ -18069,10 +18069,10 @@
         <v>1.05</v>
       </c>
       <c r="I393" t="n">
-        <v>0.1381</v>
+        <v>0.1405</v>
       </c>
       <c r="J393" t="n">
-        <v>3.8668</v>
+        <v>3.934</v>
       </c>
     </row>
     <row r="394">
@@ -18109,10 +18109,10 @@
         <v>0.99</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.0359</v>
+        <v>-0.0202</v>
       </c>
       <c r="J394" t="n">
-        <v>-1.0052</v>
+        <v>-0.5656</v>
       </c>
     </row>
     <row r="395">
@@ -18149,10 +18149,10 @@
         <v>0.78</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.4108</v>
+        <v>-0.2582</v>
       </c>
       <c r="J395" t="n">
-        <v>-11.5024</v>
+        <v>-7.2296</v>
       </c>
     </row>
     <row r="396">
@@ -18189,10 +18189,10 @@
         <v>0.63</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.6081</v>
+        <v>-0.401</v>
       </c>
       <c r="J396" t="n">
-        <v>-17.0268</v>
+        <v>-11.228</v>
       </c>
     </row>
     <row r="397">
@@ -18229,10 +18229,10 @@
         <v>1.24</v>
       </c>
       <c r="I397" t="n">
-        <v>0.6792</v>
+        <v>0.6676</v>
       </c>
       <c r="J397" t="n">
-        <v>19.0176</v>
+        <v>18.6928</v>
       </c>
     </row>
     <row r="398">
@@ -18269,10 +18269,10 @@
         <v>1.23</v>
       </c>
       <c r="I398" t="n">
-        <v>0.6542</v>
+        <v>0.6435</v>
       </c>
       <c r="J398" t="n">
-        <v>18.3176</v>
+        <v>18.018</v>
       </c>
     </row>
     <row r="399">
@@ -18309,10 +18309,10 @@
         <v>1.23</v>
       </c>
       <c r="I399" t="n">
-        <v>0.6542</v>
+        <v>0.6435</v>
       </c>
       <c r="J399" t="n">
-        <v>18.3176</v>
+        <v>18.018</v>
       </c>
     </row>
     <row r="400">
@@ -18349,10 +18349,10 @@
         <v>1.03</v>
       </c>
       <c r="I400" t="n">
-        <v>0.0385</v>
+        <v>0.098</v>
       </c>
       <c r="J400" t="n">
-        <v>1.078</v>
+        <v>2.744</v>
       </c>
     </row>
     <row r="401">
@@ -18389,10 +18389,10 @@
         <v>1</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.1016</v>
+        <v>-0.0348</v>
       </c>
       <c r="J401" t="n">
-        <v>-2.8448</v>
+        <v>-0.9744</v>
       </c>
     </row>
     <row r="402">
@@ -18429,10 +18429,10 @@
         <v>1.85</v>
       </c>
       <c r="I402" t="n">
-        <v>1.0126</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="J402" t="n">
-        <v>20.252</v>
+        <v>18.68</v>
       </c>
     </row>
     <row r="403">
@@ -18469,10 +18469,10 @@
         <v>1.67</v>
       </c>
       <c r="I403" t="n">
-        <v>0.8266</v>
+        <v>0.7583</v>
       </c>
       <c r="J403" t="n">
-        <v>16.532</v>
+        <v>15.166</v>
       </c>
     </row>
     <row r="404">
@@ -18509,10 +18509,10 @@
         <v>1.47</v>
       </c>
       <c r="I404" t="n">
-        <v>0.5939</v>
+        <v>0.5568</v>
       </c>
       <c r="J404" t="n">
-        <v>11.878</v>
+        <v>11.136</v>
       </c>
     </row>
     <row r="405">
@@ -18549,10 +18549,10 @@
         <v>1.28</v>
       </c>
       <c r="I405" t="n">
-        <v>0.3373</v>
+        <v>0.3528</v>
       </c>
       <c r="J405" t="n">
-        <v>6.746</v>
+        <v>7.056</v>
       </c>
     </row>
     <row r="406">
@@ -18589,10 +18589,10 @@
         <v>0.95</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.2245</v>
+        <v>-0.1174</v>
       </c>
       <c r="J406" t="n">
-        <v>-4.49</v>
+        <v>-2.348</v>
       </c>
     </row>
     <row r="407">
@@ -18629,10 +18629,10 @@
         <v>0.97</v>
       </c>
       <c r="I407" t="n">
-        <v>0.0638</v>
+        <v>0.0132</v>
       </c>
       <c r="J407" t="n">
-        <v>1.276</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="408">
@@ -18669,10 +18669,10 @@
         <v>0.83</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.185</v>
+        <v>-0.1651</v>
       </c>
       <c r="J408" t="n">
-        <v>-3.7</v>
+        <v>-3.302</v>
       </c>
     </row>
     <row r="409">
@@ -18709,10 +18709,10 @@
         <v>0.66</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.4789</v>
+        <v>-0.3318</v>
       </c>
       <c r="J409" t="n">
-        <v>-9.577999999999999</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="410">
@@ -18749,10 +18749,10 @@
         <v>0.62</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.3686</v>
       </c>
       <c r="J410" t="n">
-        <v>-10.836</v>
+        <v>-7.372</v>
       </c>
     </row>
     <row r="411">
@@ -18789,10 +18789,10 @@
         <v>0.36</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.8839</v>
+        <v>-0.6118</v>
       </c>
       <c r="J411" t="n">
-        <v>-17.678</v>
+        <v>-12.236</v>
       </c>
     </row>
     <row r="412">
@@ -18829,10 +18829,10 @@
         <v>1.38</v>
       </c>
       <c r="I412" t="n">
-        <v>0.6494</v>
+        <v>0.7929</v>
       </c>
       <c r="J412" t="n">
-        <v>17.5338</v>
+        <v>21.4083</v>
       </c>
     </row>
     <row r="413">
@@ -18869,10 +18869,10 @@
         <v>0.95</v>
       </c>
       <c r="I413" t="n">
-        <v>-0.0837</v>
+        <v>-0.0692</v>
       </c>
       <c r="J413" t="n">
-        <v>-2.2599</v>
+        <v>-1.8684</v>
       </c>
     </row>
     <row r="414">
@@ -18909,10 +18909,10 @@
         <v>0.89</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.2142</v>
+        <v>-0.1366</v>
       </c>
       <c r="J414" t="n">
-        <v>-5.7834</v>
+        <v>-3.6882</v>
       </c>
     </row>
     <row r="415">
@@ -18949,10 +18949,10 @@
         <v>0.89</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.2142</v>
+        <v>-0.1366</v>
       </c>
       <c r="J415" t="n">
-        <v>-5.7834</v>
+        <v>-3.6882</v>
       </c>
     </row>
     <row r="416">
@@ -18989,10 +18989,10 @@
         <v>0.49</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.5206</v>
       </c>
       <c r="J416" t="n">
-        <v>-20.6712</v>
+        <v>-14.0562</v>
       </c>
     </row>
     <row r="417">
@@ -19029,10 +19029,10 @@
         <v>1.83</v>
       </c>
       <c r="I417" t="n">
-        <v>1.83</v>
+        <v>1.5479</v>
       </c>
       <c r="J417" t="n">
-        <v>49.41</v>
+        <v>41.7933</v>
       </c>
     </row>
     <row r="418">
@@ -19069,10 +19069,10 @@
         <v>1.2</v>
       </c>
       <c r="I418" t="n">
-        <v>0.5127</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="J418" t="n">
-        <v>13.8429</v>
+        <v>15.093</v>
       </c>
     </row>
     <row r="419">
@@ -19109,10 +19109,10 @@
         <v>1.14</v>
       </c>
       <c r="I419" t="n">
-        <v>0.3442</v>
+        <v>0.4089</v>
       </c>
       <c r="J419" t="n">
-        <v>9.2934</v>
+        <v>11.0403</v>
       </c>
     </row>
     <row r="420">
@@ -19149,10 +19149,10 @@
         <v>1.1</v>
       </c>
       <c r="I420" t="n">
-        <v>0.2314</v>
+        <v>0.3002</v>
       </c>
       <c r="J420" t="n">
-        <v>6.2478</v>
+        <v>8.105399999999999</v>
       </c>
     </row>
     <row r="421">
@@ -19189,10 +19189,10 @@
         <v>0.78</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.779</v>
+        <v>-0.7287</v>
       </c>
       <c r="J421" t="n">
-        <v>-21.033</v>
+        <v>-19.6749</v>
       </c>
     </row>
     <row r="422">
@@ -19229,10 +19229,10 @@
         <v>1.15</v>
       </c>
       <c r="I422" t="n">
-        <v>0.3134</v>
+        <v>0.3485</v>
       </c>
       <c r="J422" t="n">
-        <v>9.0886</v>
+        <v>10.1065</v>
       </c>
     </row>
     <row r="423">
@@ -19269,10 +19269,10 @@
         <v>1.04</v>
       </c>
       <c r="I423" t="n">
-        <v>0.12</v>
+        <v>0.1184</v>
       </c>
       <c r="J423" t="n">
-        <v>3.48</v>
+        <v>3.4336</v>
       </c>
     </row>
     <row r="424">
@@ -19309,10 +19309,10 @@
         <v>0.97</v>
       </c>
       <c r="I424" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.049</v>
       </c>
       <c r="J424" t="n">
-        <v>-2.494</v>
+        <v>-1.421</v>
       </c>
     </row>
     <row r="425">
@@ -19349,10 +19349,10 @@
         <v>0.96</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.1089</v>
+        <v>-0.0621</v>
       </c>
       <c r="J425" t="n">
-        <v>-3.1581</v>
+        <v>-1.8009</v>
       </c>
     </row>
     <row r="426">
@@ -19389,10 +19389,10 @@
         <v>0.82</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.3514</v>
+        <v>-0.2174</v>
       </c>
       <c r="J426" t="n">
-        <v>-10.1906</v>
+        <v>-6.3046</v>
       </c>
     </row>
     <row r="427">
@@ -19429,10 +19429,10 @@
         <v>1.74</v>
       </c>
       <c r="I427" t="n">
-        <v>1.7218</v>
+        <v>1.4746</v>
       </c>
       <c r="J427" t="n">
-        <v>49.9322</v>
+        <v>42.7634</v>
       </c>
     </row>
     <row r="428">
@@ -19469,10 +19469,10 @@
         <v>1.12</v>
       </c>
       <c r="I428" t="n">
-        <v>0.3725</v>
+        <v>0.3747</v>
       </c>
       <c r="J428" t="n">
-        <v>10.8025</v>
+        <v>10.8663</v>
       </c>
     </row>
     <row r="429">
@@ -19509,10 +19509,10 @@
         <v>0.99</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.1444</v>
+        <v>-0.0803</v>
       </c>
       <c r="J429" t="n">
-        <v>-4.1876</v>
+        <v>-2.3287</v>
       </c>
     </row>
     <row r="430">
@@ -19549,10 +19549,10 @@
         <v>0.88</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.5016</v>
+        <v>-0.4371</v>
       </c>
       <c r="J430" t="n">
-        <v>-14.5464</v>
+        <v>-12.6759</v>
       </c>
     </row>
     <row r="431">
@@ -19589,10 +19589,10 @@
         <v>0.82</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.6567</v>
+        <v>-0.6002</v>
       </c>
       <c r="J431" t="n">
-        <v>-19.0443</v>
+        <v>-17.4058</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5286/event_5286_evp_summary.xlsx
+++ b/database/event/5286/event_5286_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7286</v>
+        <v>5.4192</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0338</v>
+        <v>0.978</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9482</v>
+        <v>1.8427</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7286</v>
+        <v>5.4192</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7674</v>
+        <v>3.4083</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9612</v>
+        <v>2.0109</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9128</v>
+        <v>4.7348</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9128</v>
+        <v>4.7348</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9612</v>
+        <v>2.0109</v>
       </c>
       <c r="K2" t="n">
         <v>316</v>
@@ -529,7 +529,7 @@
         <v>29</v>
       </c>
       <c r="M2" t="n">
-        <v>6.874</v>
+        <v>6.745699999999999</v>
       </c>
       <c r="N2" t="n">
         <v>345</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4645</v>
+        <v>5.1628</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9862</v>
+        <v>0.9317</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8289</v>
+        <v>1.726</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4645</v>
+        <v>5.1628</v>
       </c>
       <c r="F3" t="n">
-        <v>5.1646</v>
+        <v>4.9038</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2999</v>
+        <v>0.259</v>
       </c>
       <c r="H3" t="n">
-        <v>7.9806</v>
+        <v>8.007899999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>8.650499999999999</v>
+        <v>8.4259</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2999</v>
+        <v>0.259</v>
       </c>
       <c r="K3" t="n">
         <v>384</v>
@@ -575,7 +575,7 @@
         <v>29</v>
       </c>
       <c r="M3" t="n">
-        <v>8.950399999999998</v>
+        <v>8.684900000000001</v>
       </c>
       <c r="N3" t="n">
         <v>413</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7185</v>
+        <v>4.3267</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8516</v>
+        <v>0.7808</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4922</v>
+        <v>1.3454</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7185</v>
+        <v>4.3267</v>
       </c>
       <c r="F4" t="n">
-        <v>4.7185</v>
+        <v>4.3267</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.0011</v>
+        <v>6.7449</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0011</v>
+        <v>6.7449</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7.0011</v>
+        <v>6.7449</v>
       </c>
       <c r="N4" t="n">
         <v>296</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6306</v>
+        <v>4.2785</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8357</v>
+        <v>0.7721</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4525</v>
+        <v>1.3235</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6306</v>
+        <v>4.2785</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4438</v>
+        <v>4.4964</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1868</v>
+        <v>-0.2179</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2021</v>
+        <v>7.1163</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2021</v>
+        <v>7.4878</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1868</v>
+        <v>-0.2179</v>
       </c>
       <c r="K5" t="n">
-        <v>316</v>
+        <v>384</v>
       </c>
       <c r="L5" t="n">
         <v>29</v>
       </c>
       <c r="M5" t="n">
-        <v>5.3889</v>
+        <v>7.2699</v>
       </c>
       <c r="N5" t="n">
-        <v>345</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5646</v>
+        <v>4.2164</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8238</v>
+        <v>0.7609</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4227</v>
+        <v>1.2952</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5646</v>
+        <v>4.2164</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7704</v>
+        <v>3.0602</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2058</v>
+        <v>1.1562</v>
       </c>
       <c r="H6" t="n">
-        <v>7.115</v>
+        <v>3.9729</v>
       </c>
       <c r="I6" t="n">
-        <v>7.7123</v>
+        <v>3.9729</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2058</v>
+        <v>1.1562</v>
       </c>
       <c r="K6" t="n">
-        <v>384</v>
+        <v>316</v>
       </c>
       <c r="L6" t="n">
         <v>29</v>
       </c>
       <c r="M6" t="n">
-        <v>7.5065</v>
+        <v>5.1291</v>
       </c>
       <c r="N6" t="n">
-        <v>413</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5074</v>
+        <v>4.1196</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8135</v>
+        <v>0.7435</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3969</v>
+        <v>1.2511</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5074</v>
+        <v>4.1196</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7401</v>
+        <v>2.4508</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7673</v>
+        <v>1.6688</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7401</v>
+        <v>2.639</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7401</v>
+        <v>2.639</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7673</v>
+        <v>1.6688</v>
       </c>
       <c r="K7" t="n">
         <v>316</v>
@@ -759,7 +759,7 @@
         <v>29</v>
       </c>
       <c r="M7" t="n">
-        <v>4.507400000000001</v>
+        <v>4.3078</v>
       </c>
       <c r="N7" t="n">
         <v>345</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.453</v>
+        <v>4.0689</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8036</v>
+        <v>0.7343</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3723</v>
+        <v>1.228</v>
       </c>
       <c r="E8" t="n">
-        <v>4.453</v>
+        <v>4.0689</v>
       </c>
       <c r="F8" t="n">
-        <v>4.453</v>
+        <v>4.0689</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>6.4182</v>
+        <v>6.1806</v>
       </c>
       <c r="I8" t="n">
-        <v>6.4182</v>
+        <v>6.1806</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>6.4182</v>
+        <v>6.1806</v>
       </c>
       <c r="N8" t="n">
         <v>318</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4989</v>
+        <v>3.1435</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6315</v>
+        <v>0.5673</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9416</v>
+        <v>0.8068</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4989</v>
+        <v>3.1435</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4989</v>
+        <v>3.1435</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3231</v>
+        <v>4.1552</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3231</v>
+        <v>4.1552</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3231</v>
+        <v>4.1552</v>
       </c>
       <c r="N9" t="n">
         <v>318</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2563</v>
+        <v>2.954</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5877</v>
+        <v>0.5331</v>
       </c>
       <c r="D10" t="n">
-        <v>0.832</v>
+        <v>0.7205</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2563</v>
+        <v>2.954</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2563</v>
+        <v>2.954</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7905</v>
+        <v>3.7404</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7905</v>
+        <v>3.7404</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7905</v>
+        <v>3.7404</v>
       </c>
       <c r="N10" t="n">
         <v>318</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1172</v>
+        <v>2.7649</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5626</v>
+        <v>0.499</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7692</v>
+        <v>0.6344</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1172</v>
+        <v>2.7649</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1172</v>
+        <v>2.7649</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4851</v>
+        <v>3.3266</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4851</v>
+        <v>3.3266</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4851</v>
+        <v>3.3266</v>
       </c>
       <c r="N11" t="n">
         <v>216</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9639</v>
+        <v>2.6669</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5349</v>
+        <v>0.4813</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7</v>
+        <v>0.5898</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9639</v>
+        <v>2.6669</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6238</v>
+        <v>3.3577</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6599</v>
+        <v>-0.6908</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5974</v>
+        <v>4.6241</v>
       </c>
       <c r="I12" t="n">
-        <v>4.9833</v>
+        <v>4.8655</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6599</v>
+        <v>-0.6908</v>
       </c>
       <c r="K12" t="n">
         <v>384</v>
@@ -989,7 +989,7 @@
         <v>29</v>
       </c>
       <c r="M12" t="n">
-        <v>4.323399999999999</v>
+        <v>4.1747</v>
       </c>
       <c r="N12" t="n">
         <v>413</v>
@@ -998,139 +998,139 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8258</v>
+        <v>2.5081</v>
       </c>
       <c r="C13" t="n">
-        <v>0.51</v>
+        <v>0.4526</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6377</v>
+        <v>0.5175</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8258</v>
+        <v>2.5081</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8258</v>
+        <v>2.5081</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8453</v>
+        <v>2.7646</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8453</v>
+        <v>2.7646</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>318</v>
+        <v>237</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8453</v>
+        <v>2.7646</v>
       </c>
       <c r="N13" t="n">
-        <v>318</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8215</v>
+        <v>2.4858</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5092</v>
+        <v>0.4486</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6358</v>
+        <v>0.5074</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8215</v>
+        <v>2.4858</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8215</v>
+        <v>2.4858</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8357</v>
+        <v>2.7158</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8357</v>
+        <v>2.7158</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8357</v>
+        <v>2.7158</v>
       </c>
       <c r="N14" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8133</v>
+        <v>2.482</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5077</v>
+        <v>0.4479</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6321</v>
+        <v>0.5057</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8133</v>
+        <v>2.482</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8133</v>
+        <v>2.482</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8178</v>
+        <v>2.7074</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8178</v>
+        <v>2.7074</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>216</v>
+        <v>318</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8178</v>
+        <v>2.7074</v>
       </c>
       <c r="N15" t="n">
-        <v>216</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6771</v>
+        <v>2.4165</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4831</v>
+        <v>0.4361</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5706</v>
+        <v>0.4758</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6771</v>
+        <v>2.4165</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6771</v>
+        <v>2.4165</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6771</v>
+        <v>2.5641</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6771</v>
+        <v>2.5641</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.6771</v>
+        <v>2.5641</v>
       </c>
       <c r="N16" t="n">
         <v>217</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3493</v>
+        <v>2.2432</v>
       </c>
       <c r="C17" t="n">
-        <v>0.424</v>
+        <v>0.4048</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4226</v>
+        <v>0.3969</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3493</v>
+        <v>2.2432</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3493</v>
+        <v>2.2432</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3493</v>
+        <v>2.2432</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3493</v>
+        <v>2.2432</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3493</v>
+        <v>2.2432</v>
       </c>
       <c r="N17" t="n">
         <v>216</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0725</v>
+        <v>1.9622</v>
       </c>
       <c r="C18" t="n">
-        <v>0.374</v>
+        <v>0.3541</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2976</v>
+        <v>0.269</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0725</v>
+        <v>1.9622</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4931</v>
+        <v>2.4153</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4206</v>
+        <v>-0.4531</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4931</v>
+        <v>2.5614</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7024</v>
+        <v>2.6951</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4206</v>
+        <v>-0.4531</v>
       </c>
       <c r="K18" t="n">
         <v>384</v>
@@ -1265,7 +1265,7 @@
         <v>29</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2818</v>
+        <v>2.242</v>
       </c>
       <c r="N18" t="n">
         <v>413</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0025</v>
+        <v>1.8024</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3614</v>
+        <v>0.3253</v>
       </c>
       <c r="D19" t="n">
-        <v>0.266</v>
+        <v>0.1963</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0025</v>
+        <v>1.8024</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0025</v>
+        <v>1.8024</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0025</v>
+        <v>1.8024</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0025</v>
+        <v>1.8024</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.0025</v>
+        <v>1.8024</v>
       </c>
       <c r="N19" t="n">
         <v>236</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7858</v>
+        <v>1.6931</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3223</v>
+        <v>0.3056</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1682</v>
+        <v>0.1465</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7858</v>
+        <v>1.6931</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7858</v>
+        <v>1.6931</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7858</v>
+        <v>1.6931</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7858</v>
+        <v>1.6931</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7858</v>
+        <v>1.6931</v>
       </c>
       <c r="N20" t="n">
         <v>237</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6804</v>
+        <v>1.643</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3033</v>
+        <v>0.2965</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1206</v>
+        <v>0.1237</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6804</v>
+        <v>1.643</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6804</v>
+        <v>-0.0048</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1.6478</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6804</v>
+        <v>-0.0048</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6804</v>
+        <v>-0.0048</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.6478</v>
       </c>
       <c r="K21" t="n">
-        <v>237</v>
+        <v>316</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6804</v>
+        <v>1.643</v>
       </c>
       <c r="N21" t="n">
-        <v>237</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6667</v>
+        <v>1.5939</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3008</v>
+        <v>0.2877</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1144</v>
+        <v>0.1014</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6667</v>
+        <v>1.5939</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8584</v>
+        <v>1.7399</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1917</v>
+        <v>-0.146</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8584</v>
+        <v>1.7399</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8584</v>
+        <v>1.7399</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1917</v>
+        <v>-0.146</v>
       </c>
       <c r="K22" t="n">
         <v>316</v>
@@ -1449,7 +1449,7 @@
         <v>29</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6667</v>
+        <v>1.5939</v>
       </c>
       <c r="N22" t="n">
         <v>345</v>
@@ -1458,124 +1458,124 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.5796</v>
+        <v>1.5484</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2851</v>
+        <v>0.2794</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0751</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5796</v>
+        <v>1.5484</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0108</v>
+        <v>1.5484</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5688</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0108</v>
+        <v>1.5484</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0108</v>
+        <v>1.5484</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5688</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>316</v>
+        <v>237</v>
       </c>
       <c r="L23" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5796</v>
+        <v>1.5484</v>
       </c>
       <c r="N23" t="n">
-        <v>345</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4122</v>
+        <v>1.3364</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2549</v>
+        <v>0.2412</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0005</v>
+        <v>-0.0158</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4122</v>
+        <v>1.3364</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4122</v>
+        <v>1.6415</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.3051</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4122</v>
+        <v>1.6415</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4122</v>
+        <v>1.7272</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.3051</v>
       </c>
       <c r="K24" t="n">
-        <v>296</v>
+        <v>384</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4122</v>
+        <v>1.4221</v>
       </c>
       <c r="N24" t="n">
-        <v>296</v>
+        <v>413</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3978</v>
+        <v>1.3073</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2523</v>
+        <v>0.2359</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.007</v>
+        <v>-0.0291</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3978</v>
+        <v>1.3073</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3978</v>
+        <v>1.3073</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3978</v>
+        <v>1.3073</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3978</v>
+        <v>1.3073</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3978</v>
+        <v>1.3073</v>
       </c>
       <c r="N25" t="n">
         <v>296</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3137</v>
+        <v>1.303</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2371</v>
+        <v>0.2352</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0449</v>
+        <v>-0.0311</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3137</v>
+        <v>1.303</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3137</v>
+        <v>1.303</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3137</v>
+        <v>1.303</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3137</v>
+        <v>1.303</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>236</v>
+        <v>296</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3137</v>
+        <v>1.303</v>
       </c>
       <c r="N26" t="n">
-        <v>236</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2064</v>
+        <v>1.1699</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2177</v>
+        <v>0.2111</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0934</v>
+        <v>-0.0916</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2064</v>
+        <v>1.1699</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4834</v>
+        <v>1.1699</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.277</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4834</v>
+        <v>1.1699</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6079</v>
+        <v>1.1699</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.277</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>384</v>
+        <v>236</v>
       </c>
       <c r="L27" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3309</v>
+        <v>1.1699</v>
       </c>
       <c r="N27" t="n">
-        <v>413</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.0321</v>
+        <v>1.0211</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1863</v>
+        <v>0.1843</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1721</v>
+        <v>-0.1594</v>
       </c>
       <c r="E28" t="n">
-        <v>1.0321</v>
+        <v>1.0211</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0321</v>
+        <v>1.0211</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0321</v>
+        <v>1.0211</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0321</v>
+        <v>1.0211</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.0321</v>
+        <v>1.0211</v>
       </c>
       <c r="N28" t="n">
         <v>237</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9889</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1785</v>
+        <v>0.1707</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1916</v>
+        <v>-0.1935</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9889</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9889</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9889</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9889</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9889</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>318</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4853</v>
+        <v>0.4162</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0876</v>
+        <v>0.0751</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4189</v>
+        <v>-0.4347</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4853</v>
+        <v>0.4162</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4853</v>
+        <v>0.4162</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4853</v>
+        <v>0.4162</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4853</v>
+        <v>0.4162</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4853</v>
+        <v>0.4162</v>
       </c>
       <c r="N30" t="n">
         <v>237</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1399</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0252</v>
+        <v>0.0119</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5749</v>
+        <v>-0.5941</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1399</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1399</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1399</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1399</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1399</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>296</v>
@@ -1872,32 +1872,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>Jonji</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0849</v>
+        <v>0.0469</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0153</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5997</v>
+        <v>-0.6029</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0849</v>
+        <v>0.0469</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0849</v>
+        <v>0.0469</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0849</v>
+        <v>0.0469</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0849</v>
+        <v>0.0469</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0849</v>
+        <v>0.0469</v>
       </c>
       <c r="N32" t="n">
         <v>217</v>
@@ -1918,32 +1918,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jonji</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0148</v>
+        <v>0.0011</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.601</v>
+        <v>-0.6214</v>
       </c>
       <c r="E33" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="F33" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="I33" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="N33" t="n">
         <v>217</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.0368</v>
+        <v>-0.1173</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0066</v>
+        <v>-0.0212</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6546</v>
+        <v>-0.6776</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0368</v>
+        <v>-0.1173</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0368</v>
+        <v>-0.1173</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.0368</v>
+        <v>-0.1173</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0368</v>
+        <v>-0.1173</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.0368</v>
+        <v>-0.1173</v>
       </c>
       <c r="N34" t="n">
         <v>217</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0835</v>
+        <v>-0.1719</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0151</v>
+        <v>-0.031</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6757</v>
+        <v>-0.7025</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0835</v>
+        <v>-0.1719</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.0835</v>
+        <v>-0.1719</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.0835</v>
+        <v>-0.1719</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0835</v>
+        <v>-0.1719</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0835</v>
+        <v>-0.1719</v>
       </c>
       <c r="N35" t="n">
         <v>236</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.1469</v>
+        <v>-0.2207</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0265</v>
+        <v>-0.0398</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7043</v>
+        <v>-0.7247</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.1469</v>
+        <v>-0.2207</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.1469</v>
+        <v>-0.2207</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.1469</v>
+        <v>-0.2207</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1469</v>
+        <v>-0.2207</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.1469</v>
+        <v>-0.2207</v>
       </c>
       <c r="N36" t="n">
         <v>236</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.2131</v>
+        <v>-0.2926</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0385</v>
+        <v>-0.0528</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7342</v>
+        <v>-0.7574</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.2131</v>
+        <v>-0.2926</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.2131</v>
+        <v>-0.2926</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2131</v>
+        <v>-0.2926</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2131</v>
+        <v>-0.2926</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.2131</v>
+        <v>-0.2926</v>
       </c>
       <c r="N37" t="n">
         <v>296</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.864</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1559</v>
+        <v>-0.1784</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0281</v>
+        <v>-1.0741</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.864</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.864</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.864</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.864</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.864</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9559</v>
+        <v>-1.0233</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1725</v>
+        <v>-0.1847</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0696</v>
+        <v>-1.09</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9559</v>
+        <v>-1.0233</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9559</v>
+        <v>-1.0233</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9559</v>
+        <v>-1.0233</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9559</v>
+        <v>-1.0233</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9559</v>
+        <v>-1.0233</v>
       </c>
       <c r="N39" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7135</v>
+        <v>-1.7312</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3092</v>
+        <v>-0.3124</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4116</v>
+        <v>-1.4123</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7135</v>
+        <v>-1.7312</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7135</v>
+        <v>-1.7312</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7135</v>
+        <v>-1.7312</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7135</v>
+        <v>-1.7312</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7135</v>
+        <v>-1.7312</v>
       </c>
       <c r="N40" t="n">
         <v>216</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4364</v>
+        <v>-2.4425</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4397</v>
+        <v>-0.4408</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7379</v>
+        <v>-1.7361</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4364</v>
+        <v>-2.4425</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.4364</v>
+        <v>-2.4425</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.4364</v>
+        <v>-2.4425</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4364</v>
+        <v>-2.4425</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4364</v>
+        <v>-2.4425</v>
       </c>
       <c r="N41" t="n">
         <v>217</v>
@@ -2429,10 +2429,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9002</v>
+        <v>0.8438</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9002</v>
+        <v>0.8438</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6653</v>
+        <v>0.6373</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6653</v>
+        <v>0.6373</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.21</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5928</v>
+        <v>0.5727</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5928</v>
+        <v>0.5727</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2847</v>
+        <v>0.2912</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2847</v>
+        <v>0.2912</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.89</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4205</v>
+        <v>-0.3983</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4205</v>
+        <v>-0.3983</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.08</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2321</v>
+        <v>0.2322</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2321</v>
+        <v>0.2322</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.98</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0269</v>
+        <v>-0.0358</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0269</v>
+        <v>-0.0358</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1141</v>
+        <v>-0.1286</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1141</v>
+        <v>-0.1286</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1458</v>
+        <v>-0.1613</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1458</v>
+        <v>-0.1613</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.68</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3439</v>
+        <v>-0.3572</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3439</v>
+        <v>-0.3572</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.66</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2959</v>
+        <v>1.3736</v>
       </c>
       <c r="J12" t="n">
-        <v>36.2852</v>
+        <v>38.4608</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.65</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2841</v>
+        <v>1.3566</v>
       </c>
       <c r="J13" t="n">
-        <v>35.9548</v>
+        <v>37.9848</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.35</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8671</v>
+        <v>0.825</v>
       </c>
       <c r="J14" t="n">
-        <v>24.2788</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.594</v>
+        <v>0.5835</v>
       </c>
       <c r="J15" t="n">
-        <v>16.632</v>
+        <v>16.338</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2288</v>
+        <v>0.2523</v>
       </c>
       <c r="J16" t="n">
-        <v>6.4064</v>
+        <v>7.0644</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4457</v>
+        <v>0.4203</v>
       </c>
       <c r="J17" t="n">
-        <v>12.4796</v>
+        <v>11.7684</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.76</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2501</v>
+        <v>-0.2693</v>
       </c>
       <c r="J18" t="n">
-        <v>-7.0028</v>
+        <v>-7.5404</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.7</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3065</v>
+        <v>-0.3245</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.582000000000001</v>
+        <v>-9.086</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.316</v>
+        <v>-0.3336</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.848000000000001</v>
+        <v>-9.3408</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4379</v>
+        <v>-0.4501</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.2612</v>
+        <v>-12.6028</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.38</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7418</v>
+        <v>0.7119</v>
       </c>
       <c r="J22" t="n">
-        <v>26.7048</v>
+        <v>25.6284</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0343</v>
+        <v>0.0409</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2348</v>
+        <v>1.4724</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.95</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0789</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.8404</v>
+        <v>-3.1824</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.93</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1032</v>
+        <v>-0.114</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.7152</v>
+        <v>-4.104</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1595</v>
+        <v>-0.1719</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.742</v>
+        <v>-6.1884</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5774</v>
+        <v>1.5594</v>
       </c>
       <c r="J27" t="n">
-        <v>56.7864</v>
+        <v>56.1384</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.97</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.157</v>
+        <v>-0.1541</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.652</v>
+        <v>-5.5476</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.95</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2253</v>
+        <v>-0.2197</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.110799999999999</v>
+        <v>-7.9092</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3491</v>
+        <v>-0.3355</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.5676</v>
+        <v>-12.078</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4634</v>
+        <v>-0.4402</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.6824</v>
+        <v>-15.8472</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.21</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5697</v>
+        <v>0.534</v>
       </c>
       <c r="J32" t="n">
-        <v>11.9637</v>
+        <v>11.214</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.75</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2592</v>
+        <v>-0.2783</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.4432</v>
+        <v>-5.8443</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.74</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2686</v>
+        <v>-0.2875</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.6406</v>
+        <v>-6.0375</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.64</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3628</v>
+        <v>-0.3787</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.6188</v>
+        <v>-7.9527</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.51</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4841</v>
+        <v>-0.4936</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.1661</v>
+        <v>-10.3656</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.62</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2504</v>
+        <v>1.2284</v>
       </c>
       <c r="J37" t="n">
-        <v>26.2584</v>
+        <v>25.7964</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.57</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1906</v>
+        <v>1.1643</v>
       </c>
       <c r="J38" t="n">
-        <v>25.0026</v>
+        <v>24.4503</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.34</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8472</v>
+        <v>0.8072</v>
       </c>
       <c r="J39" t="n">
-        <v>17.7912</v>
+        <v>16.9512</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.28</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7133</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>14.9793</v>
+        <v>14.469</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.12</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3155</v>
+        <v>0.3317</v>
       </c>
       <c r="J41" t="n">
-        <v>6.6255</v>
+        <v>6.9657</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.97</v>
       </c>
       <c r="I42" t="n">
-        <v>1.6565</v>
+        <v>1.6572</v>
       </c>
       <c r="J42" t="n">
-        <v>33.13</v>
+        <v>33.144</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.71</v>
       </c>
       <c r="I43" t="n">
-        <v>1.3561</v>
+        <v>1.3411</v>
       </c>
       <c r="J43" t="n">
-        <v>27.122</v>
+        <v>26.822</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7579</v>
+        <v>0.7287</v>
       </c>
       <c r="J44" t="n">
-        <v>15.158</v>
+        <v>14.574</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.02</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0031</v>
+        <v>0.0366</v>
       </c>
       <c r="J45" t="n">
-        <v>0.062</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.95</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2941</v>
+        <v>-0.268</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.882</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.95</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0402</v>
+        <v>-0.0585</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.804</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.75</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.258</v>
+        <v>-0.2774</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.16</v>
+        <v>-5.548</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.71</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2952</v>
+        <v>-0.3138</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.904</v>
+        <v>-6.276</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3046</v>
+        <v>-0.3229</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.092</v>
+        <v>-6.458</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3234</v>
+        <v>-0.3411</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.468</v>
+        <v>-6.822</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1548</v>
+        <v>1.1112</v>
       </c>
       <c r="J52" t="n">
-        <v>32.3344</v>
+        <v>31.1136</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3298</v>
+        <v>0.3288</v>
       </c>
       <c r="J53" t="n">
-        <v>9.234400000000001</v>
+        <v>9.2064</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.03</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1179</v>
+        <v>0.1273</v>
       </c>
       <c r="J54" t="n">
-        <v>3.3012</v>
+        <v>3.5644</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3672</v>
+        <v>-0.3547</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.2816</v>
+        <v>-9.9316</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6138</v>
+        <v>-0.5774</v>
       </c>
       <c r="J56" t="n">
-        <v>-17.1864</v>
+        <v>-16.1672</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.62</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0691</v>
+        <v>1.0337</v>
       </c>
       <c r="J57" t="n">
-        <v>29.9348</v>
+        <v>28.9436</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.29</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5803</v>
+        <v>0.5673</v>
       </c>
       <c r="J58" t="n">
-        <v>16.2484</v>
+        <v>15.8844</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.84</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2047</v>
+        <v>-0.2169</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.7316</v>
+        <v>-6.0732</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2453</v>
+        <v>-0.2574</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.8684</v>
+        <v>-7.2072</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3138</v>
+        <v>-0.3247</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.7864</v>
+        <v>-9.0916</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.3</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6901</v>
+        <v>0.6513</v>
       </c>
       <c r="J62" t="n">
-        <v>18.6327</v>
+        <v>17.5851</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.92</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0963</v>
+        <v>-0.1119</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.6001</v>
+        <v>-3.0213</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.76</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2598</v>
+        <v>-0.2768</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.0146</v>
+        <v>-7.4736</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.66</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3555</v>
+        <v>-0.3696</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.5985</v>
+        <v>-9.979200000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.61</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4023</v>
+        <v>-0.4145</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.8621</v>
+        <v>-11.1915</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2421</v>
+        <v>1.2143</v>
       </c>
       <c r="J67" t="n">
-        <v>33.5367</v>
+        <v>32.7861</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.24</v>
       </c>
       <c r="I68" t="n">
-        <v>0.646</v>
+        <v>0.6242</v>
       </c>
       <c r="J68" t="n">
-        <v>17.442</v>
+        <v>16.8534</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.23</v>
       </c>
       <c r="I69" t="n">
-        <v>0.623</v>
+        <v>0.6035</v>
       </c>
       <c r="J69" t="n">
-        <v>16.821</v>
+        <v>16.2945</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.2</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5515</v>
+        <v>0.5394</v>
       </c>
       <c r="J70" t="n">
-        <v>14.8905</v>
+        <v>14.5638</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0614</v>
+        <v>-0.0425</v>
       </c>
       <c r="J71" t="n">
-        <v>-1.6578</v>
+        <v>-1.1475</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.17</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3885</v>
+        <v>0.3859</v>
       </c>
       <c r="J72" t="n">
-        <v>10.101</v>
+        <v>10.0334</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.14</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3309</v>
+        <v>0.3318</v>
       </c>
       <c r="J73" t="n">
-        <v>8.603400000000001</v>
+        <v>8.626799999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0485</v>
+        <v>-0.0571</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.261</v>
+        <v>-1.4846</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.82</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2167</v>
+        <v>-0.2307</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.6342</v>
+        <v>-5.9982</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2269</v>
+        <v>-0.2408</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.8994</v>
+        <v>-6.2608</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.29</v>
       </c>
       <c r="I77" t="n">
-        <v>0.788</v>
+        <v>0.7448</v>
       </c>
       <c r="J77" t="n">
-        <v>20.488</v>
+        <v>19.3648</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.28</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7644</v>
+        <v>0.7241</v>
       </c>
       <c r="J78" t="n">
-        <v>19.8744</v>
+        <v>18.8266</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1983</v>
+        <v>0.2095</v>
       </c>
       <c r="J79" t="n">
-        <v>5.1558</v>
+        <v>5.447</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1337</v>
+        <v>0.1478</v>
       </c>
       <c r="J80" t="n">
-        <v>3.4762</v>
+        <v>3.8428</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.04</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1337</v>
+        <v>0.1478</v>
       </c>
       <c r="J81" t="n">
-        <v>3.4762</v>
+        <v>3.8428</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.69</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3222</v>
+        <v>1.307</v>
       </c>
       <c r="J82" t="n">
-        <v>29.0884</v>
+        <v>28.754</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.66</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2873</v>
+        <v>1.2697</v>
       </c>
       <c r="J83" t="n">
-        <v>28.3206</v>
+        <v>27.9334</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.41</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9785</v>
+        <v>0.9301</v>
       </c>
       <c r="J84" t="n">
-        <v>21.527</v>
+        <v>20.4622</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.37</v>
       </c>
       <c r="I85" t="n">
-        <v>0.9012</v>
+        <v>0.8568</v>
       </c>
       <c r="J85" t="n">
-        <v>19.8264</v>
+        <v>18.8496</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.1</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2469</v>
+        <v>0.2714</v>
       </c>
       <c r="J86" t="n">
-        <v>5.4318</v>
+        <v>5.9708</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.09</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3744</v>
+        <v>0.3421</v>
       </c>
       <c r="J87" t="n">
-        <v>8.236800000000001</v>
+        <v>7.5262</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.66</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.3315</v>
+        <v>-0.351</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.293</v>
+        <v>-7.722</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3498</v>
+        <v>-0.3686</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.6956</v>
+        <v>-8.1092</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.55</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4336</v>
+        <v>-0.4482</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.539199999999999</v>
+        <v>-9.8604</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.49</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4898</v>
+        <v>-0.501</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.7756</v>
+        <v>-11.022</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.56</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2227</v>
+        <v>1.1903</v>
       </c>
       <c r="J92" t="n">
-        <v>36.681</v>
+        <v>35.709</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.16</v>
       </c>
       <c r="I93" t="n">
-        <v>0.466</v>
+        <v>0.4591</v>
       </c>
       <c r="J93" t="n">
-        <v>13.98</v>
+        <v>13.773</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2782</v>
+        <v>0.2868</v>
       </c>
       <c r="J94" t="n">
-        <v>8.346</v>
+        <v>8.603999999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.07</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2193</v>
+        <v>0.2317</v>
       </c>
       <c r="J95" t="n">
-        <v>6.579</v>
+        <v>6.951</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.03</v>
       </c>
       <c r="I96" t="n">
-        <v>0.089</v>
+        <v>0.1073</v>
       </c>
       <c r="J96" t="n">
-        <v>2.67</v>
+        <v>3.219</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.46</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8963</v>
+        <v>0.8468</v>
       </c>
       <c r="J97" t="n">
-        <v>26.889</v>
+        <v>25.404</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.16</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3695</v>
+        <v>0.3681</v>
       </c>
       <c r="J98" t="n">
-        <v>11.085</v>
+        <v>11.043</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1962</v>
+        <v>-0.2103</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.886</v>
+        <v>-6.309</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.77</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2667</v>
+        <v>-0.2801</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.000999999999999</v>
+        <v>-8.403</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3531</v>
+        <v>-0.3644</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.593</v>
+        <v>-10.932</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.88</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.0872</v>
+        <v>-0.1157</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.744</v>
+        <v>-2.314</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.67</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3144</v>
+        <v>-0.3361</v>
       </c>
       <c r="J103" t="n">
-        <v>-6.288</v>
+        <v>-6.722</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.66</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3239</v>
+        <v>-0.3452</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.478</v>
+        <v>-6.904</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.51</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4605</v>
+        <v>-0.4751</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.502000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.41</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5551</v>
+        <v>-0.5631</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.102</v>
+        <v>-11.262</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.7078</v>
       </c>
       <c r="J107" t="n">
-        <v>14.082</v>
+        <v>14.156</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6543</v>
+        <v>0.6612</v>
       </c>
       <c r="J108" t="n">
-        <v>13.086</v>
+        <v>13.224</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.48</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5646</v>
+        <v>0.5766</v>
       </c>
       <c r="J109" t="n">
-        <v>11.292</v>
+        <v>11.532</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.46</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.5578</v>
       </c>
       <c r="J110" t="n">
-        <v>10.898</v>
+        <v>11.156</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.26</v>
       </c>
       <c r="I111" t="n">
-        <v>0.326</v>
+        <v>0.3483</v>
       </c>
       <c r="J111" t="n">
-        <v>6.52</v>
+        <v>6.966</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.42</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0299</v>
+        <v>0.978</v>
       </c>
       <c r="J112" t="n">
-        <v>27.8073</v>
+        <v>26.406</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.41</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0145</v>
+        <v>0.9606</v>
       </c>
       <c r="J113" t="n">
-        <v>27.3915</v>
+        <v>25.9362</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.9208</v>
+        <v>0.8665</v>
       </c>
       <c r="J114" t="n">
-        <v>24.8616</v>
+        <v>23.3955</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.98</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1517</v>
+        <v>-0.1398</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.0959</v>
+        <v>-3.7746</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.97</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.189</v>
+        <v>-0.1764</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.103</v>
+        <v>-4.7628</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.28</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6519</v>
+        <v>0.6171</v>
       </c>
       <c r="J117" t="n">
-        <v>17.6013</v>
+        <v>16.6617</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.85</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1716</v>
+        <v>-0.1889</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.6332</v>
+        <v>-5.1003</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.74</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2794</v>
+        <v>-0.2959</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.5438</v>
+        <v>-7.9893</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.72</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2987</v>
+        <v>-0.3147</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.0649</v>
+        <v>-8.4969</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3463</v>
+        <v>-0.3607</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.350099999999999</v>
+        <v>-9.738899999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1761</v>
+        <v>1.1349</v>
       </c>
       <c r="J122" t="n">
-        <v>35.283</v>
+        <v>34.047</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.28</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7872</v>
+        <v>0.74</v>
       </c>
       <c r="J123" t="n">
-        <v>23.616</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.99</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0725</v>
+        <v>-0.0718</v>
       </c>
       <c r="J124" t="n">
-        <v>-2.175</v>
+        <v>-2.154</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3126</v>
+        <v>-0.3033</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.378</v>
+        <v>-9.099</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.71</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8713</v>
+        <v>-0.8033</v>
       </c>
       <c r="J126" t="n">
-        <v>-26.139</v>
+        <v>-24.099</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.5</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9278</v>
+        <v>0.8806</v>
       </c>
       <c r="J127" t="n">
-        <v>27.834</v>
+        <v>26.418</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.99</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0251</v>
+        <v>-0.0287</v>
       </c>
       <c r="J128" t="n">
-        <v>-0.753</v>
+        <v>-0.861</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.95</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0902</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.436</v>
+        <v>-2.706</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1173</v>
+        <v>-0.128</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.519</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.14</v>
+        <v>-0.1514</v>
       </c>
       <c r="J131" t="n">
-        <v>-4.2</v>
+        <v>-4.542</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.11</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2631</v>
+        <v>0.2693</v>
       </c>
       <c r="J132" t="n">
-        <v>7.893</v>
+        <v>8.079000000000001</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.09</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2226</v>
+        <v>0.2303</v>
       </c>
       <c r="J133" t="n">
-        <v>6.678</v>
+        <v>6.909</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1806</v>
+        <v>0.1895</v>
       </c>
       <c r="J134" t="n">
-        <v>5.418</v>
+        <v>5.685</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0871</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.319</v>
+        <v>-2.613</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1896</v>
+        <v>-0.2027</v>
       </c>
       <c r="J136" t="n">
-        <v>-5.688</v>
+        <v>-6.081</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.34</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9225</v>
+        <v>0.8599</v>
       </c>
       <c r="J137" t="n">
-        <v>27.675</v>
+        <v>25.797</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5082</v>
+        <v>0.4935</v>
       </c>
       <c r="J138" t="n">
-        <v>15.246</v>
+        <v>14.805</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3505</v>
+        <v>0.3496</v>
       </c>
       <c r="J139" t="n">
-        <v>10.515</v>
+        <v>10.488</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.97</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1549</v>
+        <v>-0.1526</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.647</v>
+        <v>-4.578</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.89</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4049</v>
+        <v>-0.3873</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.147</v>
+        <v>-11.619</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9764</v>
+        <v>0.9273</v>
       </c>
       <c r="J142" t="n">
-        <v>24.41</v>
+        <v>23.1825</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.24</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4989</v>
+        <v>0.4916</v>
       </c>
       <c r="J143" t="n">
-        <v>12.4725</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.96</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.067</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.675</v>
+        <v>-1.885</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2333</v>
+        <v>-0.2458</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.8325</v>
+        <v>-6.145</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.65</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3872</v>
+        <v>-0.3962</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.68</v>
+        <v>-9.904999999999999</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.82</v>
       </c>
       <c r="I147" t="n">
-        <v>1.5422</v>
+        <v>1.528</v>
       </c>
       <c r="J147" t="n">
-        <v>38.555</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.07</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2168</v>
+        <v>0.23</v>
       </c>
       <c r="J148" t="n">
-        <v>5.42</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.06</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1861</v>
+        <v>0.201</v>
       </c>
       <c r="J149" t="n">
-        <v>4.6525</v>
+        <v>5.025</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.06</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1861</v>
+        <v>0.201</v>
       </c>
       <c r="J150" t="n">
-        <v>4.6525</v>
+        <v>5.025</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.95</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2484</v>
+        <v>-0.2359</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.21</v>
+        <v>-5.8975</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0639</v>
+        <v>-0.0921</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.1502</v>
+        <v>-1.6578</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1129</v>
+        <v>-0.1407</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.0322</v>
+        <v>-2.5326</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.55</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4238</v>
+        <v>-0.4405</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.6284</v>
+        <v>-7.929</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.48</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4895</v>
+        <v>-0.5021</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.811</v>
+        <v>-9.037800000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.36</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.6075</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.8594</v>
+        <v>-10.935</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.19</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1383</v>
+        <v>1.1453</v>
       </c>
       <c r="J157" t="n">
-        <v>20.4894</v>
+        <v>20.6154</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.62</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6959</v>
+        <v>0.7016</v>
       </c>
       <c r="J158" t="n">
-        <v>12.5262</v>
+        <v>12.6288</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.6</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6766</v>
+        <v>0.6834</v>
       </c>
       <c r="J159" t="n">
-        <v>12.1788</v>
+        <v>12.3012</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.29</v>
       </c>
       <c r="I160" t="n">
-        <v>0.353</v>
+        <v>0.376</v>
       </c>
       <c r="J160" t="n">
-        <v>6.354</v>
+        <v>6.768</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.09</v>
       </c>
       <c r="I161" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1258</v>
       </c>
       <c r="J161" t="n">
-        <v>1.7748</v>
+        <v>2.2644</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.92</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5835</v>
+        <v>1.5834</v>
       </c>
       <c r="J162" t="n">
-        <v>34.837</v>
+        <v>34.8348</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.42</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9939</v>
+        <v>0.9465</v>
       </c>
       <c r="J163" t="n">
-        <v>21.8658</v>
+        <v>20.823</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.35</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8562</v>
+        <v>0.8175</v>
       </c>
       <c r="J164" t="n">
-        <v>18.8364</v>
+        <v>17.985</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.33</v>
       </c>
       <c r="I165" t="n">
-        <v>0.8122</v>
+        <v>0.7789</v>
       </c>
       <c r="J165" t="n">
-        <v>17.8684</v>
+        <v>17.1358</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.26</v>
       </c>
       <c r="I166" t="n">
-        <v>0.6526</v>
+        <v>0.6381</v>
       </c>
       <c r="J166" t="n">
-        <v>14.3572</v>
+        <v>14.0382</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.01</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1562</v>
+        <v>0.1301</v>
       </c>
       <c r="J167" t="n">
-        <v>3.4364</v>
+        <v>2.8622</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.78</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2196</v>
+        <v>-0.2417</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.8312</v>
+        <v>-5.3174</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.6</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3882</v>
+        <v>-0.405</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.5404</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.54</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4443</v>
+        <v>-0.4581</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.7746</v>
+        <v>-10.0782</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.54</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4443</v>
+        <v>-0.4581</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.7746</v>
+        <v>-10.0782</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9266</v>
+        <v>0.8629</v>
       </c>
       <c r="J172" t="n">
-        <v>33.3576</v>
+        <v>31.0644</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.1</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3251</v>
+        <v>0.3256</v>
       </c>
       <c r="J173" t="n">
-        <v>11.7036</v>
+        <v>11.7216</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.08</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2699</v>
+        <v>0.2739</v>
       </c>
       <c r="J174" t="n">
-        <v>9.7164</v>
+        <v>9.8604</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0193</v>
+        <v>-0.0132</v>
       </c>
       <c r="J175" t="n">
-        <v>-0.6948</v>
+        <v>-0.4752</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.91</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3441</v>
+        <v>-0.3321</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.3876</v>
+        <v>-11.9556</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.1</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2382</v>
+        <v>0.2466</v>
       </c>
       <c r="J177" t="n">
-        <v>8.575200000000001</v>
+        <v>8.877599999999999</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1765</v>
+        <v>0.1865</v>
       </c>
       <c r="J178" t="n">
-        <v>6.354</v>
+        <v>6.714</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.03</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0872</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J179" t="n">
-        <v>3.1392</v>
+        <v>3.4812</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0618</v>
+        <v>0.0704</v>
       </c>
       <c r="J180" t="n">
-        <v>2.2248</v>
+        <v>2.5344</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.0668</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.4048</v>
+        <v>-2.7108</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.36</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9392</v>
+        <v>0.8801</v>
       </c>
       <c r="J182" t="n">
-        <v>32.872</v>
+        <v>30.8035</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.35</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9176</v>
+        <v>0.8603</v>
       </c>
       <c r="J183" t="n">
-        <v>32.116</v>
+        <v>30.1105</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6377</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>22.3195</v>
+        <v>21.469</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2088</v>
+        <v>-0.1996</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.308</v>
+        <v>-6.986</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2745</v>
+        <v>-0.262</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.6075</v>
+        <v>-9.17</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.41</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7703</v>
       </c>
       <c r="J187" t="n">
-        <v>28.35</v>
+        <v>26.9605</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.11</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2698</v>
+        <v>0.2742</v>
       </c>
       <c r="J188" t="n">
-        <v>9.443</v>
+        <v>9.597</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.97</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.049</v>
+        <v>-0.0574</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.715</v>
+        <v>-2.009</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.75</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2869</v>
+        <v>-0.2999</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.0415</v>
+        <v>-10.4965</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3349</v>
+        <v>-0.3466</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.7215</v>
+        <v>-12.131</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.94</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5863</v>
+        <v>1.5896</v>
       </c>
       <c r="J192" t="n">
-        <v>30.1397</v>
+        <v>30.2024</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.57</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1702</v>
+        <v>1.1467</v>
       </c>
       <c r="J193" t="n">
-        <v>22.2338</v>
+        <v>21.7873</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.52</v>
       </c>
       <c r="I194" t="n">
-        <v>1.1137</v>
+        <v>1.0852</v>
       </c>
       <c r="J194" t="n">
-        <v>21.1603</v>
+        <v>20.6188</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.38</v>
       </c>
       <c r="I195" t="n">
-        <v>0.9034</v>
+        <v>0.8623</v>
       </c>
       <c r="J195" t="n">
-        <v>17.1646</v>
+        <v>16.3837</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.34</v>
       </c>
       <c r="I196" t="n">
-        <v>0.8161</v>
+        <v>0.7857</v>
       </c>
       <c r="J196" t="n">
-        <v>15.5059</v>
+        <v>14.9283</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.86</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.1084</v>
+        <v>-0.1372</v>
       </c>
       <c r="J197" t="n">
-        <v>-2.0596</v>
+        <v>-2.6068</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.77</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2105</v>
+        <v>-0.2367</v>
       </c>
       <c r="J198" t="n">
-        <v>-3.9995</v>
+        <v>-4.4973</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4123</v>
+        <v>-0.4301</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.8337</v>
+        <v>-8.171900000000001</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.47</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4967</v>
+        <v>-0.5092</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.4373</v>
+        <v>-9.674799999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.43</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5346</v>
+        <v>-0.5444</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.1574</v>
+        <v>-10.3436</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.3</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6705</v>
+        <v>0.6368</v>
       </c>
       <c r="J202" t="n">
-        <v>16.092</v>
+        <v>15.2832</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.99</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0075</v>
+        <v>-0.0153</v>
       </c>
       <c r="J203" t="n">
-        <v>-0.18</v>
+        <v>-0.3672</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.78</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2447</v>
+        <v>-0.261</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.8728</v>
+        <v>-6.264</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.7</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3221</v>
+        <v>-0.3366</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.7304</v>
+        <v>-8.0784</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3694</v>
+        <v>-0.3822</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.865600000000001</v>
+        <v>-9.172800000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.44</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0502</v>
+        <v>1.0037</v>
       </c>
       <c r="J207" t="n">
-        <v>25.2048</v>
+        <v>24.0888</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.44</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0502</v>
+        <v>1.0037</v>
       </c>
       <c r="J208" t="n">
-        <v>25.2048</v>
+        <v>24.0888</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.29</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7557</v>
+        <v>0.7226</v>
       </c>
       <c r="J209" t="n">
-        <v>18.1368</v>
+        <v>17.3424</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.23</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.6018</v>
       </c>
       <c r="J210" t="n">
-        <v>14.892</v>
+        <v>14.4432</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.33</v>
+        <v>-0.3084</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.92</v>
+        <v>-7.4016</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.9</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9849</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="J212" t="n">
-        <v>21.6678</v>
+        <v>21.3246</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.51</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6025</v>
+        <v>0.6109</v>
       </c>
       <c r="J213" t="n">
-        <v>13.255</v>
+        <v>13.4398</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.45</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5404</v>
+        <v>0.5523</v>
       </c>
       <c r="J214" t="n">
-        <v>11.8888</v>
+        <v>12.1506</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.06</v>
       </c>
       <c r="I215" t="n">
-        <v>0.0697</v>
+        <v>0.0921</v>
       </c>
       <c r="J215" t="n">
-        <v>1.5334</v>
+        <v>2.0262</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.06</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0697</v>
+        <v>0.0921</v>
       </c>
       <c r="J216" t="n">
-        <v>1.5334</v>
+        <v>2.0262</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.01</v>
       </c>
       <c r="I217" t="n">
-        <v>0.0975</v>
+        <v>0.0853</v>
       </c>
       <c r="J217" t="n">
-        <v>2.145</v>
+        <v>1.8766</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.77</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2376</v>
+        <v>-0.2577</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.2272</v>
+        <v>-5.6694</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3114</v>
+        <v>-0.3301</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.8508</v>
+        <v>-7.2622</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3114</v>
+        <v>-0.3301</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.8508</v>
+        <v>-7.2622</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.54</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4517</v>
+        <v>-0.4639</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.9374</v>
+        <v>-10.2058</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.32</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6479</v>
+        <v>0.6259</v>
       </c>
       <c r="J222" t="n">
-        <v>18.7891</v>
+        <v>18.1511</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.12</v>
       </c>
       <c r="I223" t="n">
-        <v>0.284</v>
+        <v>0.289</v>
       </c>
       <c r="J223" t="n">
-        <v>8.236000000000001</v>
+        <v>8.381</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.03</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0902</v>
+        <v>0.0988</v>
       </c>
       <c r="J224" t="n">
-        <v>2.6158</v>
+        <v>2.8652</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.92</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1127</v>
+        <v>-0.1245</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.2683</v>
+        <v>-3.6105</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3749</v>
+        <v>-0.3849</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.8721</v>
+        <v>-11.1621</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.25</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7148</v>
+        <v>0.6763</v>
       </c>
       <c r="J227" t="n">
-        <v>20.7292</v>
+        <v>19.6127</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.2</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5659</v>
       </c>
       <c r="J228" t="n">
-        <v>17.1158</v>
+        <v>16.4111</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.14</v>
       </c>
       <c r="I229" t="n">
-        <v>0.435</v>
+        <v>0.4261</v>
       </c>
       <c r="J229" t="n">
-        <v>12.615</v>
+        <v>12.3569</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.93</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2816</v>
+        <v>-0.2745</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.166399999999999</v>
+        <v>-7.9605</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.87</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4562</v>
+        <v>-0.4351</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.2298</v>
+        <v>-12.6179</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.56</v>
       </c>
       <c r="I232" t="n">
-        <v>1.221</v>
+        <v>1.1888</v>
       </c>
       <c r="J232" t="n">
-        <v>36.63</v>
+        <v>35.664</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5617</v>
+        <v>0.5462</v>
       </c>
       <c r="J233" t="n">
-        <v>16.851</v>
+        <v>16.386</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.14</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4136</v>
+        <v>0.4117</v>
       </c>
       <c r="J234" t="n">
-        <v>12.408</v>
+        <v>12.351</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.06</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1871</v>
+        <v>0.2017</v>
       </c>
       <c r="J235" t="n">
-        <v>5.613</v>
+        <v>6.051</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.98</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1417</v>
+        <v>-0.1327</v>
       </c>
       <c r="J236" t="n">
-        <v>-4.251</v>
+        <v>-3.981</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.24</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5317</v>
+        <v>0.5157</v>
       </c>
       <c r="J237" t="n">
-        <v>15.951</v>
+        <v>15.471</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2615</v>
+        <v>0.2635</v>
       </c>
       <c r="J238" t="n">
-        <v>7.845</v>
+        <v>7.905</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0832</v>
+        <v>-0.0953</v>
       </c>
       <c r="J239" t="n">
-        <v>-2.496</v>
+        <v>-2.859</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2326</v>
+        <v>-0.2474</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.978</v>
+        <v>-7.422</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.65</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3771</v>
+        <v>-0.3882</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.313</v>
+        <v>-11.646</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.54</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1647</v>
+        <v>1.1344</v>
       </c>
       <c r="J242" t="n">
-        <v>27.9528</v>
+        <v>27.2256</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.47</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0782</v>
+        <v>1.0394</v>
       </c>
       <c r="J243" t="n">
-        <v>25.8768</v>
+        <v>24.9456</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.32</v>
       </c>
       <c r="I244" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.7752</v>
       </c>
       <c r="J244" t="n">
-        <v>19.512</v>
+        <v>18.6048</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.21</v>
       </c>
       <c r="I245" t="n">
-        <v>0.5605</v>
+        <v>0.5506</v>
       </c>
       <c r="J245" t="n">
-        <v>13.452</v>
+        <v>13.2144</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.09</v>
       </c>
       <c r="I246" t="n">
-        <v>0.2444</v>
+        <v>0.2632</v>
       </c>
       <c r="J246" t="n">
-        <v>5.8656</v>
+        <v>6.3168</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.86</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1492</v>
+        <v>-0.1692</v>
       </c>
       <c r="J247" t="n">
-        <v>-3.5808</v>
+        <v>-4.0608</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.83</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1812</v>
+        <v>-0.2011</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.3488</v>
+        <v>-4.8264</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.79</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2215</v>
+        <v>-0.2411</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.316</v>
+        <v>-5.7864</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.76</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2494</v>
+        <v>-0.2688</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.9856</v>
+        <v>-6.4512</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.58</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4181</v>
+        <v>-0.4315</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.0344</v>
+        <v>-10.356</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.13</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3467</v>
+        <v>0.3393</v>
       </c>
       <c r="J252" t="n">
-        <v>10.0543</v>
+        <v>9.839700000000001</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.01</v>
       </c>
       <c r="I253" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="J253" t="n">
-        <v>1.9024</v>
+        <v>1.8386</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.96</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0515</v>
+        <v>-0.0636</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.4935</v>
+        <v>-1.8444</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.78</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2444</v>
+        <v>-0.2608</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.0876</v>
+        <v>-7.5632</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.53</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4801</v>
+        <v>-0.4877</v>
       </c>
       <c r="J256" t="n">
-        <v>-13.9229</v>
+        <v>-14.1433</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.33</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8915</v>
+        <v>0.8336</v>
       </c>
       <c r="J257" t="n">
-        <v>25.8535</v>
+        <v>24.1744</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.32</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8681</v>
+        <v>0.8132</v>
       </c>
       <c r="J258" t="n">
-        <v>25.1749</v>
+        <v>23.5828</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1055</v>
+        <v>0.1188</v>
       </c>
       <c r="J259" t="n">
-        <v>3.0595</v>
+        <v>3.4452</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.97</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1602</v>
+        <v>-0.1563</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.6458</v>
+        <v>-4.5327</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.93</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.292</v>
+        <v>-0.2818</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.468</v>
+        <v>-8.1722</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.67</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8219</v>
+        <v>0.8062</v>
       </c>
       <c r="J262" t="n">
-        <v>23.8351</v>
+        <v>23.3798</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.24</v>
       </c>
       <c r="I263" t="n">
-        <v>0.336</v>
+        <v>0.3507</v>
       </c>
       <c r="J263" t="n">
-        <v>9.744</v>
+        <v>10.1703</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.09</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1443</v>
+        <v>0.1606</v>
       </c>
       <c r="J264" t="n">
-        <v>4.1847</v>
+        <v>4.6574</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.06</v>
       </c>
       <c r="I265" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.1147</v>
       </c>
       <c r="J265" t="n">
-        <v>2.8855</v>
+        <v>3.3263</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.66</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.388</v>
+        <v>-0.3952</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.252</v>
+        <v>-11.4608</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.11</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2073</v>
+        <v>0.2154</v>
       </c>
       <c r="J267" t="n">
-        <v>6.0117</v>
+        <v>6.2466</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.07</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1433</v>
+        <v>0.1522</v>
       </c>
       <c r="J268" t="n">
-        <v>4.1557</v>
+        <v>4.4138</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.01</v>
       </c>
       <c r="I269" t="n">
-        <v>0.0307</v>
+        <v>0.0353</v>
       </c>
       <c r="J269" t="n">
-        <v>0.8903</v>
+        <v>1.0237</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.97</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0487</v>
+        <v>-0.0572</v>
       </c>
       <c r="J270" t="n">
-        <v>-1.4123</v>
+        <v>-1.6588</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.76</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2767</v>
+        <v>-0.2899</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.0243</v>
+        <v>-8.4071</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.29</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6166</v>
+        <v>0.594</v>
       </c>
       <c r="J272" t="n">
-        <v>17.2648</v>
+        <v>16.632</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.09</v>
       </c>
       <c r="I273" t="n">
-        <v>0.237</v>
+        <v>0.2408</v>
       </c>
       <c r="J273" t="n">
-        <v>6.636</v>
+        <v>6.7424</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.97</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.047</v>
+        <v>-0.056</v>
       </c>
       <c r="J274" t="n">
-        <v>-1.316</v>
+        <v>-1.568</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.224</v>
+        <v>-0.2386</v>
       </c>
       <c r="J275" t="n">
-        <v>-6.272</v>
+        <v>-6.6808</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.63</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3971</v>
+        <v>-0.4072</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.1188</v>
+        <v>-11.4016</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.42</v>
       </c>
       <c r="I277" t="n">
-        <v>1.0495</v>
+        <v>0.9969</v>
       </c>
       <c r="J277" t="n">
-        <v>29.386</v>
+        <v>27.9132</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.32</v>
       </c>
       <c r="I278" t="n">
-        <v>0.8562</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="J278" t="n">
-        <v>23.9736</v>
+        <v>22.5372</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.04</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1322</v>
+        <v>0.1468</v>
       </c>
       <c r="J279" t="n">
-        <v>3.7016</v>
+        <v>4.1104</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.03</v>
       </c>
       <c r="I280" t="n">
-        <v>0.0975</v>
+        <v>0.1132</v>
       </c>
       <c r="J280" t="n">
-        <v>2.73</v>
+        <v>3.1696</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.93</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3005</v>
+        <v>-0.2877</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.414</v>
+        <v>-8.0556</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.47</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1029</v>
+        <v>1.0623</v>
       </c>
       <c r="J282" t="n">
-        <v>29.7783</v>
+        <v>28.6821</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9073</v>
+        <v>0.8528</v>
       </c>
       <c r="J283" t="n">
-        <v>24.4971</v>
+        <v>23.0256</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.32</v>
       </c>
       <c r="I284" t="n">
-        <v>0.8394</v>
+        <v>0.7932</v>
       </c>
       <c r="J284" t="n">
-        <v>22.6638</v>
+        <v>21.4164</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.98</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1447</v>
+        <v>-0.1349</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.9069</v>
+        <v>-3.6423</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.88</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4605</v>
+        <v>-0.4323</v>
       </c>
       <c r="J286" t="n">
-        <v>-12.4335</v>
+        <v>-11.6721</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.17</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4224</v>
+        <v>0.4108</v>
       </c>
       <c r="J287" t="n">
-        <v>11.4048</v>
+        <v>11.0916</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.14</v>
       </c>
       <c r="I288" t="n">
-        <v>0.3629</v>
+        <v>0.3552</v>
       </c>
       <c r="J288" t="n">
-        <v>9.798299999999999</v>
+        <v>9.590400000000001</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.84</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1856</v>
+        <v>-0.2021</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.0112</v>
+        <v>-5.4567</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.7</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3231</v>
+        <v>-0.3374</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.723699999999999</v>
+        <v>-9.1098</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.61</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4077</v>
+        <v>-0.4187</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.0079</v>
+        <v>-11.3049</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.44</v>
       </c>
       <c r="I292" t="n">
-        <v>0.6504</v>
+        <v>0.6324</v>
       </c>
       <c r="J292" t="n">
-        <v>23.4144</v>
+        <v>22.7664</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.16</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2764</v>
+        <v>0.2835</v>
       </c>
       <c r="J293" t="n">
-        <v>9.9504</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.12</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2173</v>
+        <v>0.2264</v>
       </c>
       <c r="J294" t="n">
-        <v>7.8228</v>
+        <v>8.150399999999999</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.76</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2797</v>
+        <v>-0.2923</v>
       </c>
       <c r="J295" t="n">
-        <v>-10.0692</v>
+        <v>-10.5228</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.57</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4575</v>
+        <v>-0.4641</v>
       </c>
       <c r="J296" t="n">
-        <v>-16.47</v>
+        <v>-16.7076</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.61</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7595</v>
       </c>
       <c r="J297" t="n">
-        <v>27.8532</v>
+        <v>27.342</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.08</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1356</v>
+        <v>0.1501</v>
       </c>
       <c r="J298" t="n">
-        <v>4.8816</v>
+        <v>5.4036</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.96</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0722</v>
+        <v>-0.0794</v>
       </c>
       <c r="J299" t="n">
-        <v>-2.5992</v>
+        <v>-2.8584</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0974</v>
+        <v>-0.1062</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.5064</v>
+        <v>-3.8232</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.85</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.1978</v>
+        <v>-0.2091</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.1208</v>
+        <v>-7.5276</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.65</v>
       </c>
       <c r="I302" t="n">
-        <v>1.3237</v>
+        <v>1.2997</v>
       </c>
       <c r="J302" t="n">
-        <v>31.7688</v>
+        <v>31.1928</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.13</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3793</v>
+        <v>0.3821</v>
       </c>
       <c r="J303" t="n">
-        <v>9.103199999999999</v>
+        <v>9.170400000000001</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.12</v>
       </c>
       <c r="I304" t="n">
-        <v>0.3523</v>
+        <v>0.3574</v>
       </c>
       <c r="J304" t="n">
-        <v>8.4552</v>
+        <v>8.5776</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.12</v>
       </c>
       <c r="I305" t="n">
-        <v>0.3523</v>
+        <v>0.3574</v>
       </c>
       <c r="J305" t="n">
-        <v>8.4552</v>
+        <v>8.5776</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.1</v>
       </c>
       <c r="I306" t="n">
-        <v>0.2969</v>
+        <v>0.3063</v>
       </c>
       <c r="J306" t="n">
-        <v>7.1256</v>
+        <v>7.3512</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.19</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4806</v>
+        <v>0.461</v>
       </c>
       <c r="J307" t="n">
-        <v>11.5344</v>
+        <v>11.064</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.93</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0848</v>
+        <v>-0.0999</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.0352</v>
+        <v>-2.3976</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.9</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1195</v>
+        <v>-0.1357</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.868</v>
+        <v>-3.2568</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.67</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3463</v>
+        <v>-0.3607</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.311199999999999</v>
+        <v>-8.6568</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.57</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4397</v>
+        <v>-0.45</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.5528</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.36</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9302</v>
+        <v>0.8734</v>
       </c>
       <c r="J312" t="n">
-        <v>25.1154</v>
+        <v>23.5818</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.3</v>
       </c>
       <c r="I313" t="n">
-        <v>0.7946</v>
+        <v>0.7537</v>
       </c>
       <c r="J313" t="n">
-        <v>21.4542</v>
+        <v>20.3499</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.24</v>
       </c>
       <c r="I314" t="n">
-        <v>0.6549</v>
+        <v>0.6301</v>
       </c>
       <c r="J314" t="n">
-        <v>17.6823</v>
+        <v>17.0127</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.13</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3856</v>
+        <v>0.3864</v>
       </c>
       <c r="J315" t="n">
-        <v>10.4112</v>
+        <v>10.4328</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.95</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2494</v>
+        <v>-0.2366</v>
       </c>
       <c r="J316" t="n">
-        <v>-6.7338</v>
+        <v>-6.3882</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.17</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3918</v>
+        <v>0.3883</v>
       </c>
       <c r="J317" t="n">
-        <v>10.5786</v>
+        <v>10.4841</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.16</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3727</v>
+        <v>0.3704</v>
       </c>
       <c r="J318" t="n">
-        <v>10.0629</v>
+        <v>10.0008</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0733</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.9791</v>
+        <v>-2.2707</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.91</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.12</v>
+        <v>-0.1331</v>
       </c>
       <c r="J320" t="n">
-        <v>-3.24</v>
+        <v>-3.5937</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.67</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3614</v>
+        <v>-0.3725</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.7578</v>
+        <v>-10.0575</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.44</v>
       </c>
       <c r="I322" t="n">
-        <v>1.0682</v>
+        <v>1.0212</v>
       </c>
       <c r="J322" t="n">
-        <v>28.8414</v>
+        <v>27.5724</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.33</v>
       </c>
       <c r="I323" t="n">
-        <v>0.8678</v>
+        <v>0.8171</v>
       </c>
       <c r="J323" t="n">
-        <v>23.4306</v>
+        <v>22.0617</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.25</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6818</v>
+        <v>0.6533</v>
       </c>
       <c r="J324" t="n">
-        <v>18.4086</v>
+        <v>17.6391</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.17</v>
       </c>
       <c r="I325" t="n">
-        <v>0.4909</v>
+        <v>0.4817</v>
       </c>
       <c r="J325" t="n">
-        <v>13.2543</v>
+        <v>13.0059</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.72</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.8718</v>
+        <v>-0.7995</v>
       </c>
       <c r="J326" t="n">
-        <v>-23.5386</v>
+        <v>-21.5865</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.31</v>
       </c>
       <c r="I327" t="n">
-        <v>0.6493</v>
+        <v>0.6241</v>
       </c>
       <c r="J327" t="n">
-        <v>17.5311</v>
+        <v>16.8507</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.09</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2353</v>
+        <v>0.2395</v>
       </c>
       <c r="J328" t="n">
-        <v>6.3531</v>
+        <v>6.4665</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.97</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0475</v>
+        <v>-0.0563</v>
       </c>
       <c r="J329" t="n">
-        <v>-1.2825</v>
+        <v>-1.5201</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.92</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1079</v>
+        <v>-0.1207</v>
       </c>
       <c r="J330" t="n">
-        <v>-2.9133</v>
+        <v>-3.2589</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.53</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4891</v>
+        <v>-0.4948</v>
       </c>
       <c r="J331" t="n">
-        <v>-13.2057</v>
+        <v>-13.3596</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.65</v>
       </c>
       <c r="I332" t="n">
-        <v>1.3052</v>
+        <v>1.2833</v>
       </c>
       <c r="J332" t="n">
-        <v>36.5456</v>
+        <v>35.9324</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.53</v>
       </c>
       <c r="I333" t="n">
-        <v>1.1581</v>
+        <v>1.1262</v>
       </c>
       <c r="J333" t="n">
-        <v>32.4268</v>
+        <v>31.5336</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.42</v>
       </c>
       <c r="I334" t="n">
-        <v>1.0156</v>
+        <v>0.965</v>
       </c>
       <c r="J334" t="n">
-        <v>28.4368</v>
+        <v>27.02</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.08</v>
       </c>
       <c r="I335" t="n">
-        <v>0.222</v>
+        <v>0.2408</v>
       </c>
       <c r="J335" t="n">
-        <v>6.216</v>
+        <v>6.7424</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.8</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.6966</v>
+        <v>-0.6405</v>
       </c>
       <c r="J336" t="n">
-        <v>-19.5048</v>
+        <v>-17.934</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.22</v>
       </c>
       <c r="I337" t="n">
-        <v>0.5476</v>
+        <v>0.5209</v>
       </c>
       <c r="J337" t="n">
-        <v>15.3328</v>
+        <v>14.5852</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.87</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1499</v>
+        <v>-0.1672</v>
       </c>
       <c r="J338" t="n">
-        <v>-4.1972</v>
+        <v>-4.6816</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.75</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2676</v>
+        <v>-0.2848</v>
       </c>
       <c r="J339" t="n">
-        <v>-7.4928</v>
+        <v>-7.9744</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3251</v>
+        <v>-0.3407</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.1028</v>
+        <v>-9.5396</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.65</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3629</v>
+        <v>-0.3771</v>
       </c>
       <c r="J341" t="n">
-        <v>-10.1612</v>
+        <v>-10.5588</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.53</v>
       </c>
       <c r="I342" t="n">
-        <v>1.1803</v>
+        <v>1.1457</v>
       </c>
       <c r="J342" t="n">
-        <v>30.6878</v>
+        <v>29.7882</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.5</v>
       </c>
       <c r="I343" t="n">
-        <v>1.142</v>
+        <v>1.1047</v>
       </c>
       <c r="J343" t="n">
-        <v>29.692</v>
+        <v>28.7222</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.1</v>
       </c>
       <c r="I344" t="n">
-        <v>0.303</v>
+        <v>0.3106</v>
       </c>
       <c r="J344" t="n">
-        <v>7.878</v>
+        <v>8.0756</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.98</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1442</v>
+        <v>-0.1345</v>
       </c>
       <c r="J345" t="n">
-        <v>-3.7492</v>
+        <v>-3.497</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.88</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.46</v>
+        <v>-0.432</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.96</v>
+        <v>-11.232</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.23</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5452</v>
+        <v>0.5224</v>
       </c>
       <c r="J347" t="n">
-        <v>14.1752</v>
+        <v>13.5824</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.97</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.037</v>
+        <v>-0.0482</v>
       </c>
       <c r="J348" t="n">
-        <v>-0.962</v>
+        <v>-1.2532</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.84</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1839</v>
+        <v>-0.2007</v>
       </c>
       <c r="J349" t="n">
-        <v>-4.7814</v>
+        <v>-5.2182</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.76</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2632</v>
+        <v>-0.2794</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.8432</v>
+        <v>-7.2644</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.58</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4335</v>
+        <v>-0.4436</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.271</v>
+        <v>-11.5336</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.61</v>
       </c>
       <c r="I352" t="n">
-        <v>0.7245</v>
+        <v>0.7216</v>
       </c>
       <c r="J352" t="n">
-        <v>18.1125</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.38</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4783</v>
+        <v>0.4909</v>
       </c>
       <c r="J353" t="n">
-        <v>11.9575</v>
+        <v>12.2725</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.33</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4231</v>
+        <v>0.4382</v>
       </c>
       <c r="J354" t="n">
-        <v>10.5775</v>
+        <v>10.955</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.28</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3679</v>
+        <v>0.3849</v>
       </c>
       <c r="J355" t="n">
-        <v>9.1975</v>
+        <v>9.6225</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.257</v>
+        <v>-0.2645</v>
       </c>
       <c r="J356" t="n">
-        <v>-6.425</v>
+        <v>-6.6125</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.13</v>
       </c>
       <c r="I357" t="n">
-        <v>0.2693</v>
+        <v>0.2687</v>
       </c>
       <c r="J357" t="n">
-        <v>6.7325</v>
+        <v>6.7175</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.99</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.0052</v>
+        <v>-0.0134</v>
       </c>
       <c r="J358" t="n">
-        <v>-0.13</v>
+        <v>-0.335</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.89</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1325</v>
+        <v>-0.1485</v>
       </c>
       <c r="J359" t="n">
-        <v>-3.3125</v>
+        <v>-3.7125</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.71</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3107</v>
+        <v>-0.3259</v>
       </c>
       <c r="J360" t="n">
-        <v>-7.7675</v>
+        <v>-8.147500000000001</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.63</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3863</v>
+        <v>-0.3987</v>
       </c>
       <c r="J361" t="n">
-        <v>-9.657500000000001</v>
+        <v>-9.967499999999999</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.32</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6355</v>
+        <v>0.6168</v>
       </c>
       <c r="J362" t="n">
-        <v>19.065</v>
+        <v>18.504</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.21</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4437</v>
+        <v>0.4409</v>
       </c>
       <c r="J363" t="n">
-        <v>13.311</v>
+        <v>13.227</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>0.96</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0759</v>
       </c>
       <c r="J364" t="n">
-        <v>-2.028</v>
+        <v>-2.277</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>0.89</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.1502</v>
+        <v>-0.162</v>
       </c>
       <c r="J365" t="n">
-        <v>-4.506</v>
+        <v>-4.86</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.84</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.2034</v>
+        <v>-0.2158</v>
       </c>
       <c r="J366" t="n">
-        <v>-6.102</v>
+        <v>-6.474</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.28</v>
       </c>
       <c r="I367" t="n">
-        <v>0.7824</v>
+        <v>0.7366</v>
       </c>
       <c r="J367" t="n">
-        <v>23.472</v>
+        <v>22.098</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.09</v>
       </c>
       <c r="I368" t="n">
-        <v>0.297</v>
+        <v>0.2995</v>
       </c>
       <c r="J368" t="n">
-        <v>8.91</v>
+        <v>8.984999999999999</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.08</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2689</v>
+        <v>0.2732</v>
       </c>
       <c r="J369" t="n">
-        <v>8.067</v>
+        <v>8.196</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>1.06</v>
       </c>
       <c r="I370" t="n">
-        <v>0.2097</v>
+        <v>0.2173</v>
       </c>
       <c r="J370" t="n">
-        <v>6.291</v>
+        <v>6.519</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.95</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.222</v>
+        <v>-0.2174</v>
       </c>
       <c r="J371" t="n">
-        <v>-6.66</v>
+        <v>-6.522</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.17</v>
       </c>
       <c r="I372" t="n">
-        <v>0.3885</v>
+        <v>0.3859</v>
       </c>
       <c r="J372" t="n">
-        <v>16.317</v>
+        <v>16.2078</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.05</v>
       </c>
       <c r="I373" t="n">
-        <v>0.1431</v>
+        <v>0.1506</v>
       </c>
       <c r="J373" t="n">
-        <v>6.0102</v>
+        <v>6.3252</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>0.99</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.0195</v>
+        <v>-0.0245</v>
       </c>
       <c r="J374" t="n">
-        <v>-0.819</v>
+        <v>-1.029</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.91</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1211</v>
+        <v>-0.1339</v>
       </c>
       <c r="J375" t="n">
-        <v>-5.0862</v>
+        <v>-5.6238</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.79</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.2469</v>
+        <v>-0.2606</v>
       </c>
       <c r="J376" t="n">
-        <v>-10.3698</v>
+        <v>-10.9452</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.42</v>
       </c>
       <c r="I377" t="n">
-        <v>1.0555</v>
+        <v>1.0027</v>
       </c>
       <c r="J377" t="n">
-        <v>44.331</v>
+        <v>42.1134</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.24</v>
       </c>
       <c r="I378" t="n">
-        <v>0.6736</v>
+        <v>0.643</v>
       </c>
       <c r="J378" t="n">
-        <v>28.2912</v>
+        <v>27.006</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>1.09</v>
       </c>
       <c r="I379" t="n">
-        <v>0.2909</v>
+        <v>0.2954</v>
       </c>
       <c r="J379" t="n">
-        <v>12.2178</v>
+        <v>12.4068</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.96</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.1978</v>
+        <v>-0.1919</v>
       </c>
       <c r="J380" t="n">
-        <v>-8.307600000000001</v>
+        <v>-8.059799999999999</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.92</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3252</v>
+        <v>-0.3121</v>
       </c>
       <c r="J381" t="n">
-        <v>-13.6584</v>
+        <v>-13.1082</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.37</v>
       </c>
       <c r="I382" t="n">
-        <v>0.7524</v>
+        <v>0.7171</v>
       </c>
       <c r="J382" t="n">
-        <v>20.3148</v>
+        <v>19.3617</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>1.08</v>
       </c>
       <c r="I383" t="n">
-        <v>0.2135</v>
+        <v>0.2186</v>
       </c>
       <c r="J383" t="n">
-        <v>5.7645</v>
+        <v>5.9022</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>0.95</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.0728</v>
+        <v>-0.0837</v>
       </c>
       <c r="J384" t="n">
-        <v>-1.9656</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.82</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.2148</v>
+        <v>-0.2293</v>
       </c>
       <c r="J385" t="n">
-        <v>-5.7996</v>
+        <v>-6.1911</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.61</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4164</v>
+        <v>-0.4256</v>
       </c>
       <c r="J386" t="n">
-        <v>-11.2428</v>
+        <v>-11.4912</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.43</v>
       </c>
       <c r="I387" t="n">
-        <v>1.0515</v>
+        <v>1.0019</v>
       </c>
       <c r="J387" t="n">
-        <v>28.3905</v>
+        <v>27.0513</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.32</v>
       </c>
       <c r="I388" t="n">
-        <v>0.8406</v>
+        <v>0.794</v>
       </c>
       <c r="J388" t="n">
-        <v>22.6962</v>
+        <v>21.438</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>1.13</v>
       </c>
       <c r="I389" t="n">
-        <v>0.3856</v>
+        <v>0.3864</v>
       </c>
       <c r="J389" t="n">
-        <v>10.4112</v>
+        <v>10.4328</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>1.12</v>
       </c>
       <c r="I390" t="n">
-        <v>0.3587</v>
+        <v>0.3618</v>
       </c>
       <c r="J390" t="n">
-        <v>9.684900000000001</v>
+        <v>9.768599999999999</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.98</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.1437</v>
+        <v>-0.1342</v>
       </c>
       <c r="J391" t="n">
-        <v>-3.8799</v>
+        <v>-3.6234</v>
       </c>
     </row>
     <row r="392">
@@ -18029,10 +18029,10 @@
         <v>1.52</v>
       </c>
       <c r="I392" t="n">
-        <v>0.981</v>
+        <v>0.9291</v>
       </c>
       <c r="J392" t="n">
-        <v>27.468</v>
+        <v>26.0148</v>
       </c>
     </row>
     <row r="393">
@@ -18069,10 +18069,10 @@
         <v>1.05</v>
       </c>
       <c r="I393" t="n">
-        <v>0.1405</v>
+        <v>0.1488</v>
       </c>
       <c r="J393" t="n">
-        <v>3.934</v>
+        <v>4.1664</v>
       </c>
     </row>
     <row r="394">
@@ -18109,10 +18109,10 @@
         <v>0.99</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.0202</v>
+        <v>-0.0249</v>
       </c>
       <c r="J394" t="n">
-        <v>-0.5656</v>
+        <v>-0.6972</v>
       </c>
     </row>
     <row r="395">
@@ -18149,10 +18149,10 @@
         <v>0.78</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.2582</v>
+        <v>-0.2715</v>
       </c>
       <c r="J395" t="n">
-        <v>-7.2296</v>
+        <v>-7.602</v>
       </c>
     </row>
     <row r="396">
@@ -18189,10 +18189,10 @@
         <v>0.63</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.401</v>
+        <v>-0.4103</v>
       </c>
       <c r="J396" t="n">
-        <v>-11.228</v>
+        <v>-11.4884</v>
       </c>
     </row>
     <row r="397">
@@ -18229,10 +18229,10 @@
         <v>1.24</v>
       </c>
       <c r="I397" t="n">
-        <v>0.6676</v>
+        <v>0.6389</v>
       </c>
       <c r="J397" t="n">
-        <v>18.6928</v>
+        <v>17.8892</v>
       </c>
     </row>
     <row r="398">
@@ -18269,10 +18269,10 @@
         <v>1.23</v>
       </c>
       <c r="I398" t="n">
-        <v>0.6435</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="J398" t="n">
-        <v>18.018</v>
+        <v>17.2872</v>
       </c>
     </row>
     <row r="399">
@@ -18309,10 +18309,10 @@
         <v>1.23</v>
       </c>
       <c r="I399" t="n">
-        <v>0.6435</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="J399" t="n">
-        <v>18.018</v>
+        <v>17.2872</v>
       </c>
     </row>
     <row r="400">
@@ -18349,10 +18349,10 @@
         <v>1.03</v>
       </c>
       <c r="I400" t="n">
-        <v>0.098</v>
+        <v>0.1136</v>
       </c>
       <c r="J400" t="n">
-        <v>2.744</v>
+        <v>3.1808</v>
       </c>
     </row>
     <row r="401">
@@ -18389,10 +18389,10 @@
         <v>1</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.0348</v>
+        <v>-0.024</v>
       </c>
       <c r="J401" t="n">
-        <v>-0.9744</v>
+        <v>-0.672</v>
       </c>
     </row>
     <row r="402">
@@ -18429,10 +18429,10 @@
         <v>1.85</v>
       </c>
       <c r="I402" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9201</v>
       </c>
       <c r="J402" t="n">
-        <v>18.68</v>
+        <v>18.402</v>
       </c>
     </row>
     <row r="403">
@@ -18469,10 +18469,10 @@
         <v>1.67</v>
       </c>
       <c r="I403" t="n">
-        <v>0.7583</v>
+        <v>0.7574</v>
       </c>
       <c r="J403" t="n">
-        <v>15.166</v>
+        <v>15.148</v>
       </c>
     </row>
     <row r="404">
@@ -18509,10 +18509,10 @@
         <v>1.47</v>
       </c>
       <c r="I404" t="n">
-        <v>0.5568</v>
+        <v>0.5687</v>
       </c>
       <c r="J404" t="n">
-        <v>11.136</v>
+        <v>11.374</v>
       </c>
     </row>
     <row r="405">
@@ -18549,10 +18549,10 @@
         <v>1.28</v>
       </c>
       <c r="I405" t="n">
-        <v>0.3528</v>
+        <v>0.3736</v>
       </c>
       <c r="J405" t="n">
-        <v>7.056</v>
+        <v>7.472</v>
       </c>
     </row>
     <row r="406">
@@ -18589,10 +18589,10 @@
         <v>0.95</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.1174</v>
+        <v>-0.1185</v>
       </c>
       <c r="J406" t="n">
-        <v>-2.348</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="407">
@@ -18629,10 +18629,10 @@
         <v>0.97</v>
       </c>
       <c r="I407" t="n">
-        <v>0.0132</v>
+        <v>-0.0119</v>
       </c>
       <c r="J407" t="n">
-        <v>0.264</v>
+        <v>-0.238</v>
       </c>
     </row>
     <row r="408">
@@ -18669,10 +18669,10 @@
         <v>0.83</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.1651</v>
+        <v>-0.1886</v>
       </c>
       <c r="J408" t="n">
-        <v>-3.302</v>
+        <v>-3.772</v>
       </c>
     </row>
     <row r="409">
@@ -18709,10 +18709,10 @@
         <v>0.66</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.3318</v>
+        <v>-0.3512</v>
       </c>
       <c r="J409" t="n">
-        <v>-6.636</v>
+        <v>-7.024</v>
       </c>
     </row>
     <row r="410">
@@ -18749,10 +18749,10 @@
         <v>0.62</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.3686</v>
+        <v>-0.3866</v>
       </c>
       <c r="J410" t="n">
-        <v>-7.372</v>
+        <v>-7.732</v>
       </c>
     </row>
     <row r="411">
@@ -18789,10 +18789,10 @@
         <v>0.36</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.6118</v>
+        <v>-0.6143</v>
       </c>
       <c r="J411" t="n">
-        <v>-12.236</v>
+        <v>-12.286</v>
       </c>
     </row>
     <row r="412">
@@ -18829,10 +18829,10 @@
         <v>1.38</v>
       </c>
       <c r="I412" t="n">
-        <v>0.7929</v>
+        <v>0.7498</v>
       </c>
       <c r="J412" t="n">
-        <v>21.4083</v>
+        <v>20.2446</v>
       </c>
     </row>
     <row r="413">
@@ -18869,10 +18869,10 @@
         <v>0.95</v>
       </c>
       <c r="I413" t="n">
-        <v>-0.0692</v>
+        <v>-0.081</v>
       </c>
       <c r="J413" t="n">
-        <v>-1.8684</v>
+        <v>-2.187</v>
       </c>
     </row>
     <row r="414">
@@ -18909,10 +18909,10 @@
         <v>0.89</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.1366</v>
+        <v>-0.1515</v>
       </c>
       <c r="J414" t="n">
-        <v>-3.6882</v>
+        <v>-4.0905</v>
       </c>
     </row>
     <row r="415">
@@ -18949,10 +18949,10 @@
         <v>0.89</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.1366</v>
+        <v>-0.1515</v>
       </c>
       <c r="J415" t="n">
-        <v>-3.6882</v>
+        <v>-4.0905</v>
       </c>
     </row>
     <row r="416">
@@ -18989,10 +18989,10 @@
         <v>0.49</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.5206</v>
+        <v>-0.5252</v>
       </c>
       <c r="J416" t="n">
-        <v>-14.0562</v>
+        <v>-14.1804</v>
       </c>
     </row>
     <row r="417">
@@ -19029,10 +19029,10 @@
         <v>1.83</v>
       </c>
       <c r="I417" t="n">
-        <v>1.5479</v>
+        <v>1.535</v>
       </c>
       <c r="J417" t="n">
-        <v>41.7933</v>
+        <v>41.445</v>
       </c>
     </row>
     <row r="418">
@@ -19069,10 +19069,10 @@
         <v>1.2</v>
       </c>
       <c r="I418" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5445</v>
       </c>
       <c r="J418" t="n">
-        <v>15.093</v>
+        <v>14.7015</v>
       </c>
     </row>
     <row r="419">
@@ -19109,10 +19109,10 @@
         <v>1.14</v>
       </c>
       <c r="I419" t="n">
-        <v>0.4089</v>
+        <v>0.4084</v>
       </c>
       <c r="J419" t="n">
-        <v>11.0403</v>
+        <v>11.0268</v>
       </c>
     </row>
     <row r="420">
@@ -19149,10 +19149,10 @@
         <v>1.1</v>
       </c>
       <c r="I420" t="n">
-        <v>0.3002</v>
+        <v>0.3086</v>
       </c>
       <c r="J420" t="n">
-        <v>8.105399999999999</v>
+        <v>8.3322</v>
       </c>
     </row>
     <row r="421">
@@ -19189,10 +19189,10 @@
         <v>0.78</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.7287</v>
+        <v>-0.6724</v>
       </c>
       <c r="J421" t="n">
-        <v>-19.6749</v>
+        <v>-18.1548</v>
       </c>
     </row>
     <row r="422">
@@ -19229,10 +19229,10 @@
         <v>1.15</v>
       </c>
       <c r="I422" t="n">
-        <v>0.3485</v>
+        <v>0.3488</v>
       </c>
       <c r="J422" t="n">
-        <v>10.1065</v>
+        <v>10.1152</v>
       </c>
     </row>
     <row r="423">
@@ -19269,10 +19269,10 @@
         <v>1.04</v>
       </c>
       <c r="I423" t="n">
-        <v>0.1184</v>
+        <v>0.1263</v>
       </c>
       <c r="J423" t="n">
-        <v>3.4336</v>
+        <v>3.6627</v>
       </c>
     </row>
     <row r="424">
@@ -19309,10 +19309,10 @@
         <v>0.97</v>
       </c>
       <c r="I424" t="n">
-        <v>-0.049</v>
+        <v>-0.0574</v>
       </c>
       <c r="J424" t="n">
-        <v>-1.421</v>
+        <v>-1.6646</v>
       </c>
     </row>
     <row r="425">
@@ -19349,10 +19349,10 @@
         <v>0.96</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.0621</v>
+        <v>-0.0717</v>
       </c>
       <c r="J425" t="n">
-        <v>-1.8009</v>
+        <v>-2.0793</v>
       </c>
     </row>
     <row r="426">
@@ -19389,10 +19389,10 @@
         <v>0.82</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.2174</v>
+        <v>-0.2313</v>
       </c>
       <c r="J426" t="n">
-        <v>-6.3046</v>
+        <v>-6.7077</v>
       </c>
     </row>
     <row r="427">
@@ -19429,10 +19429,10 @@
         <v>1.74</v>
       </c>
       <c r="I427" t="n">
-        <v>1.4746</v>
+        <v>1.4523</v>
       </c>
       <c r="J427" t="n">
-        <v>42.7634</v>
+        <v>42.1167</v>
       </c>
     </row>
     <row r="428">
@@ -19469,10 +19469,10 @@
         <v>1.12</v>
       </c>
       <c r="I428" t="n">
-        <v>0.3747</v>
+        <v>0.3726</v>
       </c>
       <c r="J428" t="n">
-        <v>10.8663</v>
+        <v>10.8054</v>
       </c>
     </row>
     <row r="429">
@@ -19509,10 +19509,10 @@
         <v>0.99</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.0803</v>
+        <v>-0.0772</v>
       </c>
       <c r="J429" t="n">
-        <v>-2.3287</v>
+        <v>-2.2388</v>
       </c>
     </row>
     <row r="430">
@@ -19549,10 +19549,10 @@
         <v>0.88</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.4371</v>
+        <v>-0.4159</v>
       </c>
       <c r="J430" t="n">
-        <v>-12.6759</v>
+        <v>-12.0611</v>
       </c>
     </row>
     <row r="431">
@@ -19589,10 +19589,10 @@
         <v>0.82</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.6002</v>
+        <v>-0.5628</v>
       </c>
       <c r="J431" t="n">
-        <v>-17.4058</v>
+        <v>-16.3212</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5286/event_5286_evp_summary.xlsx
+++ b/database/event/5286/event_5286_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.4192</v>
+        <v>5.3339</v>
       </c>
       <c r="C2" t="n">
-        <v>0.978</v>
+        <v>0.9626</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8427</v>
+        <v>1.8241</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4192</v>
+        <v>5.3339</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4083</v>
+        <v>3.322</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0109</v>
+        <v>2.0119</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7348</v>
+        <v>4.6629</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7348</v>
+        <v>4.6629</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0109</v>
+        <v>2.0119</v>
       </c>
       <c r="K2" t="n">
         <v>316</v>
@@ -529,7 +529,7 @@
         <v>29</v>
       </c>
       <c r="M2" t="n">
-        <v>6.745699999999999</v>
+        <v>6.674799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>345</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1628</v>
+        <v>4.8793</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9317</v>
+        <v>0.8806</v>
       </c>
       <c r="D3" t="n">
-        <v>1.726</v>
+        <v>1.617</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1628</v>
+        <v>4.8793</v>
       </c>
       <c r="F3" t="n">
-        <v>4.9038</v>
+        <v>4.6482</v>
       </c>
       <c r="G3" t="n">
-        <v>0.259</v>
+        <v>0.2311</v>
       </c>
       <c r="H3" t="n">
-        <v>8.007899999999999</v>
+        <v>7.7022</v>
       </c>
       <c r="I3" t="n">
-        <v>8.4259</v>
+        <v>8.119400000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.259</v>
+        <v>0.2311</v>
       </c>
       <c r="K3" t="n">
         <v>384</v>
@@ -575,7 +575,7 @@
         <v>29</v>
       </c>
       <c r="M3" t="n">
-        <v>8.684900000000001</v>
+        <v>8.3505</v>
       </c>
       <c r="N3" t="n">
         <v>413</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3267</v>
+        <v>4.1847</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7808</v>
+        <v>0.7552</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3454</v>
+        <v>1.3005</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3267</v>
+        <v>4.1847</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3267</v>
+        <v>4.4403</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0.2556</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7449</v>
+        <v>7.2258</v>
       </c>
       <c r="I4" t="n">
-        <v>6.7449</v>
+        <v>7.6171</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0.2556</v>
       </c>
       <c r="K4" t="n">
-        <v>296</v>
+        <v>384</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M4" t="n">
-        <v>6.7449</v>
+        <v>7.361499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>296</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2785</v>
+        <v>4.1779</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7721</v>
+        <v>0.754</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3235</v>
+        <v>1.2974</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2785</v>
+        <v>4.1779</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4964</v>
+        <v>4.1779</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2179</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7.1163</v>
+        <v>6.6244</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4878</v>
+        <v>6.6244</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2179</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>384</v>
+        <v>296</v>
       </c>
       <c r="L5" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>7.2699</v>
+        <v>6.6244</v>
       </c>
       <c r="N5" t="n">
-        <v>413</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2164</v>
+        <v>4.1059</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7609</v>
+        <v>0.741</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2952</v>
+        <v>1.2646</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2164</v>
+        <v>4.1059</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0602</v>
+        <v>3.0119</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1562</v>
+        <v>1.094</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9729</v>
+        <v>3.9523</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9729</v>
+        <v>3.9523</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1562</v>
+        <v>1.094</v>
       </c>
       <c r="K6" t="n">
         <v>316</v>
@@ -713,7 +713,7 @@
         <v>29</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1291</v>
+        <v>5.0463</v>
       </c>
       <c r="N6" t="n">
         <v>345</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1196</v>
+        <v>4.0289</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7435</v>
+        <v>0.7271</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2511</v>
+        <v>1.2296</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1196</v>
+        <v>4.0289</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4508</v>
+        <v>2.3961</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6688</v>
+        <v>1.6328</v>
       </c>
       <c r="H7" t="n">
-        <v>2.639</v>
+        <v>2.5409</v>
       </c>
       <c r="I7" t="n">
-        <v>2.639</v>
+        <v>2.5409</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6688</v>
+        <v>1.6328</v>
       </c>
       <c r="K7" t="n">
         <v>316</v>
@@ -759,7 +759,7 @@
         <v>29</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3078</v>
+        <v>4.1737</v>
       </c>
       <c r="N7" t="n">
         <v>345</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0689</v>
+        <v>3.8546</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7343</v>
+        <v>0.6956</v>
       </c>
       <c r="D8" t="n">
-        <v>1.228</v>
+        <v>1.1502</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0689</v>
+        <v>3.8546</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0689</v>
+        <v>3.8546</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>6.1806</v>
+        <v>5.8834</v>
       </c>
       <c r="I8" t="n">
-        <v>6.1806</v>
+        <v>5.8834</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>6.1806</v>
+        <v>5.8834</v>
       </c>
       <c r="N8" t="n">
         <v>318</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1435</v>
+        <v>3.0532</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5673</v>
+        <v>0.551</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8068</v>
+        <v>0.7851</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1435</v>
+        <v>3.0532</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1435</v>
+        <v>3.0532</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1552</v>
+        <v>4.047</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1552</v>
+        <v>4.047</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1552</v>
+        <v>4.047</v>
       </c>
       <c r="N9" t="n">
         <v>318</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.954</v>
+        <v>2.8195</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5331</v>
+        <v>0.5088</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7205</v>
+        <v>0.6786</v>
       </c>
       <c r="E10" t="n">
-        <v>2.954</v>
+        <v>2.8195</v>
       </c>
       <c r="F10" t="n">
-        <v>2.954</v>
+        <v>2.8195</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7404</v>
+        <v>3.5112</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7404</v>
+        <v>3.5112</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7404</v>
+        <v>3.5112</v>
       </c>
       <c r="N10" t="n">
         <v>318</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7649</v>
+        <v>2.684</v>
       </c>
       <c r="C11" t="n">
-        <v>0.499</v>
+        <v>0.4844</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6344</v>
+        <v>0.6169</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7649</v>
+        <v>2.684</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7649</v>
+        <v>2.684</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3266</v>
+        <v>3.2008</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3266</v>
+        <v>3.2008</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3266</v>
+        <v>3.2008</v>
       </c>
       <c r="N11" t="n">
         <v>216</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6669</v>
+        <v>2.5353</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4813</v>
+        <v>0.4575</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5898</v>
+        <v>0.5492</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6669</v>
+        <v>2.5353</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3577</v>
+        <v>3.196</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6908</v>
+        <v>-0.6607</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6241</v>
+        <v>4.3741</v>
       </c>
       <c r="I12" t="n">
-        <v>4.8655</v>
+        <v>4.611</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6908</v>
+        <v>-0.6607</v>
       </c>
       <c r="K12" t="n">
         <v>384</v>
@@ -989,7 +989,7 @@
         <v>29</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1747</v>
+        <v>3.9503</v>
       </c>
       <c r="N12" t="n">
         <v>413</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5081</v>
+        <v>2.4156</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4526</v>
+        <v>0.4359</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5175</v>
+        <v>0.4946</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5081</v>
+        <v>2.4156</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5081</v>
+        <v>2.4156</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7646</v>
+        <v>2.5857</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7646</v>
+        <v>2.5857</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>237</v>
+        <v>318</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7646</v>
+        <v>2.5857</v>
       </c>
       <c r="N13" t="n">
-        <v>237</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4858</v>
+        <v>2.3972</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4486</v>
+        <v>0.4326</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5074</v>
+        <v>0.4863</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4858</v>
+        <v>2.3972</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4858</v>
+        <v>2.3972</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7158</v>
+        <v>2.5436</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7158</v>
+        <v>2.5436</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7158</v>
+        <v>2.5436</v>
       </c>
       <c r="N14" t="n">
         <v>216</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>Xeppaa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.482</v>
+        <v>2.3831</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4479</v>
+        <v>0.4301</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5057</v>
+        <v>0.4798</v>
       </c>
       <c r="E15" t="n">
-        <v>2.482</v>
+        <v>2.3831</v>
       </c>
       <c r="F15" t="n">
-        <v>2.482</v>
+        <v>2.3831</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7074</v>
+        <v>2.5111</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7074</v>
+        <v>2.5111</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>318</v>
+        <v>217</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7074</v>
+        <v>2.5111</v>
       </c>
       <c r="N15" t="n">
-        <v>318</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Xeppaa</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4165</v>
+        <v>2.3647</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4361</v>
+        <v>0.4268</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4758</v>
+        <v>0.4714</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4165</v>
+        <v>2.3647</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4165</v>
+        <v>2.3647</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5641</v>
+        <v>2.4691</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5641</v>
+        <v>2.4691</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5641</v>
+        <v>2.4691</v>
       </c>
       <c r="N16" t="n">
-        <v>217</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2432</v>
+        <v>2.2413</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4048</v>
+        <v>0.4045</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3969</v>
+        <v>0.4152</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2432</v>
+        <v>2.2413</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2432</v>
+        <v>2.2413</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2432</v>
+        <v>2.2413</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2432</v>
+        <v>2.2413</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2432</v>
+        <v>2.2413</v>
       </c>
       <c r="N17" t="n">
         <v>216</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9622</v>
+        <v>1.8812</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3541</v>
+        <v>0.3395</v>
       </c>
       <c r="D18" t="n">
-        <v>0.269</v>
+        <v>0.2512</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9622</v>
+        <v>1.8812</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4153</v>
+        <v>2.3015</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4531</v>
+        <v>-0.4203</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5614</v>
+        <v>2.3243</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6951</v>
+        <v>2.4502</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4531</v>
+        <v>-0.4203</v>
       </c>
       <c r="K18" t="n">
         <v>384</v>
@@ -1265,7 +1265,7 @@
         <v>29</v>
       </c>
       <c r="M18" t="n">
-        <v>2.242</v>
+        <v>2.0299</v>
       </c>
       <c r="N18" t="n">
         <v>413</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8024</v>
+        <v>1.6618</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3253</v>
+        <v>0.2999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1963</v>
+        <v>0.1512</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8024</v>
+        <v>1.6618</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8024</v>
+        <v>1.6618</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8024</v>
+        <v>1.6618</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8024</v>
+        <v>1.6618</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8024</v>
+        <v>1.6618</v>
       </c>
       <c r="N19" t="n">
         <v>236</v>
@@ -1320,81 +1320,81 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6931</v>
+        <v>1.6473</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3056</v>
+        <v>0.2973</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1465</v>
+        <v>0.1446</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6931</v>
+        <v>1.6473</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6931</v>
+        <v>-0.0017</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.649</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6931</v>
+        <v>-0.0017</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6931</v>
+        <v>-0.0017</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.649</v>
       </c>
       <c r="K20" t="n">
-        <v>237</v>
+        <v>316</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6931</v>
+        <v>1.6473</v>
       </c>
       <c r="N20" t="n">
-        <v>237</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.643</v>
+        <v>1.6187</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2965</v>
+        <v>0.2921</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1237</v>
+        <v>0.1316</v>
       </c>
       <c r="E21" t="n">
-        <v>1.643</v>
+        <v>1.6187</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0048</v>
+        <v>1.7543</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6478</v>
+        <v>-0.1356</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0048</v>
+        <v>1.7543</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0048</v>
+        <v>1.7543</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6478</v>
+        <v>-0.1356</v>
       </c>
       <c r="K21" t="n">
         <v>316</v>
@@ -1403,7 +1403,7 @@
         <v>29</v>
       </c>
       <c r="M21" t="n">
-        <v>1.643</v>
+        <v>1.6187</v>
       </c>
       <c r="N21" t="n">
         <v>345</v>
@@ -1412,170 +1412,170 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.5939</v>
+        <v>1.5552</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2877</v>
+        <v>0.2807</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1014</v>
+        <v>0.1027</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5939</v>
+        <v>1.5552</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7399</v>
+        <v>1.5552</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.146</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7399</v>
+        <v>1.5552</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7399</v>
+        <v>1.5552</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.146</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>316</v>
+        <v>237</v>
       </c>
       <c r="L22" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5939</v>
+        <v>1.5552</v>
       </c>
       <c r="N22" t="n">
-        <v>345</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.5484</v>
+        <v>1.3672</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2794</v>
+        <v>0.2467</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5484</v>
+        <v>1.3672</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5484</v>
+        <v>1.6479</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.2807</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5484</v>
+        <v>1.6479</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5484</v>
+        <v>1.7372</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.2807</v>
       </c>
       <c r="K23" t="n">
-        <v>237</v>
+        <v>384</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5484</v>
+        <v>1.4565</v>
       </c>
       <c r="N23" t="n">
-        <v>237</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3364</v>
+        <v>1.3581</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2412</v>
+        <v>0.2451</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0158</v>
+        <v>0.0129</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3364</v>
+        <v>1.3581</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6415</v>
+        <v>1.3581</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3051</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6415</v>
+        <v>1.3581</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7272</v>
+        <v>1.3581</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3051</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>384</v>
+        <v>237</v>
       </c>
       <c r="L24" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4221</v>
+        <v>1.3581</v>
       </c>
       <c r="N24" t="n">
-        <v>413</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3073</v>
+        <v>1.1953</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2359</v>
+        <v>0.2157</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0291</v>
+        <v>-0.0613</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3073</v>
+        <v>1.1953</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3073</v>
+        <v>1.1953</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3073</v>
+        <v>1.1953</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3073</v>
+        <v>1.1953</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3073</v>
+        <v>1.1953</v>
       </c>
       <c r="N25" t="n">
         <v>296</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.303</v>
+        <v>1.1806</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2352</v>
+        <v>0.2131</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0311</v>
+        <v>-0.068</v>
       </c>
       <c r="E26" t="n">
-        <v>1.303</v>
+        <v>1.1806</v>
       </c>
       <c r="F26" t="n">
-        <v>1.303</v>
+        <v>1.1806</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.303</v>
+        <v>1.1806</v>
       </c>
       <c r="I26" t="n">
-        <v>1.303</v>
+        <v>1.1806</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.303</v>
+        <v>1.1806</v>
       </c>
       <c r="N26" t="n">
         <v>296</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1699</v>
+        <v>1.1038</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2111</v>
+        <v>0.1992</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0916</v>
+        <v>-0.103</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1699</v>
+        <v>1.1038</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1699</v>
+        <v>1.1038</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1699</v>
+        <v>1.1038</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1699</v>
+        <v>1.1038</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1699</v>
+        <v>1.1038</v>
       </c>
       <c r="N27" t="n">
         <v>236</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.0211</v>
+        <v>0.9847</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1843</v>
+        <v>0.1777</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1594</v>
+        <v>-0.1572</v>
       </c>
       <c r="E28" t="n">
-        <v>1.0211</v>
+        <v>0.9847</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0211</v>
+        <v>0.9847</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0211</v>
+        <v>0.9847</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0211</v>
+        <v>0.9847</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.0211</v>
+        <v>0.9847</v>
       </c>
       <c r="N28" t="n">
         <v>237</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9647</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1707</v>
+        <v>0.1741</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1935</v>
+        <v>-0.1663</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9647</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9647</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9647</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9647</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9647</v>
       </c>
       <c r="N29" t="n">
         <v>318</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4162</v>
+        <v>0.3565</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0751</v>
+        <v>0.0643</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4347</v>
+        <v>-0.4434</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4162</v>
+        <v>0.3565</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4162</v>
+        <v>0.3565</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4162</v>
+        <v>0.3565</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4162</v>
+        <v>0.3565</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4162</v>
+        <v>0.3565</v>
       </c>
       <c r="N30" t="n">
         <v>237</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>motm</t>
+          <t>Jonji</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0119</v>
+        <v>0.0156</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5941</v>
+        <v>-0.5664</v>
       </c>
       <c r="E31" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>296</v>
+        <v>217</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>296</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jonji</t>
+          <t>motm</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0469</v>
+        <v>0.0548</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6029</v>
+        <v>-0.5808</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0469</v>
+        <v>0.0548</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0469</v>
+        <v>0.0548</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0469</v>
+        <v>0.0548</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0469</v>
+        <v>0.0548</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>217</v>
+        <v>296</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0469</v>
+        <v>0.0548</v>
       </c>
       <c r="N32" t="n">
-        <v>217</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0061</v>
+        <v>-0.0514</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0011</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6214</v>
+        <v>-0.6292</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0061</v>
+        <v>-0.0514</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0061</v>
+        <v>-0.0514</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0061</v>
+        <v>-0.0514</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0061</v>
+        <v>-0.0514</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0061</v>
+        <v>-0.0514</v>
       </c>
       <c r="N33" t="n">
         <v>217</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1173</v>
+        <v>-0.0977</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0212</v>
+        <v>-0.0176</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6776</v>
+        <v>-0.6503</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1173</v>
+        <v>-0.0977</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1173</v>
+        <v>-0.0977</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1173</v>
+        <v>-0.0977</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1173</v>
+        <v>-0.0977</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1173</v>
+        <v>-0.0977</v>
       </c>
       <c r="N34" t="n">
         <v>217</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.1719</v>
+        <v>-0.1791</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.031</v>
+        <v>-0.0323</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7025</v>
+        <v>-0.6874</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.1719</v>
+        <v>-0.1791</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1719</v>
+        <v>-0.1791</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.1719</v>
+        <v>-0.1791</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1719</v>
+        <v>-0.1791</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.1719</v>
+        <v>-0.1791</v>
       </c>
       <c r="N35" t="n">
         <v>236</v>
@@ -2056,185 +2056,185 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.2207</v>
+        <v>-0.2</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0398</v>
+        <v>-0.0361</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7247</v>
+        <v>-0.6969</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.2207</v>
+        <v>-0.2</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2207</v>
+        <v>-0.2</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2207</v>
+        <v>-0.2</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2207</v>
+        <v>-0.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>236</v>
+        <v>296</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.2207</v>
+        <v>-0.2</v>
       </c>
       <c r="N36" t="n">
-        <v>236</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.2926</v>
+        <v>-0.2454</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0528</v>
+        <v>-0.0443</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7574</v>
+        <v>-0.7176</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.2926</v>
+        <v>-0.2454</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.2926</v>
+        <v>-0.2454</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2926</v>
+        <v>-0.2454</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2926</v>
+        <v>-0.2454</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.2926</v>
+        <v>-0.2454</v>
       </c>
       <c r="N37" t="n">
-        <v>296</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1784</v>
+        <v>-0.1782</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0741</v>
+        <v>-1.0556</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0233</v>
+        <v>-0.9895</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1847</v>
+        <v>-0.1786</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.09</v>
+        <v>-1.0566</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0233</v>
+        <v>-0.9895</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0233</v>
+        <v>-0.9895</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0233</v>
+        <v>-0.9895</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0233</v>
+        <v>-0.9895</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0233</v>
+        <v>-0.9895</v>
       </c>
       <c r="N39" t="n">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7312</v>
+        <v>-1.6441</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3124</v>
+        <v>-0.2967</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4123</v>
+        <v>-1.3548</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7312</v>
+        <v>-1.6441</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7312</v>
+        <v>-1.6441</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7312</v>
+        <v>-1.6441</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7312</v>
+        <v>-1.6441</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7312</v>
+        <v>-1.6441</v>
       </c>
       <c r="N40" t="n">
         <v>216</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4425</v>
+        <v>-2.4287</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4408</v>
+        <v>-0.4383</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7361</v>
+        <v>-1.7122</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4425</v>
+        <v>-2.4287</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.4425</v>
+        <v>-2.4287</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.4425</v>
+        <v>-2.4287</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4425</v>
+        <v>-2.4287</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4425</v>
+        <v>-2.4287</v>
       </c>
       <c r="N41" t="n">
         <v>217</v>
@@ -2429,10 +2429,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8438</v>
+        <v>0.8212</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8438</v>
+        <v>0.8212</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6373</v>
+        <v>0.603</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6373</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.21</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5727</v>
+        <v>0.5366</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5727</v>
+        <v>0.5366</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2912</v>
+        <v>0.2579</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2912</v>
+        <v>0.2579</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.89</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3983</v>
+        <v>-0.3562</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3983</v>
+        <v>-0.3562</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.08</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2322</v>
+        <v>0.1876</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2322</v>
+        <v>0.1876</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.98</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0358</v>
+        <v>-0.028</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0358</v>
+        <v>-0.028</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1286</v>
+        <v>-0.1116</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1286</v>
+        <v>-0.1116</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1613</v>
+        <v>-0.1426</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1613</v>
+        <v>-0.1426</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.68</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3572</v>
+        <v>-0.3425</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3572</v>
+        <v>-0.3425</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.66</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3736</v>
+        <v>1.4089</v>
       </c>
       <c r="J12" t="n">
-        <v>38.4608</v>
+        <v>39.4492</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.65</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3566</v>
+        <v>1.3911</v>
       </c>
       <c r="J13" t="n">
-        <v>37.9848</v>
+        <v>38.9508</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.35</v>
       </c>
       <c r="I14" t="n">
-        <v>0.825</v>
+        <v>0.8116</v>
       </c>
       <c r="J14" t="n">
-        <v>23.1</v>
+        <v>22.7248</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5835</v>
+        <v>0.5574</v>
       </c>
       <c r="J15" t="n">
-        <v>16.338</v>
+        <v>15.6072</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2523</v>
+        <v>0.2206</v>
       </c>
       <c r="J16" t="n">
-        <v>7.0644</v>
+        <v>6.1768</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4203</v>
+        <v>0.3753</v>
       </c>
       <c r="J17" t="n">
-        <v>11.7684</v>
+        <v>10.5084</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.76</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2693</v>
+        <v>-0.2527</v>
       </c>
       <c r="J18" t="n">
-        <v>-7.5404</v>
+        <v>-7.0756</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.7</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3245</v>
+        <v>-0.3087</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.086</v>
+        <v>-8.643599999999999</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3336</v>
+        <v>-0.3182</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.3408</v>
+        <v>-8.909599999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4501</v>
+        <v>-0.4432</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.6028</v>
+        <v>-12.4096</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.38</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7119</v>
+        <v>0.6551</v>
       </c>
       <c r="J22" t="n">
-        <v>25.6284</v>
+        <v>23.5836</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0409</v>
+        <v>0.0283</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4724</v>
+        <v>1.0188</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.95</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.0722</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.1824</v>
+        <v>-2.5992</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.93</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.114</v>
+        <v>-0.0958</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.104</v>
+        <v>-3.4488</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1719</v>
+        <v>-0.1515</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.1884</v>
+        <v>-5.454</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5594</v>
+        <v>1.6079</v>
       </c>
       <c r="J27" t="n">
-        <v>56.1384</v>
+        <v>57.8844</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.97</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1541</v>
+        <v>-0.1228</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.5476</v>
+        <v>-4.4208</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.95</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2197</v>
+        <v>-0.1827</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.9092</v>
+        <v>-6.5772</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3355</v>
+        <v>-0.2935</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.078</v>
+        <v>-10.566</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4402</v>
+        <v>-0.3976</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.8472</v>
+        <v>-14.3136</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.21</v>
       </c>
       <c r="I32" t="n">
-        <v>0.534</v>
+        <v>0.4907</v>
       </c>
       <c r="J32" t="n">
-        <v>11.214</v>
+        <v>10.3047</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.75</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2783</v>
+        <v>-0.2618</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.8443</v>
+        <v>-5.4978</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.74</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2875</v>
+        <v>-0.271</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.0375</v>
+        <v>-5.691</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.64</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3787</v>
+        <v>-0.3657</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.9527</v>
+        <v>-7.6797</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.51</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4936</v>
+        <v>-0.4917</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.3656</v>
+        <v>-10.3257</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.62</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2284</v>
+        <v>1.2453</v>
       </c>
       <c r="J37" t="n">
-        <v>25.7964</v>
+        <v>26.1513</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.57</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1643</v>
+        <v>1.1795</v>
       </c>
       <c r="J38" t="n">
-        <v>24.4503</v>
+        <v>24.7695</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.34</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8072</v>
+        <v>0.7922</v>
       </c>
       <c r="J39" t="n">
-        <v>16.9512</v>
+        <v>16.6362</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.28</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6676</v>
       </c>
       <c r="J40" t="n">
-        <v>14.469</v>
+        <v>14.0196</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.12</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3317</v>
+        <v>0.2995</v>
       </c>
       <c r="J41" t="n">
-        <v>6.9657</v>
+        <v>6.2895</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.97</v>
       </c>
       <c r="I42" t="n">
-        <v>1.6572</v>
+        <v>1.7023</v>
       </c>
       <c r="J42" t="n">
-        <v>33.144</v>
+        <v>34.046</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.71</v>
       </c>
       <c r="I43" t="n">
-        <v>1.3411</v>
+        <v>1.3627</v>
       </c>
       <c r="J43" t="n">
-        <v>26.822</v>
+        <v>27.254</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7287</v>
+        <v>0.7094</v>
       </c>
       <c r="J44" t="n">
-        <v>14.574</v>
+        <v>14.188</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.02</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0366</v>
+        <v>0.0182</v>
       </c>
       <c r="J45" t="n">
-        <v>0.732</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.95</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.268</v>
+        <v>-0.2357</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.36</v>
+        <v>-4.714</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.95</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0585</v>
+        <v>-0.046</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.17</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.75</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2774</v>
+        <v>-0.2613</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.548</v>
+        <v>-5.226</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.71</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3138</v>
+        <v>-0.2981</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.276</v>
+        <v>-5.962</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3229</v>
+        <v>-0.3074</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.458</v>
+        <v>-6.148</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3411</v>
+        <v>-0.3263</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.822</v>
+        <v>-6.526</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1112</v>
+        <v>1.1254</v>
       </c>
       <c r="J52" t="n">
-        <v>31.1136</v>
+        <v>31.5112</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3288</v>
+        <v>0.2897</v>
       </c>
       <c r="J53" t="n">
-        <v>9.2064</v>
+        <v>8.111599999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.03</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1273</v>
+        <v>0.1033</v>
       </c>
       <c r="J54" t="n">
-        <v>3.5644</v>
+        <v>2.8924</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3547</v>
+        <v>-0.3121</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.9316</v>
+        <v>-8.738799999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5774</v>
+        <v>-0.5381</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.1672</v>
+        <v>-15.0668</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.62</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0337</v>
+        <v>1.0085</v>
       </c>
       <c r="J57" t="n">
-        <v>28.9436</v>
+        <v>28.238</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.29</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5673</v>
+        <v>0.5075</v>
       </c>
       <c r="J58" t="n">
-        <v>15.8844</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.84</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2169</v>
+        <v>-0.1964</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.0732</v>
+        <v>-5.4992</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2574</v>
+        <v>-0.2379</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.2072</v>
+        <v>-6.6612</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3247</v>
+        <v>-0.3087</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.0916</v>
+        <v>-8.643599999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.3</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6513</v>
+        <v>0.6031</v>
       </c>
       <c r="J62" t="n">
-        <v>17.5851</v>
+        <v>16.2837</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.92</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1119</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>-3.0213</v>
+        <v>-2.6244</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.76</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2768</v>
+        <v>-0.2583</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.4736</v>
+        <v>-6.9741</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.66</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3696</v>
+        <v>-0.3557</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.979200000000001</v>
+        <v>-9.603899999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.61</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4145</v>
+        <v>-0.4044</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.1915</v>
+        <v>-10.9188</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2143</v>
+        <v>1.2297</v>
       </c>
       <c r="J67" t="n">
-        <v>32.7861</v>
+        <v>33.2019</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.24</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6242</v>
+        <v>0.5944</v>
       </c>
       <c r="J68" t="n">
-        <v>16.8534</v>
+        <v>16.0488</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.23</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6035</v>
+        <v>0.5732</v>
       </c>
       <c r="J69" t="n">
-        <v>16.2945</v>
+        <v>15.4764</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.2</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5394</v>
+        <v>0.5077</v>
       </c>
       <c r="J70" t="n">
-        <v>14.5638</v>
+        <v>13.7079</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0425</v>
+        <v>-0.0373</v>
       </c>
       <c r="J71" t="n">
-        <v>-1.1475</v>
+        <v>-1.0071</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.17</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3859</v>
+        <v>0.3302</v>
       </c>
       <c r="J72" t="n">
-        <v>10.0334</v>
+        <v>8.5852</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.14</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3318</v>
+        <v>0.279</v>
       </c>
       <c r="J73" t="n">
-        <v>8.626799999999999</v>
+        <v>7.254</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0571</v>
+        <v>-0.045</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.4846</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.82</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2307</v>
+        <v>-0.2104</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.9982</v>
+        <v>-5.4704</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2408</v>
+        <v>-0.2206</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.2608</v>
+        <v>-5.7356</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.29</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7448</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>19.3648</v>
+        <v>18.5952</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.28</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7241</v>
+        <v>0.6933</v>
       </c>
       <c r="J78" t="n">
-        <v>18.8266</v>
+        <v>18.0258</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2095</v>
+        <v>0.18</v>
       </c>
       <c r="J79" t="n">
-        <v>5.447</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1478</v>
+        <v>0.1232</v>
       </c>
       <c r="J80" t="n">
-        <v>3.8428</v>
+        <v>3.2032</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.04</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1478</v>
+        <v>0.1232</v>
       </c>
       <c r="J81" t="n">
-        <v>3.8428</v>
+        <v>3.2032</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.69</v>
       </c>
       <c r="I82" t="n">
-        <v>1.307</v>
+        <v>1.3278</v>
       </c>
       <c r="J82" t="n">
-        <v>28.754</v>
+        <v>29.2116</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.66</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2697</v>
+        <v>1.2891</v>
       </c>
       <c r="J83" t="n">
-        <v>27.9334</v>
+        <v>28.3602</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.41</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9301</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>20.4622</v>
+        <v>20.3918</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.37</v>
       </c>
       <c r="I85" t="n">
-        <v>0.8568</v>
+        <v>0.8476</v>
       </c>
       <c r="J85" t="n">
-        <v>18.8496</v>
+        <v>18.6472</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.1</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2714</v>
+        <v>0.2387</v>
       </c>
       <c r="J86" t="n">
-        <v>5.9708</v>
+        <v>5.2514</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.09</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3421</v>
+        <v>0.3119</v>
       </c>
       <c r="J87" t="n">
-        <v>7.5262</v>
+        <v>6.8618</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.66</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.351</v>
+        <v>-0.3384</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.722</v>
+        <v>-7.4448</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3686</v>
+        <v>-0.3565</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.1092</v>
+        <v>-7.843</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.55</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4482</v>
+        <v>-0.4411</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.8604</v>
+        <v>-9.7042</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.49</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.501</v>
+        <v>-0.4993</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.022</v>
+        <v>-10.9846</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.56</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1903</v>
+        <v>1.2052</v>
       </c>
       <c r="J92" t="n">
-        <v>35.709</v>
+        <v>36.156</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.16</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4591</v>
+        <v>0.4236</v>
       </c>
       <c r="J93" t="n">
-        <v>13.773</v>
+        <v>12.708</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2868</v>
+        <v>0.2543</v>
       </c>
       <c r="J94" t="n">
-        <v>8.603999999999999</v>
+        <v>7.629</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.07</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2317</v>
+        <v>0.2016</v>
       </c>
       <c r="J95" t="n">
-        <v>6.951</v>
+        <v>6.048</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.03</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1073</v>
+        <v>0.0867</v>
       </c>
       <c r="J96" t="n">
-        <v>3.219</v>
+        <v>2.601</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.46</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8468</v>
+        <v>0.7995</v>
       </c>
       <c r="J97" t="n">
-        <v>25.404</v>
+        <v>23.985</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.16</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3681</v>
+        <v>0.3132</v>
       </c>
       <c r="J98" t="n">
-        <v>11.043</v>
+        <v>9.396000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2103</v>
+        <v>-0.1897</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.309</v>
+        <v>-5.691</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.77</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2801</v>
+        <v>-0.2612</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.403</v>
+        <v>-7.836</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3644</v>
+        <v>-0.3507</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.932</v>
+        <v>-10.521</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.88</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.1157</v>
+        <v>-0.0958</v>
       </c>
       <c r="J102" t="n">
-        <v>-2.314</v>
+        <v>-1.916</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.67</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3361</v>
+        <v>-0.3257</v>
       </c>
       <c r="J103" t="n">
-        <v>-6.722</v>
+        <v>-6.514</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.66</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3452</v>
+        <v>-0.335</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.904</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.51</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4751</v>
+        <v>-0.4708</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.502000000000001</v>
+        <v>-9.416</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.41</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5631</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.262</v>
+        <v>-11.382</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7078</v>
+        <v>0.6378</v>
       </c>
       <c r="J107" t="n">
-        <v>14.156</v>
+        <v>12.756</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6612</v>
+        <v>0.5923</v>
       </c>
       <c r="J108" t="n">
-        <v>13.224</v>
+        <v>11.846</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.48</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5766</v>
+        <v>0.5108</v>
       </c>
       <c r="J109" t="n">
-        <v>11.532</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.46</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5578</v>
+        <v>0.4928</v>
       </c>
       <c r="J110" t="n">
-        <v>11.156</v>
+        <v>9.856</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.26</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3483</v>
+        <v>0.2956</v>
       </c>
       <c r="J111" t="n">
-        <v>6.966</v>
+        <v>5.912</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.42</v>
       </c>
       <c r="I112" t="n">
-        <v>0.978</v>
+        <v>0.9718</v>
       </c>
       <c r="J112" t="n">
-        <v>26.406</v>
+        <v>26.2386</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.41</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9606</v>
+        <v>0.9516</v>
       </c>
       <c r="J113" t="n">
-        <v>25.9362</v>
+        <v>25.6932</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8665</v>
+        <v>0.8476</v>
       </c>
       <c r="J114" t="n">
-        <v>23.3955</v>
+        <v>22.8852</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.98</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1398</v>
+        <v>-0.1128</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.7746</v>
+        <v>-3.0456</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.97</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1764</v>
+        <v>-0.1454</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.7628</v>
+        <v>-3.9258</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.28</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6171</v>
+        <v>0.5671</v>
       </c>
       <c r="J117" t="n">
-        <v>16.6617</v>
+        <v>15.3117</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.85</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1889</v>
+        <v>-0.1707</v>
       </c>
       <c r="J118" t="n">
-        <v>-5.1003</v>
+        <v>-4.6089</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.74</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2959</v>
+        <v>-0.278</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.9893</v>
+        <v>-7.506</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.72</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3147</v>
+        <v>-0.2975</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.4969</v>
+        <v>-8.032500000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3607</v>
+        <v>-0.3462</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.738899999999999</v>
+        <v>-9.3474</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1349</v>
+        <v>1.1497</v>
       </c>
       <c r="J122" t="n">
-        <v>34.047</v>
+        <v>34.491</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.28</v>
       </c>
       <c r="I123" t="n">
-        <v>0.74</v>
+        <v>0.709</v>
       </c>
       <c r="J123" t="n">
-        <v>22.2</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.99</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0718</v>
+        <v>-0.0521</v>
       </c>
       <c r="J124" t="n">
-        <v>-2.154</v>
+        <v>-1.563</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3033</v>
+        <v>-0.262</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.099</v>
+        <v>-7.86</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.71</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8033</v>
+        <v>-0.78</v>
       </c>
       <c r="J126" t="n">
-        <v>-24.099</v>
+        <v>-23.4</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.5</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8806</v>
+        <v>0.8317</v>
       </c>
       <c r="J127" t="n">
-        <v>26.418</v>
+        <v>24.951</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.99</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0287</v>
+        <v>-0.0204</v>
       </c>
       <c r="J128" t="n">
-        <v>-0.861</v>
+        <v>-0.612</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.95</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0902</v>
+        <v>-0.0737</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.706</v>
+        <v>-2.211</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.128</v>
+        <v>-0.1089</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.84</v>
+        <v>-3.267</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1514</v>
+        <v>-0.1314</v>
       </c>
       <c r="J131" t="n">
-        <v>-4.542</v>
+        <v>-3.942</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.11</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2693</v>
+        <v>0.2215</v>
       </c>
       <c r="J132" t="n">
-        <v>8.079000000000001</v>
+        <v>6.645</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.09</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2303</v>
+        <v>0.1863</v>
       </c>
       <c r="J133" t="n">
-        <v>6.909</v>
+        <v>5.589</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1895</v>
+        <v>0.1501</v>
       </c>
       <c r="J134" t="n">
-        <v>5.685</v>
+        <v>4.503</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.95</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0871</v>
+        <v>-0.0712</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.613</v>
+        <v>-2.136</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2027</v>
+        <v>-0.1821</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.081</v>
+        <v>-5.463</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.34</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8599</v>
+        <v>0.8381</v>
       </c>
       <c r="J137" t="n">
-        <v>25.797</v>
+        <v>25.143</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4935</v>
+        <v>0.4536</v>
       </c>
       <c r="J138" t="n">
-        <v>14.805</v>
+        <v>13.608</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3496</v>
+        <v>0.3115</v>
       </c>
       <c r="J139" t="n">
-        <v>10.488</v>
+        <v>9.345000000000001</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.97</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1526</v>
+        <v>-0.1214</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.578</v>
+        <v>-3.642</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.89</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3873</v>
+        <v>-0.3445</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.619</v>
+        <v>-10.335</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9273</v>
+        <v>0.8832</v>
       </c>
       <c r="J142" t="n">
-        <v>23.1825</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.24</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4916</v>
+        <v>0.4326</v>
       </c>
       <c r="J143" t="n">
-        <v>12.29</v>
+        <v>10.815</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.96</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0604</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.885</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2458</v>
+        <v>-0.2259</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.145</v>
+        <v>-5.6475</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.65</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3962</v>
+        <v>-0.386</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.904999999999999</v>
+        <v>-9.65</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.82</v>
       </c>
       <c r="I147" t="n">
-        <v>1.528</v>
+        <v>1.5673</v>
       </c>
       <c r="J147" t="n">
-        <v>38.2</v>
+        <v>39.1825</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.07</v>
       </c>
       <c r="I148" t="n">
-        <v>0.23</v>
+        <v>0.2002</v>
       </c>
       <c r="J148" t="n">
-        <v>5.75</v>
+        <v>5.005</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.06</v>
       </c>
       <c r="I149" t="n">
-        <v>0.201</v>
+        <v>0.1728</v>
       </c>
       <c r="J149" t="n">
-        <v>5.025</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.06</v>
       </c>
       <c r="I150" t="n">
-        <v>0.201</v>
+        <v>0.1728</v>
       </c>
       <c r="J150" t="n">
-        <v>5.025</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.95</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2359</v>
+        <v>-0.1992</v>
       </c>
       <c r="J151" t="n">
-        <v>-5.8975</v>
+        <v>-4.98</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0921</v>
+        <v>-0.0718</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.6578</v>
+        <v>-1.2924</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1407</v>
+        <v>-0.122</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.5326</v>
+        <v>-2.196</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.55</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4405</v>
+        <v>-0.4335</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.929</v>
+        <v>-7.803</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.48</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5021</v>
+        <v>-0.5004</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.037800000000001</v>
+        <v>-9.007199999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.36</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6075</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.935</v>
+        <v>-11.169</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.19</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1453</v>
+        <v>1.1102</v>
       </c>
       <c r="J157" t="n">
-        <v>20.6154</v>
+        <v>19.9836</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.62</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7016</v>
+        <v>0.6335</v>
       </c>
       <c r="J158" t="n">
-        <v>12.6288</v>
+        <v>11.403</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.6</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6834</v>
+        <v>0.6158</v>
       </c>
       <c r="J159" t="n">
-        <v>12.3012</v>
+        <v>11.0844</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.29</v>
       </c>
       <c r="I160" t="n">
-        <v>0.376</v>
+        <v>0.3218</v>
       </c>
       <c r="J160" t="n">
-        <v>6.768</v>
+        <v>5.7924</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.09</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1258</v>
+        <v>0.0939</v>
       </c>
       <c r="J161" t="n">
-        <v>2.2644</v>
+        <v>1.6902</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.92</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5834</v>
+        <v>1.6211</v>
       </c>
       <c r="J162" t="n">
-        <v>34.8348</v>
+        <v>35.6642</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.42</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9465</v>
+        <v>0.9456</v>
       </c>
       <c r="J163" t="n">
-        <v>20.823</v>
+        <v>20.8032</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.35</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8175</v>
+        <v>0.8061</v>
       </c>
       <c r="J164" t="n">
-        <v>17.985</v>
+        <v>17.7342</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.33</v>
       </c>
       <c r="I165" t="n">
-        <v>0.7789</v>
+        <v>0.7648</v>
       </c>
       <c r="J165" t="n">
-        <v>17.1358</v>
+        <v>16.8256</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.26</v>
       </c>
       <c r="I166" t="n">
-        <v>0.6381</v>
+        <v>0.6155</v>
       </c>
       <c r="J166" t="n">
-        <v>14.0382</v>
+        <v>13.541</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.01</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1301</v>
+        <v>0.1178</v>
       </c>
       <c r="J167" t="n">
-        <v>2.8622</v>
+        <v>2.5916</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.78</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2417</v>
+        <v>-0.2272</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.3174</v>
+        <v>-4.9984</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.6</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.405</v>
+        <v>-0.3946</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.91</v>
+        <v>-8.6812</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.54</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4581</v>
+        <v>-0.4518</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.0782</v>
+        <v>-9.9396</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.54</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4581</v>
+        <v>-0.4518</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.0782</v>
+        <v>-9.9396</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8629</v>
+        <v>0.8415</v>
       </c>
       <c r="J172" t="n">
-        <v>31.0644</v>
+        <v>30.294</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.1</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3256</v>
+        <v>0.2878</v>
       </c>
       <c r="J173" t="n">
-        <v>11.7216</v>
+        <v>10.3608</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.08</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2739</v>
+        <v>0.2384</v>
       </c>
       <c r="J174" t="n">
-        <v>9.8604</v>
+        <v>8.5824</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0132</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="J175" t="n">
-        <v>-0.4752</v>
+        <v>-0.324</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.91</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3321</v>
+        <v>-0.2899</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.9556</v>
+        <v>-10.4364</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.1</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2466</v>
+        <v>0.2014</v>
       </c>
       <c r="J177" t="n">
-        <v>8.877599999999999</v>
+        <v>7.2504</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1865</v>
+        <v>0.1482</v>
       </c>
       <c r="J178" t="n">
-        <v>6.714</v>
+        <v>5.3352</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.03</v>
       </c>
       <c r="I179" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0723</v>
       </c>
       <c r="J179" t="n">
-        <v>3.4812</v>
+        <v>2.6028</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0704</v>
+        <v>0.0512</v>
       </c>
       <c r="J180" t="n">
-        <v>2.5344</v>
+        <v>1.8432</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0603</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.7108</v>
+        <v>-2.1708</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.36</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8801</v>
+        <v>0.8607</v>
       </c>
       <c r="J182" t="n">
-        <v>30.8035</v>
+        <v>30.1245</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.35</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8603</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="J183" t="n">
-        <v>30.1105</v>
+        <v>29.372</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.579</v>
       </c>
       <c r="J184" t="n">
-        <v>21.469</v>
+        <v>20.265</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1996</v>
+        <v>-0.165</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.986</v>
+        <v>-5.775</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.262</v>
+        <v>-0.2234</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.17</v>
+        <v>-7.819</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.41</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7703</v>
+        <v>0.7178</v>
       </c>
       <c r="J187" t="n">
-        <v>26.9605</v>
+        <v>25.123</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.11</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2742</v>
+        <v>0.2256</v>
       </c>
       <c r="J188" t="n">
-        <v>9.597</v>
+        <v>7.896</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.97</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0574</v>
+        <v>-0.0452</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.009</v>
+        <v>-1.582</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.75</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2999</v>
+        <v>-0.2819</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.4965</v>
+        <v>-9.8665</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3466</v>
+        <v>-0.3316</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.131</v>
+        <v>-11.606</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.94</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5896</v>
+        <v>1.6279</v>
       </c>
       <c r="J192" t="n">
-        <v>30.2024</v>
+        <v>30.9301</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.57</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1467</v>
+        <v>1.1665</v>
       </c>
       <c r="J193" t="n">
-        <v>21.7873</v>
+        <v>22.1635</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.52</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0852</v>
+        <v>1.1039</v>
       </c>
       <c r="J194" t="n">
-        <v>20.6188</v>
+        <v>20.9741</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.38</v>
       </c>
       <c r="I195" t="n">
-        <v>0.8623</v>
+        <v>0.8568</v>
       </c>
       <c r="J195" t="n">
-        <v>16.3837</v>
+        <v>16.2792</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.34</v>
       </c>
       <c r="I196" t="n">
-        <v>0.7857</v>
+        <v>0.7742</v>
       </c>
       <c r="J196" t="n">
-        <v>14.9283</v>
+        <v>14.7098</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.86</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.1372</v>
+        <v>-0.1176</v>
       </c>
       <c r="J197" t="n">
-        <v>-2.6068</v>
+        <v>-2.2344</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.77</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2367</v>
+        <v>-0.2221</v>
       </c>
       <c r="J198" t="n">
-        <v>-4.4973</v>
+        <v>-4.2199</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4301</v>
+        <v>-0.4227</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.171900000000001</v>
+        <v>-8.0313</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.47</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5092</v>
+        <v>-0.5083</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.674799999999999</v>
+        <v>-9.6577</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.43</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5444</v>
+        <v>-0.5478</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.3436</v>
+        <v>-10.4082</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.3</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6368</v>
+        <v>0.5848</v>
       </c>
       <c r="J202" t="n">
-        <v>15.2832</v>
+        <v>14.0352</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.99</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0153</v>
+        <v>-0.0108</v>
       </c>
       <c r="J203" t="n">
-        <v>-0.3672</v>
+        <v>-0.2592</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.78</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.261</v>
+        <v>-0.2417</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.264</v>
+        <v>-5.8008</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.7</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3366</v>
+        <v>-0.3205</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.0784</v>
+        <v>-7.692</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3822</v>
+        <v>-0.3694</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.172800000000001</v>
+        <v>-8.865600000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.44</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0037</v>
+        <v>1.0026</v>
       </c>
       <c r="J207" t="n">
-        <v>24.0888</v>
+        <v>24.0624</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.44</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0037</v>
+        <v>1.0026</v>
       </c>
       <c r="J208" t="n">
-        <v>24.0888</v>
+        <v>24.0624</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.29</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7226</v>
+        <v>0.6972</v>
       </c>
       <c r="J209" t="n">
-        <v>17.3424</v>
+        <v>16.7328</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.23</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6018</v>
+        <v>0.5722</v>
       </c>
       <c r="J210" t="n">
-        <v>14.4432</v>
+        <v>13.7328</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3084</v>
+        <v>-0.2703</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.4016</v>
+        <v>-6.4872</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.9</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9054</v>
       </c>
       <c r="J212" t="n">
-        <v>21.3246</v>
+        <v>19.9188</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.51</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6109</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="J213" t="n">
-        <v>13.4398</v>
+        <v>11.9196</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.45</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5523</v>
+        <v>0.4856</v>
       </c>
       <c r="J214" t="n">
-        <v>12.1506</v>
+        <v>10.6832</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.06</v>
       </c>
       <c r="I215" t="n">
-        <v>0.0921</v>
+        <v>0.067</v>
       </c>
       <c r="J215" t="n">
-        <v>2.0262</v>
+        <v>1.474</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.06</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0921</v>
+        <v>0.067</v>
       </c>
       <c r="J216" t="n">
-        <v>2.0262</v>
+        <v>1.474</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.01</v>
       </c>
       <c r="I217" t="n">
-        <v>0.0853</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J217" t="n">
-        <v>1.8766</v>
+        <v>1.7864</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.77</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2577</v>
+        <v>-0.2422</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.6694</v>
+        <v>-5.3284</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3301</v>
+        <v>-0.3152</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.2622</v>
+        <v>-6.9344</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3301</v>
+        <v>-0.3152</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.2622</v>
+        <v>-6.9344</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.54</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4639</v>
+        <v>-0.4583</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.2058</v>
+        <v>-10.0826</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.32</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6259</v>
+        <v>0.5673</v>
       </c>
       <c r="J222" t="n">
-        <v>18.1511</v>
+        <v>16.4517</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.12</v>
       </c>
       <c r="I223" t="n">
-        <v>0.289</v>
+        <v>0.2395</v>
       </c>
       <c r="J223" t="n">
-        <v>8.381</v>
+        <v>6.9455</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.03</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0988</v>
+        <v>0.0732</v>
       </c>
       <c r="J224" t="n">
-        <v>2.8652</v>
+        <v>2.1228</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.92</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1245</v>
+        <v>-0.1058</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.6105</v>
+        <v>-3.0682</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3849</v>
+        <v>-0.3733</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.1621</v>
+        <v>-10.8257</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.25</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6763</v>
+        <v>0.6415</v>
       </c>
       <c r="J227" t="n">
-        <v>19.6127</v>
+        <v>18.6035</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.2</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5659</v>
+        <v>0.5266</v>
       </c>
       <c r="J228" t="n">
-        <v>16.4111</v>
+        <v>15.2714</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.14</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4261</v>
+        <v>0.3855</v>
       </c>
       <c r="J229" t="n">
-        <v>12.3569</v>
+        <v>11.1795</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.93</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2745</v>
+        <v>-0.2343</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.9605</v>
+        <v>-6.7947</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.87</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4351</v>
+        <v>-0.3922</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.6179</v>
+        <v>-11.3738</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.56</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1888</v>
+        <v>1.2036</v>
       </c>
       <c r="J232" t="n">
-        <v>35.664</v>
+        <v>36.108</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5462</v>
+        <v>0.5115</v>
       </c>
       <c r="J233" t="n">
-        <v>16.386</v>
+        <v>15.345</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.14</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4117</v>
+        <v>0.3767</v>
       </c>
       <c r="J234" t="n">
-        <v>12.351</v>
+        <v>11.301</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.06</v>
       </c>
       <c r="I235" t="n">
-        <v>0.2017</v>
+        <v>0.1734</v>
       </c>
       <c r="J235" t="n">
-        <v>6.051</v>
+        <v>5.202</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.98</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1327</v>
+        <v>-0.1055</v>
       </c>
       <c r="J236" t="n">
-        <v>-3.981</v>
+        <v>-3.165</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.24</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5157</v>
+        <v>0.4579</v>
       </c>
       <c r="J237" t="n">
-        <v>15.471</v>
+        <v>13.737</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2635</v>
+        <v>0.2157</v>
       </c>
       <c r="J238" t="n">
-        <v>7.905</v>
+        <v>6.471</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0953</v>
+        <v>-0.0798</v>
       </c>
       <c r="J239" t="n">
-        <v>-2.859</v>
+        <v>-2.394</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2474</v>
+        <v>-0.2274</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.422</v>
+        <v>-6.822</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.65</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3882</v>
+        <v>-0.3763</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.646</v>
+        <v>-11.289</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.54</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1344</v>
+        <v>1.1479</v>
       </c>
       <c r="J242" t="n">
-        <v>27.2256</v>
+        <v>27.5496</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.47</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0394</v>
+        <v>1.0457</v>
       </c>
       <c r="J243" t="n">
-        <v>24.9456</v>
+        <v>25.0968</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.32</v>
       </c>
       <c r="I244" t="n">
-        <v>0.7752</v>
+        <v>0.7554</v>
       </c>
       <c r="J244" t="n">
-        <v>18.6048</v>
+        <v>18.1296</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.21</v>
       </c>
       <c r="I245" t="n">
-        <v>0.5506</v>
+        <v>0.5218</v>
       </c>
       <c r="J245" t="n">
-        <v>13.2144</v>
+        <v>12.5232</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.09</v>
       </c>
       <c r="I246" t="n">
-        <v>0.2632</v>
+        <v>0.2322</v>
       </c>
       <c r="J246" t="n">
-        <v>6.3168</v>
+        <v>5.5728</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.86</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1692</v>
+        <v>-0.1535</v>
       </c>
       <c r="J247" t="n">
-        <v>-4.0608</v>
+        <v>-3.684</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.83</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2011</v>
+        <v>-0.1851</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.8264</v>
+        <v>-4.4424</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.79</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2411</v>
+        <v>-0.2248</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.7864</v>
+        <v>-5.3952</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.76</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2688</v>
+        <v>-0.2524</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.4512</v>
+        <v>-6.0576</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.58</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4315</v>
+        <v>-0.4227</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.356</v>
+        <v>-10.1448</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.13</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3393</v>
+        <v>0.2878</v>
       </c>
       <c r="J252" t="n">
-        <v>9.839700000000001</v>
+        <v>8.3462</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.01</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0634</v>
+        <v>0.0446</v>
       </c>
       <c r="J253" t="n">
-        <v>1.8386</v>
+        <v>1.2934</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.96</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0636</v>
+        <v>-0.0524</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.8444</v>
+        <v>-1.5196</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.78</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2608</v>
+        <v>-0.2416</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.5632</v>
+        <v>-7.0064</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.53</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4877</v>
+        <v>-0.4862</v>
       </c>
       <c r="J256" t="n">
-        <v>-14.1433</v>
+        <v>-14.0998</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.33</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8336</v>
+        <v>0.8098</v>
       </c>
       <c r="J257" t="n">
-        <v>24.1744</v>
+        <v>23.4842</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.32</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8132</v>
+        <v>0.7877</v>
       </c>
       <c r="J258" t="n">
-        <v>23.5828</v>
+        <v>22.8433</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1188</v>
+        <v>0.0969</v>
       </c>
       <c r="J259" t="n">
-        <v>3.4452</v>
+        <v>2.8101</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.97</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1563</v>
+        <v>-0.1249</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.5327</v>
+        <v>-3.6221</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.93</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2818</v>
+        <v>-0.2415</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.1722</v>
+        <v>-7.0035</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.67</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8062</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="J262" t="n">
-        <v>23.3798</v>
+        <v>21.3846</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.24</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3507</v>
+        <v>0.2918</v>
       </c>
       <c r="J263" t="n">
-        <v>10.1703</v>
+        <v>8.462199999999999</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.09</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1606</v>
+        <v>0.125</v>
       </c>
       <c r="J264" t="n">
-        <v>4.6574</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.06</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1147</v>
+        <v>0.0868</v>
       </c>
       <c r="J265" t="n">
-        <v>3.3263</v>
+        <v>2.5172</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.66</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3952</v>
+        <v>-0.3862</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.4608</v>
+        <v>-11.1998</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.11</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2154</v>
+        <v>0.1989</v>
       </c>
       <c r="J267" t="n">
-        <v>6.2466</v>
+        <v>5.7681</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.07</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1522</v>
+        <v>0.1352</v>
       </c>
       <c r="J268" t="n">
-        <v>4.4138</v>
+        <v>3.9208</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.01</v>
       </c>
       <c r="I269" t="n">
-        <v>0.0353</v>
+        <v>0.0266</v>
       </c>
       <c r="J269" t="n">
-        <v>1.0237</v>
+        <v>0.7714</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.97</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0572</v>
+        <v>-0.0451</v>
       </c>
       <c r="J270" t="n">
-        <v>-1.6588</v>
+        <v>-1.3079</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.76</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2899</v>
+        <v>-0.2715</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.4071</v>
+        <v>-7.8735</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.29</v>
       </c>
       <c r="I272" t="n">
-        <v>0.594</v>
+        <v>0.5364</v>
       </c>
       <c r="J272" t="n">
-        <v>16.632</v>
+        <v>15.0192</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.09</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2408</v>
+        <v>0.195</v>
       </c>
       <c r="J273" t="n">
-        <v>6.7424</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.97</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.056</v>
+        <v>-0.0445</v>
       </c>
       <c r="J274" t="n">
-        <v>-1.568</v>
+        <v>-1.246</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2386</v>
+        <v>-0.2184</v>
       </c>
       <c r="J275" t="n">
-        <v>-6.6808</v>
+        <v>-6.1152</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.63</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4072</v>
+        <v>-0.3972</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.4016</v>
+        <v>-11.1216</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.42</v>
       </c>
       <c r="I277" t="n">
-        <v>0.9969</v>
+        <v>0.993</v>
       </c>
       <c r="J277" t="n">
-        <v>27.9132</v>
+        <v>27.804</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.32</v>
       </c>
       <c r="I278" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.7793</v>
       </c>
       <c r="J278" t="n">
-        <v>22.5372</v>
+        <v>21.8204</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.04</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1468</v>
+        <v>0.1223</v>
       </c>
       <c r="J279" t="n">
-        <v>4.1104</v>
+        <v>3.4244</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.03</v>
       </c>
       <c r="I280" t="n">
-        <v>0.1132</v>
+        <v>0.0921</v>
       </c>
       <c r="J280" t="n">
-        <v>3.1696</v>
+        <v>2.5788</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.93</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2877</v>
+        <v>-0.2476</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.0556</v>
+        <v>-6.9328</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.47</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0623</v>
+        <v>1.0696</v>
       </c>
       <c r="J282" t="n">
-        <v>28.6821</v>
+        <v>28.8792</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.8528</v>
+        <v>0.832</v>
       </c>
       <c r="J283" t="n">
-        <v>23.0256</v>
+        <v>22.464</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.32</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7932</v>
+        <v>0.7684</v>
       </c>
       <c r="J284" t="n">
-        <v>21.4164</v>
+        <v>20.7468</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.98</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1349</v>
+        <v>-0.1077</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.6423</v>
+        <v>-2.9079</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.88</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4323</v>
+        <v>-0.3915</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.6721</v>
+        <v>-10.5705</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.17</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4108</v>
+        <v>0.3563</v>
       </c>
       <c r="J287" t="n">
-        <v>11.0916</v>
+        <v>9.620100000000001</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.14</v>
       </c>
       <c r="I288" t="n">
-        <v>0.3552</v>
+        <v>0.3026</v>
       </c>
       <c r="J288" t="n">
-        <v>9.590400000000001</v>
+        <v>8.170199999999999</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.84</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2021</v>
+        <v>-0.1825</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.4567</v>
+        <v>-4.9275</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.7</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3374</v>
+        <v>-0.3213</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.1098</v>
+        <v>-8.6751</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.61</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4187</v>
+        <v>-0.4094</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.3049</v>
+        <v>-11.0538</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.44</v>
       </c>
       <c r="I292" t="n">
-        <v>0.6324</v>
+        <v>0.6646</v>
       </c>
       <c r="J292" t="n">
-        <v>22.7664</v>
+        <v>23.9256</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.16</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2835</v>
+        <v>0.2704</v>
       </c>
       <c r="J293" t="n">
-        <v>10.206</v>
+        <v>9.734400000000001</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.12</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2264</v>
+        <v>0.2105</v>
       </c>
       <c r="J294" t="n">
-        <v>8.150399999999999</v>
+        <v>7.578</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.76</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2923</v>
+        <v>-0.274</v>
       </c>
       <c r="J295" t="n">
-        <v>-10.5228</v>
+        <v>-9.864000000000001</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.57</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4641</v>
+        <v>-0.4611</v>
       </c>
       <c r="J296" t="n">
-        <v>-16.7076</v>
+        <v>-16.5996</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.61</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7595</v>
+        <v>0.6911</v>
       </c>
       <c r="J297" t="n">
-        <v>27.342</v>
+        <v>24.8796</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.08</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1501</v>
+        <v>0.115</v>
       </c>
       <c r="J298" t="n">
-        <v>5.4036</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.96</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0794</v>
+        <v>-0.0639</v>
       </c>
       <c r="J299" t="n">
-        <v>-2.8584</v>
+        <v>-2.3004</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1062</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.8232</v>
+        <v>-3.1824</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.85</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2091</v>
+        <v>-0.1887</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.5276</v>
+        <v>-6.7932</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.65</v>
       </c>
       <c r="I302" t="n">
-        <v>1.2997</v>
+        <v>1.3196</v>
       </c>
       <c r="J302" t="n">
-        <v>31.1928</v>
+        <v>31.6704</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.13</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3821</v>
+        <v>0.3486</v>
       </c>
       <c r="J303" t="n">
-        <v>9.170400000000001</v>
+        <v>8.366400000000001</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.12</v>
       </c>
       <c r="I304" t="n">
-        <v>0.3574</v>
+        <v>0.3242</v>
       </c>
       <c r="J304" t="n">
-        <v>8.5776</v>
+        <v>7.7808</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.12</v>
       </c>
       <c r="I305" t="n">
-        <v>0.3574</v>
+        <v>0.3242</v>
       </c>
       <c r="J305" t="n">
-        <v>8.5776</v>
+        <v>7.7808</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.1</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3063</v>
+        <v>0.2741</v>
       </c>
       <c r="J306" t="n">
-        <v>7.3512</v>
+        <v>6.5784</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.19</v>
       </c>
       <c r="I307" t="n">
-        <v>0.461</v>
+        <v>0.4081</v>
       </c>
       <c r="J307" t="n">
-        <v>11.064</v>
+        <v>9.7944</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.93</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0999</v>
+        <v>-0.0858</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.3976</v>
+        <v>-2.0592</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.9</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1357</v>
+        <v>-0.1196</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.2568</v>
+        <v>-2.8704</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.67</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3607</v>
+        <v>-0.3462</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.6568</v>
+        <v>-8.3088</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.57</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.45</v>
+        <v>-0.4436</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.8</v>
+        <v>-10.6464</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.36</v>
       </c>
       <c r="I312" t="n">
-        <v>0.8734</v>
+        <v>0.8541</v>
       </c>
       <c r="J312" t="n">
-        <v>23.5818</v>
+        <v>23.0607</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.3</v>
       </c>
       <c r="I313" t="n">
-        <v>0.7537</v>
+        <v>0.7264</v>
       </c>
       <c r="J313" t="n">
-        <v>20.3499</v>
+        <v>19.6128</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.24</v>
       </c>
       <c r="I314" t="n">
-        <v>0.6301</v>
+        <v>0.5976</v>
       </c>
       <c r="J314" t="n">
-        <v>17.0127</v>
+        <v>16.1352</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.13</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3864</v>
+        <v>0.352</v>
       </c>
       <c r="J315" t="n">
-        <v>10.4328</v>
+        <v>9.504</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.95</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2366</v>
+        <v>-0.1999</v>
       </c>
       <c r="J316" t="n">
-        <v>-6.3882</v>
+        <v>-5.3973</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.17</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3883</v>
+        <v>0.3325</v>
       </c>
       <c r="J317" t="n">
-        <v>10.4841</v>
+        <v>8.977499999999999</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.16</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3704</v>
+        <v>0.3155</v>
       </c>
       <c r="J318" t="n">
-        <v>10.0008</v>
+        <v>8.5185</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.2707</v>
+        <v>-1.863</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.91</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1331</v>
+        <v>-0.1144</v>
       </c>
       <c r="J320" t="n">
-        <v>-3.5937</v>
+        <v>-3.0888</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.67</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3725</v>
+        <v>-0.3595</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.0575</v>
+        <v>-9.7065</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.44</v>
       </c>
       <c r="I322" t="n">
-        <v>1.0212</v>
+        <v>1.0218</v>
       </c>
       <c r="J322" t="n">
-        <v>27.5724</v>
+        <v>27.5886</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.33</v>
       </c>
       <c r="I323" t="n">
-        <v>0.8171</v>
+        <v>0.7932</v>
       </c>
       <c r="J323" t="n">
-        <v>22.0617</v>
+        <v>21.4164</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.25</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6533</v>
+        <v>0.6209</v>
       </c>
       <c r="J324" t="n">
-        <v>17.6391</v>
+        <v>16.7643</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.17</v>
       </c>
       <c r="I325" t="n">
-        <v>0.4817</v>
+        <v>0.4461</v>
       </c>
       <c r="J325" t="n">
-        <v>13.0059</v>
+        <v>12.0447</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.72</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7995</v>
+        <v>-0.7786</v>
       </c>
       <c r="J326" t="n">
-        <v>-21.5865</v>
+        <v>-21.0222</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.31</v>
       </c>
       <c r="I327" t="n">
-        <v>0.6241</v>
+        <v>0.5668</v>
       </c>
       <c r="J327" t="n">
-        <v>16.8507</v>
+        <v>15.3036</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.09</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2395</v>
+        <v>0.1939</v>
       </c>
       <c r="J328" t="n">
-        <v>6.4665</v>
+        <v>5.2353</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.97</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0563</v>
+        <v>-0.0447</v>
       </c>
       <c r="J329" t="n">
-        <v>-1.5201</v>
+        <v>-1.2069</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.92</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1207</v>
+        <v>-0.1029</v>
       </c>
       <c r="J330" t="n">
-        <v>-3.2589</v>
+        <v>-2.7783</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.53</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4948</v>
+        <v>-0.4952</v>
       </c>
       <c r="J331" t="n">
-        <v>-13.3596</v>
+        <v>-13.3704</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.65</v>
       </c>
       <c r="I332" t="n">
-        <v>1.2833</v>
+        <v>1.3017</v>
       </c>
       <c r="J332" t="n">
-        <v>35.9324</v>
+        <v>36.4476</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.53</v>
       </c>
       <c r="I333" t="n">
-        <v>1.1262</v>
+        <v>1.139</v>
       </c>
       <c r="J333" t="n">
-        <v>31.5336</v>
+        <v>31.892</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.42</v>
       </c>
       <c r="I334" t="n">
-        <v>0.965</v>
+        <v>0.9589</v>
       </c>
       <c r="J334" t="n">
-        <v>27.02</v>
+        <v>26.8492</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.08</v>
       </c>
       <c r="I335" t="n">
-        <v>0.2408</v>
+        <v>0.2106</v>
       </c>
       <c r="J335" t="n">
-        <v>6.7424</v>
+        <v>5.8968</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.8</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.6405</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="J336" t="n">
-        <v>-17.934</v>
+        <v>-17.0912</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.22</v>
       </c>
       <c r="I337" t="n">
-        <v>0.5209</v>
+        <v>0.4697</v>
       </c>
       <c r="J337" t="n">
-        <v>14.5852</v>
+        <v>13.1516</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.87</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1672</v>
+        <v>-0.1502</v>
       </c>
       <c r="J338" t="n">
-        <v>-4.6816</v>
+        <v>-4.2056</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.75</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2848</v>
+        <v>-0.2668</v>
       </c>
       <c r="J339" t="n">
-        <v>-7.9744</v>
+        <v>-7.4704</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3407</v>
+        <v>-0.325</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.5396</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.65</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3771</v>
+        <v>-0.3638</v>
       </c>
       <c r="J341" t="n">
-        <v>-10.5588</v>
+        <v>-10.1864</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.53</v>
       </c>
       <c r="I342" t="n">
-        <v>1.1457</v>
+        <v>1.1587</v>
       </c>
       <c r="J342" t="n">
-        <v>29.7882</v>
+        <v>30.1262</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.5</v>
       </c>
       <c r="I343" t="n">
-        <v>1.1047</v>
+        <v>1.1161</v>
       </c>
       <c r="J343" t="n">
-        <v>28.7222</v>
+        <v>29.0186</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.1</v>
       </c>
       <c r="I344" t="n">
-        <v>0.3106</v>
+        <v>0.2777</v>
       </c>
       <c r="J344" t="n">
-        <v>8.0756</v>
+        <v>7.2202</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.98</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1345</v>
+        <v>-0.1073</v>
       </c>
       <c r="J345" t="n">
-        <v>-3.497</v>
+        <v>-2.7898</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.88</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.432</v>
+        <v>-0.3911</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.232</v>
+        <v>-10.1686</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.23</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5224</v>
+        <v>0.468</v>
       </c>
       <c r="J347" t="n">
-        <v>13.5824</v>
+        <v>12.168</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.97</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.0482</v>
+        <v>-0.0387</v>
       </c>
       <c r="J348" t="n">
-        <v>-1.2532</v>
+        <v>-1.0062</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.84</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.2007</v>
+        <v>-0.1815</v>
       </c>
       <c r="J349" t="n">
-        <v>-5.2182</v>
+        <v>-4.719</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.76</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2794</v>
+        <v>-0.2607</v>
       </c>
       <c r="J350" t="n">
-        <v>-7.2644</v>
+        <v>-6.7782</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.58</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4436</v>
+        <v>-0.4367</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.5336</v>
+        <v>-11.3542</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.61</v>
       </c>
       <c r="I352" t="n">
-        <v>0.7216</v>
+        <v>0.6494</v>
       </c>
       <c r="J352" t="n">
-        <v>18.04</v>
+        <v>16.235</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.38</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4909</v>
+        <v>0.4248</v>
       </c>
       <c r="J353" t="n">
-        <v>12.2725</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.33</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4382</v>
+        <v>0.3755</v>
       </c>
       <c r="J354" t="n">
-        <v>10.955</v>
+        <v>9.387499999999999</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.28</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3849</v>
+        <v>0.3263</v>
       </c>
       <c r="J355" t="n">
-        <v>9.6225</v>
+        <v>8.157500000000001</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.2645</v>
+        <v>-0.2475</v>
       </c>
       <c r="J356" t="n">
-        <v>-6.6125</v>
+        <v>-6.1875</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.13</v>
       </c>
       <c r="I357" t="n">
-        <v>0.2687</v>
+        <v>0.2567</v>
       </c>
       <c r="J357" t="n">
-        <v>6.7175</v>
+        <v>6.4175</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.99</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.0134</v>
+        <v>-0.0091</v>
       </c>
       <c r="J358" t="n">
-        <v>-0.335</v>
+        <v>-0.2275</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.89</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1485</v>
+        <v>-0.1313</v>
       </c>
       <c r="J359" t="n">
-        <v>-3.7125</v>
+        <v>-3.2825</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.71</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3259</v>
+        <v>-0.3092</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.147500000000001</v>
+        <v>-7.73</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.63</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3987</v>
+        <v>-0.3873</v>
       </c>
       <c r="J361" t="n">
-        <v>-9.967499999999999</v>
+        <v>-9.682499999999999</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.32</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6168</v>
+        <v>0.5574</v>
       </c>
       <c r="J362" t="n">
-        <v>18.504</v>
+        <v>16.722</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.21</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4409</v>
+        <v>0.3832</v>
       </c>
       <c r="J363" t="n">
-        <v>13.227</v>
+        <v>11.496</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>0.96</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.0759</v>
+        <v>-0.0608</v>
       </c>
       <c r="J364" t="n">
-        <v>-2.277</v>
+        <v>-1.824</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>0.89</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.162</v>
+        <v>-0.1418</v>
       </c>
       <c r="J365" t="n">
-        <v>-4.86</v>
+        <v>-4.254</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.84</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.2158</v>
+        <v>-0.1953</v>
       </c>
       <c r="J366" t="n">
-        <v>-6.474</v>
+        <v>-5.859</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.28</v>
       </c>
       <c r="I367" t="n">
-        <v>0.7366</v>
+        <v>0.7055</v>
       </c>
       <c r="J367" t="n">
-        <v>22.098</v>
+        <v>21.165</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.09</v>
       </c>
       <c r="I368" t="n">
-        <v>0.2995</v>
+        <v>0.2631</v>
       </c>
       <c r="J368" t="n">
-        <v>8.984999999999999</v>
+        <v>7.893</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.08</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2732</v>
+        <v>0.2381</v>
       </c>
       <c r="J369" t="n">
-        <v>8.196</v>
+        <v>7.143</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>1.06</v>
       </c>
       <c r="I370" t="n">
-        <v>0.2173</v>
+        <v>0.1858</v>
       </c>
       <c r="J370" t="n">
-        <v>6.519</v>
+        <v>5.574</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.95</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.2174</v>
+        <v>-0.1806</v>
       </c>
       <c r="J371" t="n">
-        <v>-6.522</v>
+        <v>-5.418</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.17</v>
       </c>
       <c r="I372" t="n">
-        <v>0.3859</v>
+        <v>0.3302</v>
       </c>
       <c r="J372" t="n">
-        <v>16.2078</v>
+        <v>13.8684</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.05</v>
       </c>
       <c r="I373" t="n">
-        <v>0.1506</v>
+        <v>0.1158</v>
       </c>
       <c r="J373" t="n">
-        <v>6.3252</v>
+        <v>4.8636</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>0.99</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.0245</v>
+        <v>-0.0178</v>
       </c>
       <c r="J374" t="n">
-        <v>-1.029</v>
+        <v>-0.7476</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.91</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1339</v>
+        <v>-0.115</v>
       </c>
       <c r="J375" t="n">
-        <v>-5.6238</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.79</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.2606</v>
+        <v>-0.241</v>
       </c>
       <c r="J376" t="n">
-        <v>-10.9452</v>
+        <v>-10.122</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.42</v>
       </c>
       <c r="I377" t="n">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="J377" t="n">
-        <v>42.1134</v>
+        <v>42.0042</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.24</v>
       </c>
       <c r="I378" t="n">
-        <v>0.643</v>
+        <v>0.6079</v>
       </c>
       <c r="J378" t="n">
-        <v>27.006</v>
+        <v>25.5318</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>1.09</v>
       </c>
       <c r="I379" t="n">
-        <v>0.2954</v>
+        <v>0.2608</v>
       </c>
       <c r="J379" t="n">
-        <v>12.4068</v>
+        <v>10.9536</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.96</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.1919</v>
+        <v>-0.1573</v>
       </c>
       <c r="J380" t="n">
-        <v>-8.059799999999999</v>
+        <v>-6.6066</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.92</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3121</v>
+        <v>-0.2708</v>
       </c>
       <c r="J381" t="n">
-        <v>-13.1082</v>
+        <v>-11.3736</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.37</v>
       </c>
       <c r="I382" t="n">
-        <v>0.7171</v>
+        <v>0.6631</v>
       </c>
       <c r="J382" t="n">
-        <v>19.3617</v>
+        <v>17.9037</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>1.08</v>
       </c>
       <c r="I383" t="n">
-        <v>0.2186</v>
+        <v>0.1751</v>
       </c>
       <c r="J383" t="n">
-        <v>5.9022</v>
+        <v>4.7277</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>0.95</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.0837</v>
+        <v>-0.0688</v>
       </c>
       <c r="J384" t="n">
-        <v>-2.2599</v>
+        <v>-1.8576</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.82</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.2293</v>
+        <v>-0.2089</v>
       </c>
       <c r="J385" t="n">
-        <v>-6.1911</v>
+        <v>-5.6403</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.61</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4256</v>
+        <v>-0.4176</v>
       </c>
       <c r="J386" t="n">
-        <v>-11.4912</v>
+        <v>-11.2752</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.43</v>
       </c>
       <c r="I387" t="n">
-        <v>1.0019</v>
+        <v>0.9992</v>
       </c>
       <c r="J387" t="n">
-        <v>27.0513</v>
+        <v>26.9784</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.32</v>
       </c>
       <c r="I388" t="n">
-        <v>0.794</v>
+        <v>0.7691</v>
       </c>
       <c r="J388" t="n">
-        <v>21.438</v>
+        <v>20.7657</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>1.13</v>
       </c>
       <c r="I389" t="n">
-        <v>0.3864</v>
+        <v>0.352</v>
       </c>
       <c r="J389" t="n">
-        <v>10.4328</v>
+        <v>9.504</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>1.12</v>
       </c>
       <c r="I390" t="n">
-        <v>0.3618</v>
+        <v>0.3278</v>
       </c>
       <c r="J390" t="n">
-        <v>9.768599999999999</v>
+        <v>8.8506</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.98</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.1342</v>
+        <v>-0.107</v>
       </c>
       <c r="J391" t="n">
-        <v>-3.6234</v>
+        <v>-2.889</v>
       </c>
     </row>
     <row r="392">
@@ -18029,10 +18029,10 @@
         <v>1.52</v>
       </c>
       <c r="I392" t="n">
-        <v>0.9291</v>
+        <v>0.8881</v>
       </c>
       <c r="J392" t="n">
-        <v>26.0148</v>
+        <v>24.8668</v>
       </c>
     </row>
     <row r="393">
@@ -18069,10 +18069,10 @@
         <v>1.05</v>
       </c>
       <c r="I393" t="n">
-        <v>0.1488</v>
+        <v>0.1145</v>
       </c>
       <c r="J393" t="n">
-        <v>4.1664</v>
+        <v>3.206</v>
       </c>
     </row>
     <row r="394">
@@ -18109,10 +18109,10 @@
         <v>0.99</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.0249</v>
+        <v>-0.018</v>
       </c>
       <c r="J394" t="n">
-        <v>-0.6972</v>
+        <v>-0.504</v>
       </c>
     </row>
     <row r="395">
@@ -18149,10 +18149,10 @@
         <v>0.78</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.2715</v>
+        <v>-0.2523</v>
       </c>
       <c r="J395" t="n">
-        <v>-7.602</v>
+        <v>-7.0644</v>
       </c>
     </row>
     <row r="396">
@@ -18189,10 +18189,10 @@
         <v>0.63</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.4103</v>
+        <v>-0.4011</v>
       </c>
       <c r="J396" t="n">
-        <v>-11.4884</v>
+        <v>-11.2308</v>
       </c>
     </row>
     <row r="397">
@@ -18229,10 +18229,10 @@
         <v>1.24</v>
       </c>
       <c r="I397" t="n">
-        <v>0.6389</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="J397" t="n">
-        <v>17.8892</v>
+        <v>16.9204</v>
       </c>
     </row>
     <row r="398">
@@ -18269,10 +18269,10 @@
         <v>1.23</v>
       </c>
       <c r="I398" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.5821</v>
       </c>
       <c r="J398" t="n">
-        <v>17.2872</v>
+        <v>16.2988</v>
       </c>
     </row>
     <row r="399">
@@ -18309,10 +18309,10 @@
         <v>1.23</v>
       </c>
       <c r="I399" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.5821</v>
       </c>
       <c r="J399" t="n">
-        <v>17.2872</v>
+        <v>16.2988</v>
       </c>
     </row>
     <row r="400">
@@ -18349,10 +18349,10 @@
         <v>1.03</v>
       </c>
       <c r="I400" t="n">
-        <v>0.1136</v>
+        <v>0.0924</v>
       </c>
       <c r="J400" t="n">
-        <v>3.1808</v>
+        <v>2.5872</v>
       </c>
     </row>
     <row r="401">
@@ -18389,10 +18389,10 @@
         <v>1</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.024</v>
+        <v>-0.0186</v>
       </c>
       <c r="J401" t="n">
-        <v>-0.672</v>
+        <v>-0.5208</v>
       </c>
     </row>
     <row r="402">
@@ -18429,10 +18429,10 @@
         <v>1.85</v>
       </c>
       <c r="I402" t="n">
-        <v>0.9201</v>
+        <v>0.8515</v>
       </c>
       <c r="J402" t="n">
-        <v>18.402</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="403">
@@ -18469,10 +18469,10 @@
         <v>1.67</v>
       </c>
       <c r="I403" t="n">
-        <v>0.7574</v>
+        <v>0.6863</v>
       </c>
       <c r="J403" t="n">
-        <v>15.148</v>
+        <v>13.726</v>
       </c>
     </row>
     <row r="404">
@@ -18509,10 +18509,10 @@
         <v>1.47</v>
       </c>
       <c r="I404" t="n">
-        <v>0.5687</v>
+        <v>0.5024</v>
       </c>
       <c r="J404" t="n">
-        <v>11.374</v>
+        <v>10.048</v>
       </c>
     </row>
     <row r="405">
@@ -18549,10 +18549,10 @@
         <v>1.28</v>
       </c>
       <c r="I405" t="n">
-        <v>0.3736</v>
+        <v>0.3188</v>
       </c>
       <c r="J405" t="n">
-        <v>7.472</v>
+        <v>6.376</v>
       </c>
     </row>
     <row r="406">
@@ -18589,10 +18589,10 @@
         <v>0.95</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.1185</v>
+        <v>-0.104</v>
       </c>
       <c r="J406" t="n">
-        <v>-2.37</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="407">
@@ -18629,10 +18629,10 @@
         <v>0.97</v>
       </c>
       <c r="I407" t="n">
-        <v>-0.0119</v>
+        <v>0.0028</v>
       </c>
       <c r="J407" t="n">
-        <v>-0.238</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="408">
@@ -18669,10 +18669,10 @@
         <v>0.83</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.1886</v>
+        <v>-0.173</v>
       </c>
       <c r="J408" t="n">
-        <v>-3.772</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="409">
@@ -18709,10 +18709,10 @@
         <v>0.66</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.3512</v>
+        <v>-0.3385</v>
       </c>
       <c r="J409" t="n">
-        <v>-7.024</v>
+        <v>-6.77</v>
       </c>
     </row>
     <row r="410">
@@ -18749,10 +18749,10 @@
         <v>0.62</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.3866</v>
+        <v>-0.3752</v>
       </c>
       <c r="J410" t="n">
-        <v>-7.732</v>
+        <v>-7.504</v>
       </c>
     </row>
     <row r="411">
@@ -18789,10 +18789,10 @@
         <v>0.36</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.6143</v>
+        <v>-0.6293</v>
       </c>
       <c r="J411" t="n">
-        <v>-12.286</v>
+        <v>-12.586</v>
       </c>
     </row>
     <row r="412">
@@ -18829,10 +18829,10 @@
         <v>1.38</v>
       </c>
       <c r="I412" t="n">
-        <v>0.7498</v>
+        <v>0.7006</v>
       </c>
       <c r="J412" t="n">
-        <v>20.2446</v>
+        <v>18.9162</v>
       </c>
     </row>
     <row r="413">
@@ -18869,10 +18869,10 @@
         <v>0.95</v>
       </c>
       <c r="I413" t="n">
-        <v>-0.081</v>
+        <v>-0.0675</v>
       </c>
       <c r="J413" t="n">
-        <v>-2.187</v>
+        <v>-1.8225</v>
       </c>
     </row>
     <row r="414">
@@ -18909,10 +18909,10 @@
         <v>0.89</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.1515</v>
+        <v>-0.1329</v>
       </c>
       <c r="J414" t="n">
-        <v>-4.0905</v>
+        <v>-3.5883</v>
       </c>
     </row>
     <row r="415">
@@ -18949,10 +18949,10 @@
         <v>0.89</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.1515</v>
+        <v>-0.1329</v>
       </c>
       <c r="J415" t="n">
-        <v>-4.0905</v>
+        <v>-3.5883</v>
       </c>
     </row>
     <row r="416">
@@ -18989,10 +18989,10 @@
         <v>0.49</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.5252</v>
+        <v>-0.5294</v>
       </c>
       <c r="J416" t="n">
-        <v>-14.1804</v>
+        <v>-14.2938</v>
       </c>
     </row>
     <row r="417">
@@ -19029,10 +19029,10 @@
         <v>1.83</v>
       </c>
       <c r="I417" t="n">
-        <v>1.535</v>
+        <v>1.5741</v>
       </c>
       <c r="J417" t="n">
-        <v>41.445</v>
+        <v>42.5007</v>
       </c>
     </row>
     <row r="418">
@@ -19069,10 +19069,10 @@
         <v>1.2</v>
       </c>
       <c r="I418" t="n">
-        <v>0.5445</v>
+        <v>0.5108</v>
       </c>
       <c r="J418" t="n">
-        <v>14.7015</v>
+        <v>13.7916</v>
       </c>
     </row>
     <row r="419">
@@ -19109,10 +19109,10 @@
         <v>1.14</v>
       </c>
       <c r="I419" t="n">
-        <v>0.4084</v>
+        <v>0.3743</v>
       </c>
       <c r="J419" t="n">
-        <v>11.0268</v>
+        <v>10.1061</v>
       </c>
     </row>
     <row r="420">
@@ -19149,10 +19149,10 @@
         <v>1.1</v>
       </c>
       <c r="I420" t="n">
-        <v>0.3086</v>
+        <v>0.2761</v>
       </c>
       <c r="J420" t="n">
-        <v>8.3322</v>
+        <v>7.4547</v>
       </c>
     </row>
     <row r="421">
@@ -19189,10 +19189,10 @@
         <v>0.78</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.6724</v>
+        <v>-0.6419</v>
       </c>
       <c r="J421" t="n">
-        <v>-18.1548</v>
+        <v>-17.3313</v>
       </c>
     </row>
     <row r="422">
@@ -19229,10 +19229,10 @@
         <v>1.15</v>
       </c>
       <c r="I422" t="n">
-        <v>0.3488</v>
+        <v>0.2949</v>
       </c>
       <c r="J422" t="n">
-        <v>10.1152</v>
+        <v>8.552099999999999</v>
       </c>
     </row>
     <row r="423">
@@ -19269,10 +19269,10 @@
         <v>1.04</v>
       </c>
       <c r="I423" t="n">
-        <v>0.1263</v>
+        <v>0.0953</v>
       </c>
       <c r="J423" t="n">
-        <v>3.6627</v>
+        <v>2.7637</v>
       </c>
     </row>
     <row r="424">
@@ -19309,10 +19309,10 @@
         <v>0.97</v>
       </c>
       <c r="I424" t="n">
-        <v>-0.0574</v>
+        <v>-0.0452</v>
       </c>
       <c r="J424" t="n">
-        <v>-1.6646</v>
+        <v>-1.3108</v>
       </c>
     </row>
     <row r="425">
@@ -19349,10 +19349,10 @@
         <v>0.96</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.0717</v>
+        <v>-0.0577</v>
       </c>
       <c r="J425" t="n">
-        <v>-2.0793</v>
+        <v>-1.6733</v>
       </c>
     </row>
     <row r="426">
@@ -19389,10 +19389,10 @@
         <v>0.82</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.2313</v>
+        <v>-0.2109</v>
       </c>
       <c r="J426" t="n">
-        <v>-6.7077</v>
+        <v>-6.1161</v>
       </c>
     </row>
     <row r="427">
@@ -19429,10 +19429,10 @@
         <v>1.74</v>
       </c>
       <c r="I427" t="n">
-        <v>1.4523</v>
+        <v>1.4889</v>
       </c>
       <c r="J427" t="n">
-        <v>42.1167</v>
+        <v>43.1781</v>
       </c>
     </row>
     <row r="428">
@@ -19469,10 +19469,10 @@
         <v>1.12</v>
       </c>
       <c r="I428" t="n">
-        <v>0.3726</v>
+        <v>0.3346</v>
       </c>
       <c r="J428" t="n">
-        <v>10.8054</v>
+        <v>9.7034</v>
       </c>
     </row>
     <row r="429">
@@ -19509,10 +19509,10 @@
         <v>0.99</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.0772</v>
+        <v>-0.0568</v>
       </c>
       <c r="J429" t="n">
-        <v>-2.2388</v>
+        <v>-1.6472</v>
       </c>
     </row>
     <row r="430">
@@ -19549,10 +19549,10 @@
         <v>0.88</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.4159</v>
+        <v>-0.3732</v>
       </c>
       <c r="J430" t="n">
-        <v>-12.0611</v>
+        <v>-10.8228</v>
       </c>
     </row>
     <row r="431">
@@ -19589,10 +19589,10 @@
         <v>0.82</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.5628</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J431" t="n">
-        <v>-16.3212</v>
+        <v>-15.1873</v>
       </c>
     </row>
   </sheetData>
